--- a/utils/monday_sprint_sprint_2026-13.xlsx
+++ b/utils/monday_sprint_sprint_2026-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1665" uniqueCount="471">
   <si>
     <t>Ticket</t>
   </si>
@@ -87,33 +87,36 @@
     <t>15/04/2026</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>Feito</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Abril</t>
+  </si>
+  <si>
+    <t>37473</t>
+  </si>
+  <si>
+    <t>Bloqueio de apontamento eletrônico - Painel de consulta</t>
+  </si>
+  <si>
+    <t>Boa tarde senhores. Conforme discutido em reunião, abro este chamado para duas situações; 1. Setores a serem liberados a abrir apontamento eletrônico produtivo de sequencias que não tiveram a movimentação da fusão ou setores anteriores a fusão realizada. Corte: 1408/1411/1412/1413/1414/1415/1416/141</t>
+  </si>
+  <si>
+    <t>Bruno da Silva</t>
+  </si>
+  <si>
+    <t>25/03/2026</t>
+  </si>
+  <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>Feito</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Abril</t>
-  </si>
-  <si>
-    <t>37473</t>
-  </si>
-  <si>
-    <t>Bloqueio de apontamento eletrônico - Painel de consulta</t>
-  </si>
-  <si>
-    <t>Boa tarde senhores. Conforme discutido em reunião, abro este chamado para duas situações; 1. Setores a serem liberados a abrir apontamento eletrônico produtivo de sequencias que não tiveram a movimentação da fusão ou setores anteriores a fusão realizada. Corte: 1408/1411/1412/1413/1414/1415/1416/141</t>
-  </si>
-  <si>
-    <t>Bruno da Silva</t>
-  </si>
-  <si>
-    <t>25/03/2026</t>
-  </si>
-  <si>
     <t>A fazer</t>
   </si>
   <si>
@@ -318,6 +321,18 @@
     <t>Incluir OTF Romaneio</t>
   </si>
   <si>
+    <t>Boa tarde Gentileza incluir OTF no romaneio. Dúvidas, estou a disposição.</t>
+  </si>
+  <si>
+    <t>Rafael De Souza</t>
+  </si>
+  <si>
+    <t>07/10/2024</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
     <t>32141</t>
   </si>
   <si>
@@ -375,9 +390,6 @@
     <t>27/10/2025</t>
   </si>
   <si>
-    <t>Outubro</t>
-  </si>
-  <si>
     <t>33549</t>
   </si>
   <si>
@@ -429,849 +441,837 @@
     <t>Alteração de registro de pintura</t>
   </si>
   <si>
-    <t>Sistema de registro de pintura: Teria como o Log aparecer de uma forma parecida com essa descrição? ( Cadastro de quem alterou), (Descrição do que foi alterado Ex. Alterado medição da camada Top Coat com tolerância: Min.: ........., Max.: .........., Medição anterior: ............, Alterado para: ..</t>
+    <t>38154</t>
+  </si>
+  <si>
+    <t>Altona | CC 40104 Bloqueado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Sandro Favor criar uma regra na pré-lista ou requisição para que ao digitar o CC 40104 - 1.5.02.002 - Depósito e Despacho (Embalagem) O SNB veja se a conta contábil utilizada é 26851 - 5.1.2.01.120 - EMBALAGEM. Se a conta contábil for 26851, o SNB deve manter o CC 40104. Se não for a conta </t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>37659</t>
+  </si>
+  <si>
+    <t>Altona || Estoque de Consignados - Contabilização da Devolução</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Preciso alterar a contabilização de requisição de devolução do consignado: Atualmente está assim: D - 32187 C - Estoque Consignado -------------------------------- Mas o correto é: D - Resultado Custo Se for inserto, por exemplo, a conta será 5.1.2.01.115 Centro de Custo - 60600 - 1</t>
+  </si>
+  <si>
+    <t>34223</t>
+  </si>
+  <si>
+    <t>Alterar gráfico IROG - Usinagem</t>
+  </si>
+  <si>
+    <t>Boa tarde Favor realizar alteração no gráfico de cluster, podendo ser utilizado um gráfico de barras na horizontal. Segue abaixo um exemplo de como pode ser o gráfico (no eixo onde está as operações, mostrar os modelos) Att,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>19/09/2025</t>
+  </si>
+  <si>
+    <t>Setembro</t>
+  </si>
+  <si>
+    <t>38108</t>
+  </si>
+  <si>
+    <t>Lentidão no apontamento eletrônico – Mesa Redonda -  Analise</t>
+  </si>
+  <si>
+    <t>Boa tarde, O operador que está em fase de testes com o apontamento eletrônico na mesa redonda relatou que o sistema está apresentando lentidão excessiva, com travamentos frequentes. Solicitamos, por gentileza, a reavaliação do assunto já tratado no chamado nº 36298. Temos um vídeo demonstrativo no q</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>Envio de ofertar trocar o usuário responsável</t>
+  </si>
+  <si>
+    <t>37929</t>
+  </si>
+  <si>
+    <t>Indicador de ACR</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos agora iniciar a implementação dos indicadores para as ACRs e temos alguns pontos a ajustar. 1. Precisamos ter a informação de que tipo de gatilho foi nessa coluna 1. Precisamos ter uma coluna que identifique se já temos anexo (1 - sim / 0 - não) 1. A ideia é termos um um resumo q</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>Atualizar campos: data, hora e prazo da proposta</t>
+  </si>
+  <si>
+    <t>37857</t>
+  </si>
+  <si>
+    <t>INLCUIR ALTERAÇÃO ( ESTAGIO DE FRABRICAÇÃO ) AONDE ALTERA DADOS E APONTAMENTOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos da opção para alterar o estado de fabricação da peça ( bruto ) ou ( usinado, Colaboradores que apontam incorretamente esse estágio prejudica diretamente o Irog, conseguimos incluir esta opção? At.te.,</t>
+  </si>
+  <si>
+    <t>Otavio Zimmermann Neto</t>
+  </si>
+  <si>
+    <t>14/04/2026</t>
+  </si>
+  <si>
+    <t>36722</t>
+  </si>
+  <si>
+    <t>Bloco K - Integração dados Altona / Benner.</t>
+  </si>
+  <si>
+    <t>38159</t>
+  </si>
+  <si>
+    <t>Cadastrar Rota Cinza</t>
+  </si>
+  <si>
+    <t>Bom dia O cadastro da rota Cinza não esta entrando para os operadores.</t>
+  </si>
+  <si>
+    <t>37963</t>
+  </si>
+  <si>
+    <t>Chamado Caminhão Munck - WMS</t>
+  </si>
+  <si>
+    <t>Bom dia Segue chamado para implementar o sistema do WMS no caminhão Munck.</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>37974</t>
+  </si>
+  <si>
+    <t>Problemas na baixa de ordens que estão sendo programadas</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estou abrindo esse chamado referente a uns problemas que estamos tendo quanto as ordens que estamos cadastrando com método e base tempo que agora estão passando pela programação com a caixa "Gerar SS Planejamento" selecionada Ex: OS 327892 é uma preventiva mensal para a ponte rolante 14 c</t>
+  </si>
+  <si>
+    <t>37947</t>
+  </si>
+  <si>
+    <t>Sistema de apontamento - Tablets pó de ferro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia é necessário a melhoria de algumas funções no sistema de apontamento pó de ferro. 1. As sequencias de peças cortadas no dia estão aparecendo para todos os cortadores, precisamos que apenas apareça a sequência cortada para edição e verificação do cortador que cortou a peça. 2. As observações </t>
+  </si>
+  <si>
+    <t>Amanda Vitoria Aroeira Marinho</t>
+  </si>
+  <si>
+    <t>37714</t>
+  </si>
+  <si>
+    <t>Solicitação de inclusão de tela no WMS – Inclusão de saldo no endereço de recebimento</t>
+  </si>
+  <si>
+    <t>Boa tarde! Solicitamos a inclusão de uma tela no WMS do Almoxarifado para inclusão de saldo virtual no endereço de recebimento. Essa funcionalidade se faz necessária pelas seguintes situações operacionais: Quando um material é movimentado para estoque de terceiros, o saldo virtual no WMS acaba sendo</t>
+  </si>
+  <si>
+    <t>07/04/2026</t>
+  </si>
+  <si>
+    <t>38203</t>
+  </si>
+  <si>
+    <t>Melhorias no apontamento eletrônico – Corte Escarfa</t>
+  </si>
+  <si>
+    <t>Boa tarde, Retorno sobre o desenvolvimento do sistema de apontamento eletrônico – corte escarfa: * É necessário que, assim como nos demais sistemas, sejam exibidos modelo e croqui. * Para melhorar a confiabilidade do apontamento, devemos incluir perguntas de confirmação, por exemplo: “Deseja finaliz</t>
+  </si>
+  <si>
+    <t>30/04/2026</t>
+  </si>
+  <si>
+    <t>38053</t>
+  </si>
+  <si>
+    <t>FW: Alteração Liga Stara- EA4257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Solicito uma solução para um problema rotineiro que o setor de orçamento vem enfrentando, caso exista a necessidade de gerar uma simulação, de uma liga nova para itens que já fornecemos. O sistema foi bloqueado no ano passado para alteração de itens que já fornecemos, o que não é errado no </t>
+  </si>
+  <si>
+    <t>Pierro Conrrad da Silva</t>
+  </si>
+  <si>
+    <t>24/04/2026</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Preparar Ambiente</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Backend</t>
+  </si>
+  <si>
+    <t>38052</t>
+  </si>
+  <si>
+    <t>pdi eletronico</t>
+  </si>
+  <si>
+    <t>Preciso que seja ajustado o campo de observação do PDI para o inspetor, pois hoje com o limite de caracteres que tem o inspetor não consegue passar a informação completa para o Analista. att</t>
+  </si>
+  <si>
+    <t>Gerson Mendonça</t>
+  </si>
+  <si>
+    <t>38166</t>
+  </si>
+  <si>
+    <t>ENC: Condição de pagamento  para Consórcio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Richard/Sandro, Por solicitação do financeiro precisamos cadastrar uma nova condição de pagamento: Consorcio que no momento quando criamos aparece como antecipado. Aproveito a oportunidade para gerar um prazo de 15/30/45. @Larissa Gabriely Gaia Alves assim que for gerado os prazos por favor </t>
+  </si>
+  <si>
+    <t>Luciana Bello</t>
+  </si>
+  <si>
+    <t>37692</t>
+  </si>
+  <si>
+    <t>[COMPRAS] Cancelamento de saldo por item</t>
+  </si>
+  <si>
+    <t>Bom dia, Na tela de pedidos temos a opção de cancelar saldo do pedido. Gostaríamos que fosse criada a opção de cancelar o saldo em aberto somente de um material dentro do pedido. Como mostra a imagem, somente um dos itens teve entrada, mas ainda consta como aberto. Gostaríamos de cancelar esse saldo</t>
+  </si>
+  <si>
+    <t>Larissa Gabriely Gaia Alves</t>
+  </si>
+  <si>
+    <t>37690</t>
+  </si>
+  <si>
+    <t>Melhoria chamado 36233 incluir horário ponto como referência</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito uma melhoria no chamado 36233 (automatizar apontamento) para que ele tenha como base o horário ponto, ou seja, puxe desde que ele chegue na empresa até sua saída.</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>32133</t>
+  </si>
+  <si>
+    <t>Novo Recurso</t>
+  </si>
+  <si>
+    <t>Automatização planilha comercial - PARTE 2/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
+  </si>
+  <si>
+    <t>Jacson Schneider Movidesk</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>22/01/2026</t>
+  </si>
+  <si>
+    <t>37783</t>
+  </si>
+  <si>
+    <t>Inclusão coluna no Planilhão</t>
+  </si>
+  <si>
+    <t>Bom dia Flávio, Favor incluir no Planilhão da Carteira UPR uma coluna com a informação se o modelo (ferramental) está bloqueado para produção. Essa informação geramos relatório em: Modelos &gt; Consulta &gt; Cadastrado de Modelos &gt; Por modelo &gt; Conserto de Modelos &gt; Imprimir &gt; Somente em aberto Data inici</t>
+  </si>
+  <si>
+    <t>Caroline Schmitt</t>
+  </si>
+  <si>
+    <t>10/04/2026</t>
+  </si>
+  <si>
+    <t>38156</t>
+  </si>
+  <si>
+    <t>Cadastro de Linhas no Apontamento Eletrônico</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito, por gentileza, o cadastro das linhas Volvo e Alstom no sistema de apontamento eletrônico, conforme abaixo: * Alstom: utilizar o mesmo modelo aplicado à mesa redonda; * Volvo: utilizar o mesmo modelo da fase 4. Fico à disposição para quaisquer dúvidas. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>35602</t>
+  </si>
+  <si>
+    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
+  </si>
+  <si>
+    <t>35890</t>
+  </si>
+  <si>
+    <t>Criar API para receber informações do MES para a abertura da SS</t>
+  </si>
+  <si>
+    <t>31319</t>
+  </si>
+  <si>
+    <t>Ajuste na inclusão de sequência manual no coletor do WMS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de solicitar um ajuste no sistema do coletor WMS para que, ao incluir uma sequência manual, o sistema aceite a entrada independentemente da utilização de letras maiúsculas ou minúsculas. Essa melhoria contribuirá para a padronização do processo e reduzirá possíveis erros operacio</t>
+  </si>
+  <si>
+    <t>Johnny José Rocha</t>
+  </si>
+  <si>
+    <t>25/04/2025</t>
+  </si>
+  <si>
+    <t>23838</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
+  </si>
+  <si>
+    <t>36809</t>
+  </si>
+  <si>
+    <t>FINALIZAR 501</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor finalizar todos os formulários do setor 501 que estão em aberto antes da conclusão do ticket 28147. At.te</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>37190</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>11/03/2026</t>
+  </si>
+  <si>
+    <t>37095</t>
+  </si>
+  <si>
+    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
+  </si>
+  <si>
+    <t>Rodrigo Santos Rocha</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>37672</t>
+  </si>
+  <si>
+    <t>RES: Certificados de Qualidade</t>
+  </si>
+  <si>
+    <t>Bom dia Senhores, Temos algum retorno sobre a demanda abaixo? Atenciosamente, De: Andre Traleski Enviada em: terça-feira, 28 de outubro de 2025 10:26 Para: sistemas@ti-altona.movidesk.com Cc: Maciel Nolli Assunto: ENC: Certificados de Qualidade Bom dia, Favor abrir chamado para verificação das diver</t>
+  </si>
+  <si>
+    <t>Andre Traleski</t>
+  </si>
+  <si>
+    <t>36972</t>
+  </si>
+  <si>
+    <t>Inserir CPC e Ordem de compra automaticamente no GED</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos implementar uma melhoria no sistema de emissão de CPC para que, no momento da criação, a CPC seja automaticamente integrada ao GED. Além disso, é necessário avaliar a possibilidade de incluir a opção de anexar a Ordem de Compra à CPC, garantindo que esse documento também seja e</t>
+  </si>
+  <si>
+    <t>Jaqueline Cogorni Mendes</t>
+  </si>
+  <si>
+    <t>02/03/2026</t>
+  </si>
+  <si>
+    <t>38021</t>
+  </si>
+  <si>
+    <t>RES: Sucata Retorno Mar2026</t>
+  </si>
+  <si>
+    <t>Boa tarde Sandro, Favor incluir o Saldos abaixo em 31/03/2026 no sistemas de requisição, mantendo o mesmo custo médio (Isto é referente aquele problema de não contabilização do refugo nas entradas de sucata retorno em março). Conta Descrição da Conta Código Descrição do Material UN Incluir ou Retira</t>
+  </si>
+  <si>
+    <t>Rafael Pereira</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>36544</t>
+  </si>
+  <si>
+    <t>Sistema de Metas</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., O sistema de cadastro de Metas n?o est? funcionando, visto que fiz o cadastro para os setores de Inspe??o conforme abaixo: O B.I. est? trazendo a informa??o, conforme abaixo: Solicitei ao Felipe que desse uma carga de dados para avaliar, o mesmo fez e o B.I. n?o trouxe as informa??es c</t>
+  </si>
+  <si>
+    <t>Gabriel Lucas Kertichka</t>
+  </si>
+  <si>
+    <t>09/02/2026</t>
+  </si>
+  <si>
+    <t>31158</t>
+  </si>
+  <si>
+    <t>Status movimentação OM -WMS</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme verificado em Consulta O.M., se eu coloco o status de "AGUARDANDO" ele está puxando as OM entregue, ou seja, não está puxando corretamente.</t>
+  </si>
+  <si>
+    <t>14/04/2025</t>
+  </si>
+  <si>
+    <t>36816</t>
+  </si>
+  <si>
+    <t>Gráfico de barras empilhadas “Retrabalhos para aprovação”</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde! Favor elaborar uma página de BI para acompanhamento dos ensaios mecânicos. Esta página deve ser anexa ao sistema já existente "Resultados Metalúrgico" dentro da aba "Qualidade". Anexo, uma descrição de como deve ser esta página. Sugiro que leiam o documento por completo e então marcarmos </t>
+  </si>
+  <si>
+    <t>Andre Gustavo Scharf</t>
+  </si>
+  <si>
+    <t>37412</t>
+  </si>
+  <si>
+    <t>Registro de Preset - Reunião</t>
+  </si>
+  <si>
+    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
   </si>
   <si>
     <t>Lucas Sebold Movidesk</t>
   </si>
   <si>
-    <t>38154</t>
-  </si>
-  <si>
-    <t>Altona | CC 40104 Bloqueado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Sandro Favor criar uma regra na pré-lista ou requisição para que ao digitar o CC 40104 - 1.5.02.002 - Depósito e Despacho (Embalagem) O SNB veja se a conta contábil utilizada é 26851 - 5.1.2.01.120 - EMBALAGEM. Se a conta contábil for 26851, o SNB deve manter o CC 40104. Se não for a conta </t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>29/04/2026</t>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>30722</t>
+  </si>
+  <si>
+    <t>NOVO ESTADO DE FORNECIMENTO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar um novo estado de fornecimento no CPP tela WWCPP221 chamado "I.C sem fundido": Esta opção com liga 0 deve permitir a montagem de conjuntos para serem faturados no depósito sem a necessidade de um item fundido no conjunto. At.te</t>
+  </si>
+  <si>
+    <t>21/03/2025</t>
+  </si>
+  <si>
+    <t>35503</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Usinagem - subáreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na reunião realizada em 02/10/2025, foi discutido o tema apropriação do custeio. Estiveram presentes: Rafael Pereira, Paulo Cruz e Alexandre Longo. Como já existiam dois chamados1 abertos, as tarefas foram inicialmente vinculadas a eles. Porém, com a evolução das demandas, ficou acordada a abertura </t>
+  </si>
+  <si>
+    <t>28/11/2025</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Inspeção - subáreas</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>25/09/2025</t>
+  </si>
+  <si>
+    <t>38074</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO DE NOMENCLATURA DESENHOS CPP</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor renomear os termos abaixo das telas WWCPP221 e TTCPP conforme: "Desenho Fornec." para "Desenho Ref. Cliente". "DESENHOS" para "DESENHOS PARA PRODUÇÃO". At.te</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I -Mapear dados</t>
+  </si>
+  <si>
+    <t>37781</t>
+  </si>
+  <si>
+    <t>Controle de sequência por nota fiscal -Trava no ROMANEIO</t>
+  </si>
+  <si>
+    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>30712</t>
+  </si>
+  <si>
+    <t>Altona || Sistema ERP || Data Inclusão Material</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Eu fiz umas alterações em alguns itens no módulo de materiais e reparei que o sistema está mudando a data de inclusão junto com a alteração do cadastro. Esse problema não impacta em nada meu serviço, no entanto, achei importante avisar. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>36201</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
+  </si>
+  <si>
+    <t>37889</t>
+  </si>
+  <si>
+    <t>Solicitação de Transferência</t>
+  </si>
+  <si>
+    <t>Boa tarde, Por gentileza, poderia realizar a transferência dos itens destacados em verde, conforme ilustrado na imagem abaixo? Essa ação visa melhorar a experiência dos usuários no sistema. At.te</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Apoio - subáreas</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>29847</t>
+  </si>
+  <si>
+    <t>Valor do ICMS Desonerado - XML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde Sandro, O Estado de SC instituiu a obrigação do preenchimento do campo do valor do ICMS desonerado das notas, desde 01/01/2025. Campos a serem preenchidos: vICMSDeson e motDesICMS Dentro do XML da nota nós temos que informar o ICMS que foi desonerado na operação. Como nosso valor de saída </t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>31/01/2025</t>
+  </si>
+  <si>
+    <t>38057</t>
+  </si>
+  <si>
+    <t>Apontamento tablets - pó de ferro</t>
+  </si>
+  <si>
+    <t>Bom dia, as observações das paradas não estão sendo transferidas para o excel, teria como fazer esse ajuste ? Atenciosamente,</t>
+  </si>
+  <si>
+    <t>37792</t>
+  </si>
+  <si>
+    <t>VISUALIZAÇÃO DO PROCEDIMENTO DE DESMOLDAGEM NO AP119</t>
+  </si>
+  <si>
+    <t>Bom dia! No AP119, no formulário de DESMOLDAGEM não aparece nenhum procedimento anexo: Mesmo que ele tenha sido anexado no formulário, durante o preenchimento do AP119: A sugestão é que ele apareça da mesma maneira que os procedimentos aparecem quando anexados em perguntas: Precisamos que o código e</t>
+  </si>
+  <si>
+    <t>38117</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - vaso</t>
+  </si>
+  <si>
+    <t>Solicito melhorias</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>37230</t>
+  </si>
+  <si>
+    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
+  </si>
+  <si>
+    <t>13/03/2026</t>
+  </si>
+  <si>
+    <t>38043</t>
+  </si>
+  <si>
+    <t>Proporção de tempo de processo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reavaliar cálculo de rateio para intervalos iguais: - peças identificadas com divergência, (considerar o peso bruto da peça (OTF)) - EJ4293 1650kg, sequência 018MS; &gt;&gt;00:24:06 minutos - 5230585 506,25kg, sequência 022MP; &gt;&gt;00:22:11 minutos Conforme apontamento, essas duas peças iniciaram o processo </t>
+  </si>
+  <si>
+    <t>23/04/2026</t>
+  </si>
+  <si>
+    <t>08/05/2026</t>
+  </si>
+  <si>
+    <t>37591</t>
+  </si>
+  <si>
+    <t>Passar sistema de Ordens na TV e Gatilhos ACR para WEB</t>
+  </si>
+  <si>
+    <t>Boa tarde, Chamado combinado com o Tiago para fazermos a transição do sistema de TV e ACR da manutenção para a WEB. A ideia é termos mais flexibilidade para trabalhar com o sistema para deixar ele mais moderno e funcional. Muito obrigado. Att,</t>
+  </si>
+  <si>
+    <t>31/03/2026</t>
+  </si>
+  <si>
+    <t>35367</t>
+  </si>
+  <si>
+    <t>Indicadores MTTR e MDT</t>
+  </si>
+  <si>
+    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
+  </si>
+  <si>
+    <t>20/11/2025</t>
+  </si>
+  <si>
+    <t>Criar CARDs Ordens na TV e Gatilhos ACR para WEB (copy)</t>
+  </si>
+  <si>
+    <t>Criar Controlar paginação TV e Gatilhos ACR para WEB</t>
+  </si>
+  <si>
+    <t>38054</t>
+  </si>
+  <si>
+    <t>Criação de Sistema de Gestão de Treinamentos Usinagem</t>
+  </si>
+  <si>
+    <t>Bom dia, O objetivo desse ticket é para discutirmos o desenvolvimento de um Sistema Web de Gestão de Treinamentos para o setor de Usinagem. Na prática o que ele precisa fazer: * Cadastro de operadores, máquinas, instrutores e ementa de treinamentos; * Registro de treinamentos com presença digital, n</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Poburko</t>
+  </si>
+  <si>
+    <t>37298</t>
+  </si>
+  <si>
+    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
+  </si>
+  <si>
+    <t>17/03/2026</t>
+  </si>
+  <si>
+    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
+  </si>
+  <si>
+    <t>37855</t>
+  </si>
+  <si>
+    <t>Estratificação dos dados na tela Anexos do CPP</t>
+  </si>
+  <si>
+    <t>Bom dia, Sres., @Sandro, conforme conversado, precisamos de um botão "excel" para estratificar os dados na tela Anexos do CPP. Segue a tela em questão: Obrigado, Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Gabriel Zancanella</t>
+  </si>
+  <si>
+    <t>37530</t>
+  </si>
+  <si>
+    <t>Layout ofertas exportação</t>
+  </si>
+  <si>
+    <t>38071</t>
+  </si>
+  <si>
+    <t>Avaliação de Ferramenta - LogX Narwall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Estou abrindo o chamado para avaliação da integração com API aberta da Ferramental LogX da Narwal com o sistema de Invoice. Abaixo o link da documentação enviada pela empresa. Desconheço procedimentos, gentileza informar o que há necessidade do nosso lado para avaliação. Acredito que uma </t>
+  </si>
+  <si>
+    <t>37552</t>
+  </si>
+  <si>
+    <t>Requisições BINAAR - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
+  </si>
+  <si>
+    <t>30/03/2026</t>
+  </si>
+  <si>
+    <t>37746</t>
+  </si>
+  <si>
+    <t>Altona || Consignados - Diferença nos saldos</t>
+  </si>
+  <si>
+    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
+  </si>
+  <si>
+    <t>08/04/2026</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos - Reunião</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>20/08/2025</t>
+  </si>
+  <si>
+    <t>37301</t>
+  </si>
+  <si>
+    <t>Registro de solda Digital</t>
+  </si>
+  <si>
+    <t>Boa tarde Maciel, Tudo bem? Maciel, seria possível para o Registro de solda Digital assim que o soldador preencher a sequência o campo de IS já vir automático com as duas IS que estão cadastradas no roteiro? O soldador só iria selecionar a qual ele iria usar dependendo o estágio da peça conforme rot</t>
+  </si>
+  <si>
+    <t>Danilo da Silva Pereira</t>
+  </si>
+  <si>
+    <t>33956</t>
+  </si>
+  <si>
+    <t>Definição de metas de custos de manutenção (META GERAL) (copy)</t>
+  </si>
+  <si>
+    <t>Edson, Por gentileza criar campo para definição de metas para os custos de manutenção.</t>
+  </si>
+  <si>
+    <t>Robmar Xavier</t>
+  </si>
+  <si>
+    <t>05/09/2025</t>
+  </si>
+  <si>
+    <t>36842</t>
+  </si>
+  <si>
+    <t>Ajuste de Layout das ofertas</t>
+  </si>
+  <si>
+    <t>Boa Tarde Maciel, tudo bem? Favor padronizar a fonte das letras em nossas ofertas, após atualização as fontes estão aparecendo desconfiguradas e as ofertas estão saindo com "Feias". Segue exemplo a baixo: Note que os valores, e as informações da peça estão completamente fora do padrão. Aguardo corre</t>
+  </si>
+  <si>
+    <t>Alexandre Girardi</t>
+  </si>
+  <si>
+    <t>24/02/2026</t>
+  </si>
+  <si>
+    <t>37323</t>
+  </si>
+  <si>
+    <t>BOTÃO DE EXCEL NA TELA WCPP22CP1</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar um novo botão de exportar informações para o Excel na tela WCPP22CP1. At.te</t>
+  </si>
+  <si>
+    <t>18/03/2026</t>
+  </si>
+  <si>
+    <t>38435</t>
+  </si>
+  <si>
+    <t>Divergência Integração Requisições FEADLER | BINAAR | KITO</t>
+  </si>
+  <si>
+    <t>Boa tarde a todos! Ações para correção dos registros do processo de requisições e compra de materiais de peças de reposição dos fornecedores FEADLER e BINAAR. 1. @Sandro Schram: orientação do Alexandro é desenvolvimento de melhoria Sistema para lançamento item a item (não item genérico). Como na tel</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
   </si>
   <si>
     <t>12/05/2026</t>
   </si>
   <si>
-    <t>37659</t>
-  </si>
-  <si>
-    <t>Altona || Estoque de Consignados - Contabilização da Devolução</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Preciso alterar a contabilização de requisição de devolução do consignado: Atualmente está assim: D - 32187 C - Estoque Consignado -------------------------------- Mas o correto é: D - Resultado Custo Se for inserto, por exemplo, a conta será 5.1.2.01.115 Centro de Custo - 60600 - 1</t>
-  </si>
-  <si>
-    <t>34223</t>
-  </si>
-  <si>
-    <t>Alterar gráfico IROG - Usinagem</t>
-  </si>
-  <si>
-    <t>Boa tarde Favor realizar alteração no gráfico de cluster, podendo ser utilizado um gráfico de barras na horizontal. Segue abaixo um exemplo de como pode ser o gráfico (no eixo onde está as operações, mostrar os modelos) Att,</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>19/09/2025</t>
-  </si>
-  <si>
-    <t>Setembro</t>
-  </si>
-  <si>
-    <t>38108</t>
-  </si>
-  <si>
-    <t>Lentidão no apontamento eletrônico – Mesa Redonda -  Analise</t>
-  </si>
-  <si>
-    <t>Boa tarde, O operador que está em fase de testes com o apontamento eletrônico na mesa redonda relatou que o sistema está apresentando lentidão excessiva, com travamentos frequentes. Solicitamos, por gentileza, a reavaliação do assunto já tratado no chamado nº 36298. Temos um vídeo demonstrativo no q</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>Envio de ofertar trocar o usuário responsável</t>
-  </si>
-  <si>
-    <t>37929</t>
-  </si>
-  <si>
-    <t>Indicador de ACR</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos agora iniciar a implementação dos indicadores para as ACRs e temos alguns pontos a ajustar. 1. Precisamos ter a informação de que tipo de gatilho foi nessa coluna 1. Precisamos ter uma coluna que identifique se já temos anexo (1 - sim / 0 - não) 1. A ideia é termos um um resumo q</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>Atualizar campos: data, hora e prazo da proposta</t>
-  </si>
-  <si>
-    <t>37857</t>
-  </si>
-  <si>
-    <t>INLCUIR ALTERAÇÃO ( ESTAGIO DE FRABRICAÇÃO ) AONDE ALTERA DADOS E APONTAMENTOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos da opção para alterar o estado de fabricação da peça ( bruto ) ou ( usinado, Colaboradores que apontam incorretamente esse estágio prejudica diretamente o Irog, conseguimos incluir esta opção? At.te.,</t>
-  </si>
-  <si>
-    <t>Otavio Zimmermann Neto</t>
-  </si>
-  <si>
-    <t>14/04/2026</t>
-  </si>
-  <si>
-    <t>36722</t>
-  </si>
-  <si>
-    <t>Bloco K - Integração dados Altona / Benner.</t>
-  </si>
-  <si>
-    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
-  </si>
-  <si>
-    <t>38159</t>
-  </si>
-  <si>
-    <t>Cadastrar Rota Cinza</t>
-  </si>
-  <si>
-    <t>Bom dia O cadastro da rota Cinza não esta entrando para os operadores.</t>
-  </si>
-  <si>
-    <t>Rafael De Souza</t>
-  </si>
-  <si>
-    <t>37963</t>
-  </si>
-  <si>
-    <t>Chamado Caminhão Munck - WMS</t>
-  </si>
-  <si>
-    <t>Bom dia Segue chamado para implementar o sistema do WMS no caminhão Munck.</t>
-  </si>
-  <si>
-    <t>20/04/2026</t>
-  </si>
-  <si>
-    <t>37974</t>
-  </si>
-  <si>
-    <t>Problemas na baixa de ordens que estão sendo programadas</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estou abrindo esse chamado referente a uns problemas que estamos tendo quanto as ordens que estamos cadastrando com método e base tempo que agora estão passando pela programação com a caixa "Gerar SS Planejamento" selecionada Ex: OS 327892 é uma preventiva mensal para a ponte rolante 14 c</t>
-  </si>
-  <si>
-    <t>37947</t>
-  </si>
-  <si>
-    <t>Sistema de apontamento - Tablets pó de ferro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia é necessário a melhoria de algumas funções no sistema de apontamento pó de ferro. 1. As sequencias de peças cortadas no dia estão aparecendo para todos os cortadores, precisamos que apenas apareça a sequência cortada para edição e verificação do cortador que cortou a peça. 2. As observações </t>
-  </si>
-  <si>
-    <t>Amanda Vitoria Aroeira Marinho</t>
-  </si>
-  <si>
-    <t>37714</t>
-  </si>
-  <si>
-    <t>Solicitação de inclusão de tela no WMS – Inclusão de saldo no endereço de recebimento</t>
-  </si>
-  <si>
-    <t>Boa tarde! Solicitamos a inclusão de uma tela no WMS do Almoxarifado para inclusão de saldo virtual no endereço de recebimento. Essa funcionalidade se faz necessária pelas seguintes situações operacionais: Quando um material é movimentado para estoque de terceiros, o saldo virtual no WMS acaba sendo</t>
-  </si>
-  <si>
-    <t>07/04/2026</t>
-  </si>
-  <si>
-    <t>38203</t>
-  </si>
-  <si>
-    <t>Melhorias no apontamento eletrônico – Corte Escarfa</t>
-  </si>
-  <si>
-    <t>Boa tarde, Retorno sobre o desenvolvimento do sistema de apontamento eletrônico – corte escarfa: * É necessário que, assim como nos demais sistemas, sejam exibidos modelo e croqui. * Para melhorar a confiabilidade do apontamento, devemos incluir perguntas de confirmação, por exemplo: “Deseja finaliz</t>
-  </si>
-  <si>
-    <t>30/04/2026</t>
-  </si>
-  <si>
-    <t>38053</t>
-  </si>
-  <si>
-    <t>FW: Alteração Liga Stara- EA4257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Solicito uma solução para um problema rotineiro que o setor de orçamento vem enfrentando, caso exista a necessidade de gerar uma simulação, de uma liga nova para itens que já fornecemos. O sistema foi bloqueado no ano passado para alteração de itens que já fornecemos, o que não é errado no </t>
-  </si>
-  <si>
-    <t>Pierro Conrrad da Silva</t>
-  </si>
-  <si>
-    <t>24/04/2026</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Preparar Ambiente</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Backend</t>
-  </si>
-  <si>
-    <t>38052</t>
-  </si>
-  <si>
-    <t>pdi eletronico</t>
-  </si>
-  <si>
-    <t>Preciso que seja ajustado o campo de observação do PDI para o inspetor, pois hoje com o limite de caracteres que tem o inspetor não consegue passar a informação completa para o Analista. att</t>
-  </si>
-  <si>
-    <t>Gerson Mendonça</t>
-  </si>
-  <si>
-    <t>38166</t>
-  </si>
-  <si>
-    <t>ENC: Condição de pagamento  para Consórcio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Richard/Sandro, Por solicitação do financeiro precisamos cadastrar uma nova condição de pagamento: Consorcio que no momento quando criamos aparece como antecipado. Aproveito a oportunidade para gerar um prazo de 15/30/45. @Larissa Gabriely Gaia Alves assim que for gerado os prazos por favor </t>
-  </si>
-  <si>
-    <t>Luciana Bello</t>
-  </si>
-  <si>
-    <t>37692</t>
-  </si>
-  <si>
-    <t>[COMPRAS] Cancelamento de saldo por item</t>
-  </si>
-  <si>
-    <t>Bom dia, Na tela de pedidos temos a opção de cancelar saldo do pedido. Gostaríamos que fosse criada a opção de cancelar o saldo em aberto somente de um material dentro do pedido. Como mostra a imagem, somente um dos itens teve entrada, mas ainda consta como aberto. Gostaríamos de cancelar esse saldo</t>
-  </si>
-  <si>
-    <t>Larissa Gabriely Gaia Alves</t>
-  </si>
-  <si>
-    <t>37690</t>
-  </si>
-  <si>
-    <t>Melhoria chamado 36233 incluir horário ponto como referência</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito uma melhoria no chamado 36233 (automatizar apontamento) para que ele tenha como base o horário ponto, ou seja, puxe desde que ele chegue na empresa até sua saída.</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>32133</t>
-  </si>
-  <si>
-    <t>Novo Recurso</t>
-  </si>
-  <si>
-    <t>Automatização planilha comercial - PARTE 2/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
-  </si>
-  <si>
-    <t>Jacson Schneider Movidesk</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>22/01/2026</t>
-  </si>
-  <si>
-    <t>37783</t>
-  </si>
-  <si>
-    <t>Inclusão coluna no Planilhão</t>
-  </si>
-  <si>
-    <t>Bom dia Flávio, Favor incluir no Planilhão da Carteira UPR uma coluna com a informação se o modelo (ferramental) está bloqueado para produção. Essa informação geramos relatório em: Modelos &gt; Consulta &gt; Cadastrado de Modelos &gt; Por modelo &gt; Conserto de Modelos &gt; Imprimir &gt; Somente em aberto Data inici</t>
-  </si>
-  <si>
-    <t>Caroline Schmitt</t>
-  </si>
-  <si>
-    <t>10/04/2026</t>
-  </si>
-  <si>
-    <t>38156</t>
-  </si>
-  <si>
-    <t>Cadastro de Linhas no Apontamento Eletrônico</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito, por gentileza, o cadastro das linhas Volvo e Alstom no sistema de apontamento eletrônico, conforme abaixo: * Alstom: utilizar o mesmo modelo aplicado à mesa redonda; * Volvo: utilizar o mesmo modelo da fase 4. Fico à disposição para quaisquer dúvidas. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>35602</t>
-  </si>
-  <si>
-    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
-  </si>
-  <si>
-    <t>35890</t>
-  </si>
-  <si>
-    <t>Criar API para receber informações do MES para a abertura da SS</t>
-  </si>
-  <si>
-    <t>31319</t>
-  </si>
-  <si>
-    <t>Ajuste na inclusão de sequência manual no coletor do WMS</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de solicitar um ajuste no sistema do coletor WMS para que, ao incluir uma sequência manual, o sistema aceite a entrada independentemente da utilização de letras maiúsculas ou minúsculas. Essa melhoria contribuirá para a padronização do processo e reduzirá possíveis erros operacio</t>
-  </si>
-  <si>
-    <t>Johnny José Rocha</t>
-  </si>
-  <si>
-    <t>25/04/2025</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
-  </si>
-  <si>
-    <t>36809</t>
-  </si>
-  <si>
-    <t>FINALIZAR 501</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor finalizar todos os formulários do setor 501 que estão em aberto antes da conclusão do ticket 28147. At.te</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>37190</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>11/03/2026</t>
-  </si>
-  <si>
-    <t>37095</t>
-  </si>
-  <si>
-    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
-  </si>
-  <si>
-    <t>Rodrigo Santos Rocha</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>37672</t>
-  </si>
-  <si>
-    <t>RES: Certificados de Qualidade</t>
-  </si>
-  <si>
-    <t>Bom dia Senhores, Temos algum retorno sobre a demanda abaixo? Atenciosamente, De: Andre Traleski Enviada em: terça-feira, 28 de outubro de 2025 10:26 Para: sistemas@ti-altona.movidesk.com Cc: Maciel Nolli Assunto: ENC: Certificados de Qualidade Bom dia, Favor abrir chamado para verificação das diver</t>
-  </si>
-  <si>
-    <t>Andre Traleski</t>
-  </si>
-  <si>
-    <t>36972</t>
-  </si>
-  <si>
-    <t>Inserir CPC e Ordem de compra automaticamente no GED</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos implementar uma melhoria no sistema de emissão de CPC para que, no momento da criação, a CPC seja automaticamente integrada ao GED. Além disso, é necessário avaliar a possibilidade de incluir a opção de anexar a Ordem de Compra à CPC, garantindo que esse documento também seja e</t>
-  </si>
-  <si>
-    <t>Jaqueline Cogorni Mendes</t>
-  </si>
-  <si>
-    <t>02/03/2026</t>
-  </si>
-  <si>
-    <t>38021</t>
-  </si>
-  <si>
-    <t>RES: Sucata Retorno Mar2026</t>
-  </si>
-  <si>
-    <t>Boa tarde Sandro, Favor incluir o Saldos abaixo em 31/03/2026 no sistemas de requisição, mantendo o mesmo custo médio (Isto é referente aquele problema de não contabilização do refugo nas entradas de sucata retorno em março). Conta Descrição da Conta Código Descrição do Material UN Incluir ou Retira</t>
-  </si>
-  <si>
-    <t>Rafael Pereira</t>
-  </si>
-  <si>
-    <t>11/05/2026</t>
-  </si>
-  <si>
-    <t>36544</t>
-  </si>
-  <si>
-    <t>Sistema de Metas</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., O sistema de cadastro de Metas n?o est? funcionando, visto que fiz o cadastro para os setores de Inspe??o conforme abaixo: O B.I. est? trazendo a informa??o, conforme abaixo: Solicitei ao Felipe que desse uma carga de dados para avaliar, o mesmo fez e o B.I. n?o trouxe as informa??es c</t>
-  </si>
-  <si>
-    <t>Gabriel Lucas Kertichka</t>
-  </si>
-  <si>
-    <t>09/02/2026</t>
-  </si>
-  <si>
-    <t>04/05/2026</t>
-  </si>
-  <si>
-    <t>31158</t>
-  </si>
-  <si>
-    <t>Status movimentação OM -WMS</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme verificado em Consulta O.M., se eu coloco o status de "AGUARDANDO" ele está puxando as OM entregue, ou seja, não está puxando corretamente.</t>
-  </si>
-  <si>
-    <t>14/04/2025</t>
-  </si>
-  <si>
-    <t>36816</t>
-  </si>
-  <si>
-    <t>Gráfico de barras empilhadas “Retrabalhos para aprovação”</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde! Favor elaborar uma página de BI para acompanhamento dos ensaios mecânicos. Esta página deve ser anexa ao sistema já existente "Resultados Metalúrgico" dentro da aba "Qualidade". Anexo, uma descrição de como deve ser esta página. Sugiro que leiam o documento por completo e então marcarmos </t>
-  </si>
-  <si>
-    <t>Andre Gustavo Scharf</t>
-  </si>
-  <si>
-    <t>37412</t>
-  </si>
-  <si>
-    <t>Registro de Preset - Reunião</t>
-  </si>
-  <si>
-    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>30722</t>
-  </si>
-  <si>
-    <t>NOVO ESTADO DE FORNECIMENTO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar um novo estado de fornecimento no CPP tela WWCPP221 chamado "I.C sem fundido": Esta opção com liga 0 deve permitir a montagem de conjuntos para serem faturados no depósito sem a necessidade de um item fundido no conjunto. At.te</t>
-  </si>
-  <si>
-    <t>21/03/2025</t>
-  </si>
-  <si>
-    <t>35503</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Usinagem - subáreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na reunião realizada em 02/10/2025, foi discutido o tema apropriação do custeio. Estiveram presentes: Rafael Pereira, Paulo Cruz e Alexandre Longo. Como já existiam dois chamados1 abertos, as tarefas foram inicialmente vinculadas a eles. Porém, com a evolução das demandas, ficou acordada a abertura </t>
-  </si>
-  <si>
-    <t>28/11/2025</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Inspeção - subáreas</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>25/09/2025</t>
-  </si>
-  <si>
-    <t>38074</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO DE NOMENCLATURA DESENHOS CPP</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor renomear os termos abaixo das telas WWCPP221 e TTCPP conforme: "Desenho Fornec." para "Desenho Ref. Cliente". "DESENHOS" para "DESENHOS PARA PRODUÇÃO". At.te</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I -Mapear dados</t>
-  </si>
-  <si>
-    <t>37781</t>
-  </si>
-  <si>
-    <t>Controle de sequência por nota fiscal -Trava no ROMANEIO</t>
-  </si>
-  <si>
-    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>30712</t>
-  </si>
-  <si>
-    <t>Altona || Sistema ERP || Data Inclusão Material</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Eu fiz umas alterações em alguns itens no módulo de materiais e reparei que o sistema está mudando a data de inclusão junto com a alteração do cadastro. Esse problema não impacta em nada meu serviço, no entanto, achei importante avisar. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>36201</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
-  </si>
-  <si>
-    <t>37889</t>
-  </si>
-  <si>
-    <t>Solicitação de Transferência</t>
-  </si>
-  <si>
-    <t>Boa tarde, Por gentileza, poderia realizar a transferência dos itens destacados em verde, conforme ilustrado na imagem abaixo? Essa ação visa melhorar a experiência dos usuários no sistema. At.te</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Apoio - subáreas</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
-  </si>
-  <si>
-    <t>Alini Ferreira Ganda</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>29847</t>
-  </si>
-  <si>
-    <t>Valor do ICMS Desonerado - XML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde Sandro, O Estado de SC instituiu a obrigação do preenchimento do campo do valor do ICMS desonerado das notas, desde 01/01/2025. Campos a serem preenchidos: vICMSDeson e motDesICMS Dentro do XML da nota nós temos que informar o ICMS que foi desonerado na operação. Como nosso valor de saída </t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>31/01/2025</t>
-  </si>
-  <si>
-    <t>38057</t>
-  </si>
-  <si>
-    <t>Apontamento tablets - pó de ferro</t>
-  </si>
-  <si>
-    <t>Bom dia, as observações das paradas não estão sendo transferidas para o excel, teria como fazer esse ajuste ? Atenciosamente,</t>
-  </si>
-  <si>
-    <t>37792</t>
-  </si>
-  <si>
-    <t>VISUALIZAÇÃO DO PROCEDIMENTO DE DESMOLDAGEM NO AP119</t>
-  </si>
-  <si>
-    <t>Bom dia! No AP119, no formulário de DESMOLDAGEM não aparece nenhum procedimento anexo: Mesmo que ele tenha sido anexado no formulário, durante o preenchimento do AP119: A sugestão é que ele apareça da mesma maneira que os procedimentos aparecem quando anexados em perguntas: Precisamos que o código e</t>
-  </si>
-  <si>
-    <t>38117</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - vaso</t>
-  </si>
-  <si>
-    <t>Solicito melhorias</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>37230</t>
-  </si>
-  <si>
-    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
-  </si>
-  <si>
-    <t>13/03/2026</t>
-  </si>
-  <si>
-    <t>38043</t>
-  </si>
-  <si>
-    <t>Proporção de tempo de processo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reavaliar cálculo de rateio para intervalos iguais: - peças identificadas com divergência, (considerar o peso bruto da peça (OTF)) - EJ4293 1650kg, sequência 018MS; &gt;&gt;00:24:06 minutos - 5230585 506,25kg, sequência 022MP; &gt;&gt;00:22:11 minutos Conforme apontamento, essas duas peças iniciaram o processo </t>
-  </si>
-  <si>
-    <t>23/04/2026</t>
-  </si>
-  <si>
-    <t>13/05/2026</t>
-  </si>
-  <si>
-    <t>37591</t>
-  </si>
-  <si>
-    <t>Passar sistema de Ordens na TV e Gatilhos ACR para WEB</t>
-  </si>
-  <si>
-    <t>Boa tarde, Chamado combinado com o Tiago para fazermos a transição do sistema de TV e ACR da manutenção para a WEB. A ideia é termos mais flexibilidade para trabalhar com o sistema para deixar ele mais moderno e funcional. Muito obrigado. Att,</t>
-  </si>
-  <si>
-    <t>31/03/2026</t>
-  </si>
-  <si>
-    <t>35367</t>
-  </si>
-  <si>
-    <t>Indicadores MTTR e MDT</t>
-  </si>
-  <si>
-    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
-  </si>
-  <si>
-    <t>20/11/2025</t>
-  </si>
-  <si>
-    <t>Criar CARDs Ordens na TV e Gatilhos ACR para WEB (copy)</t>
-  </si>
-  <si>
-    <t>Criar Controlar paginação TV e Gatilhos ACR para WEB</t>
-  </si>
-  <si>
-    <t>38054</t>
-  </si>
-  <si>
-    <t>Criação de Sistema de Gestão de Treinamentos Usinagem</t>
-  </si>
-  <si>
-    <t>Bom dia, O objetivo desse ticket é para discutirmos o desenvolvimento de um Sistema Web de Gestão de Treinamentos para o setor de Usinagem. Na prática o que ele precisa fazer: * Cadastro de operadores, máquinas, instrutores e ementa de treinamentos; * Registro de treinamentos com presença digital, n</t>
-  </si>
-  <si>
-    <t>Pedro Henrique Poburko</t>
-  </si>
-  <si>
-    <t>37298</t>
-  </si>
-  <si>
-    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
-  </si>
-  <si>
-    <t>17/03/2026</t>
-  </si>
-  <si>
-    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
-  </si>
-  <si>
-    <t>37855</t>
-  </si>
-  <si>
-    <t>Estratificação dos dados na tela Anexos do CPP</t>
-  </si>
-  <si>
-    <t>Bom dia, Sres., @Sandro, conforme conversado, precisamos de um botão "excel" para estratificar os dados na tela Anexos do CPP. Segue a tela em questão: Obrigado, Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Gabriel Zancanella</t>
-  </si>
-  <si>
-    <t>37530</t>
-  </si>
-  <si>
-    <t>Layout ofertas exportação</t>
-  </si>
-  <si>
-    <t>38071</t>
-  </si>
-  <si>
-    <t>Avaliação de Ferramenta - LogX Narwall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Estou abrindo o chamado para avaliação da integração com API aberta da Ferramental LogX da Narwal com o sistema de Invoice. Abaixo o link da documentação enviada pela empresa. Desconheço procedimentos, gentileza informar o que há necessidade do nosso lado para avaliação. Acredito que uma </t>
-  </si>
-  <si>
-    <t>37552</t>
-  </si>
-  <si>
-    <t>Requisições BINAAR - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
-  </si>
-  <si>
-    <t>30/03/2026</t>
-  </si>
-  <si>
-    <t>37746</t>
-  </si>
-  <si>
-    <t>Altona || Consignados - Diferença nos saldos</t>
-  </si>
-  <si>
-    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
-  </si>
-  <si>
-    <t>08/04/2026</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos - Reunião</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>20/08/2025</t>
-  </si>
-  <si>
-    <t>37301</t>
-  </si>
-  <si>
-    <t>Registro de solda Digital</t>
-  </si>
-  <si>
-    <t>Boa tarde Maciel, Tudo bem? Maciel, seria possível para o Registro de solda Digital assim que o soldador preencher a sequência o campo de IS já vir automático com as duas IS que estão cadastradas no roteiro? O soldador só iria selecionar a qual ele iria usar dependendo o estágio da peça conforme rot</t>
-  </si>
-  <si>
-    <t>Danilo da Silva Pereira</t>
-  </si>
-  <si>
-    <t>33956</t>
-  </si>
-  <si>
-    <t>Definição de metas de custos de manutenção (META GERAL) (copy)</t>
-  </si>
-  <si>
-    <t>Edson, Por gentileza criar campo para definição de metas para os custos de manutenção.</t>
-  </si>
-  <si>
-    <t>Robmar Xavier</t>
-  </si>
-  <si>
-    <t>05/09/2025</t>
-  </si>
-  <si>
-    <t>36842</t>
-  </si>
-  <si>
-    <t>Ajuste de Layout das ofertas</t>
-  </si>
-  <si>
-    <t>Boa Tarde Maciel, tudo bem? Favor padronizar a fonte das letras em nossas ofertas, após atualização as fontes estão aparecendo desconfiguradas e as ofertas estão saindo com "Feias". Segue exemplo a baixo: Note que os valores, e as informações da peça estão completamente fora do padrão. Aguardo corre</t>
-  </si>
-  <si>
-    <t>Alexandre Girardi</t>
-  </si>
-  <si>
-    <t>24/02/2026</t>
-  </si>
-  <si>
-    <t>37323</t>
-  </si>
-  <si>
-    <t>BOTÃO DE EXCEL NA TELA WCPP22CP1</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar um novo botão de exportar informações para o Excel na tela WCPP22CP1. At.te</t>
-  </si>
-  <si>
-    <t>18/03/2026</t>
-  </si>
-  <si>
-    <t>38435</t>
-  </si>
-  <si>
-    <t>Divergência Integração Requisições FEADLER | BINAAR | KITO</t>
-  </si>
-  <si>
-    <t>Boa tarde a todos! Ações para correção dos registros do processo de requisições e compra de materiais de peças de reposição dos fornecedores FEADLER e BINAAR. 1. @Sandro Schram: orientação do Alexandro é desenvolvimento de melhoria Sistema para lançamento item a item (não item genérico). Como na tel</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
     <t>Maio</t>
   </si>
   <si>
@@ -1299,12 +1299,6 @@
     <t>IDENTIFICADOR ESPECIAL - LOT NUMBER (copy)</t>
   </si>
   <si>
-    <t>Bom dia, Favor criar um sistema de cadastro de identificador especial similar ao já existente da tela de cadastro TCPP45ID e consulta WCPP221J: Favor criar uma nova opção na tela TCPP45ID denominada "Possui controle ID especial?", sendo que se respondida como "SIM" permita o preenchimento dos seguin</t>
-  </si>
-  <si>
-    <t>14/01/2026</t>
-  </si>
-  <si>
     <t>37169</t>
   </si>
   <si>
@@ -1321,15 +1315,6 @@
   </si>
   <si>
     <t>Sequencial number Clientes (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde, Conforme conversado com o Sr. Flavio, precisamos criar uma regrar referente aos clientes da Altona que necessitam de um serial number fora a parte, que anda em paralelo da sequência da peça, um exemplo é a Solar Turbines. Esse "lot number" é criado no momento da programação da sequência q</t>
-  </si>
-  <si>
-    <t>Jackson Souza</t>
-  </si>
-  <si>
-    <t>12/02/2026</t>
   </si>
   <si>
     <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy) (copy) (copy)</t>
@@ -1993,21 +1978,21 @@
         <v>32</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>15</v>
@@ -2019,22 +2004,22 @@
         <v>17</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>24</v>
@@ -2043,15 +2028,15 @@
         <v>25</v>
       </c>
       <c r="M4" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>15</v>
@@ -2063,39 +2048,39 @@
         <v>17</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L5" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M5" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N5" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>15</v>
@@ -2107,10 +2092,10 @@
         <v>17</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G6" s="2" t="s">
         <v>20</v>
@@ -2122,16 +2107,16 @@
         <v>22</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M6" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N6" s="2" t="s">
         <v>27</v>
@@ -2139,34 +2124,34 @@
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K7" s="2" t="s">
         <v>24</v>
@@ -2175,15 +2160,15 @@
         <v>25</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>15</v>
@@ -2195,22 +2180,22 @@
         <v>17</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K8" s="2" t="s">
         <v>24</v>
@@ -2219,7 +2204,7 @@
         <v>25</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -2227,51 +2212,51 @@
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M9" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N9" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>15</v>
@@ -2283,31 +2268,31 @@
         <v>17</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M10" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N10" s="2" t="s">
         <v>27</v>
@@ -2315,7 +2300,7 @@
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>15</v>
@@ -2327,34 +2312,34 @@
         <v>17</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M11" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
@@ -2371,7 +2356,7 @@
         <v>17</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>30</v>
@@ -2389,60 +2374,60 @@
         <v>32</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L12" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M12" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N12" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L13" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M13" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
@@ -2459,7 +2444,7 @@
         <v>17</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>30</v>
@@ -2477,21 +2462,21 @@
         <v>32</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>15</v>
@@ -2503,22 +2488,22 @@
         <v>17</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>24</v>
@@ -2530,12 +2515,12 @@
         <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>15</v>
@@ -2547,39 +2532,39 @@
         <v>17</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M16" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>15</v>
@@ -2588,25 +2573,25 @@
         <v>16</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>24</v>
+        <v>103</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>24</v>
+        <v>104</v>
       </c>
       <c r="K17" s="2" t="s">
         <v>24</v>
@@ -2615,59 +2600,59 @@
         <v>25</v>
       </c>
       <c r="M17" s="2" t="s">
-        <v>49</v>
+        <v>70</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>24</v>
+        <v>105</v>
       </c>
     </row>
     <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>101</v>
+        <v>106</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>103</v>
+        <v>108</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>104</v>
+        <v>109</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N18" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>15</v>
@@ -2679,31 +2664,31 @@
         <v>17</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>109</v>
+        <v>114</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>110</v>
+        <v>115</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J19" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>27</v>
@@ -2711,7 +2696,7 @@
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>112</v>
+        <v>117</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2723,22 +2708,22 @@
         <v>17</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>113</v>
+        <v>118</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>114</v>
+        <v>119</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>24</v>
@@ -2750,12 +2735,12 @@
         <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>116</v>
+        <v>121</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2767,22 +2752,22 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>117</v>
+        <v>122</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>118</v>
+        <v>123</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>119</v>
+        <v>124</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>24</v>
@@ -2791,15 +2776,15 @@
         <v>25</v>
       </c>
       <c r="M21" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>120</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2811,66 +2796,66 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M22" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K23" s="2" t="s">
         <v>24</v>
@@ -2879,59 +2864,59 @@
         <v>25</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N23" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M24" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2943,22 +2928,22 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J25" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K25" s="2" t="s">
         <v>24</v>
@@ -2987,7 +2972,7 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>30</v>
@@ -3005,21 +2990,21 @@
         <v>32</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L26" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -3028,42 +3013,42 @@
         <v>16</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>139</v>
+        <v>33</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -3075,31 +3060,31 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>27</v>
@@ -3107,7 +3092,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -3119,31 +3104,31 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>27</v>
@@ -3151,7 +3136,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -3163,22 +3148,22 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="K30" s="2" t="s">
         <v>24</v>
@@ -3190,12 +3175,12 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -3207,22 +3192,22 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K31" s="2" t="s">
         <v>24</v>
@@ -3231,7 +3216,7 @@
         <v>25</v>
       </c>
       <c r="M31" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N31" s="2" t="s">
         <v>27</v>
@@ -3239,51 +3224,51 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M32" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -3295,22 +3280,22 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K33" s="2" t="s">
         <v>24</v>
@@ -3327,51 +3312,51 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M34" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -3383,22 +3368,22 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>24</v>
@@ -3407,7 +3392,7 @@
         <v>25</v>
       </c>
       <c r="M35" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N35" s="2" t="s">
         <v>27</v>
@@ -3415,7 +3400,7 @@
     </row>
     <row r="36" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>15</v>
@@ -3424,42 +3409,42 @@
         <v>16</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G36" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H36" s="2" t="s">
-        <v>65</v>
+        <v>33</v>
       </c>
       <c r="I36" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J36" s="2" t="s">
-        <v>92</v>
+        <v>33</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M36" s="2" t="s">
-        <v>26</v>
+        <v>70</v>
       </c>
       <c r="N36" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="37" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>15</v>
@@ -3471,22 +3456,22 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K37" s="2" t="s">
         <v>24</v>
@@ -3495,7 +3480,7 @@
         <v>25</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -3524,7 +3509,7 @@
         <v>20</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>177</v>
+        <v>103</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>22</v>
@@ -3533,10 +3518,10 @@
         <v>181</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M38" s="2" t="s">
         <v>26</v>
@@ -3568,7 +3553,7 @@
         <v>20</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>22</v>
@@ -3618,7 +3603,7 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="K40" s="2" t="s">
         <v>24</v>
@@ -3656,7 +3641,7 @@
         <v>20</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>22</v>
@@ -3671,7 +3656,7 @@
         <v>25</v>
       </c>
       <c r="M41" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N41" s="2" t="s">
         <v>27</v>
@@ -3697,10 +3682,10 @@
         <v>195</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>22</v>
@@ -3715,7 +3700,7 @@
         <v>25</v>
       </c>
       <c r="M42" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N42" s="2" t="s">
         <v>27</v>
@@ -3759,7 +3744,7 @@
         <v>25</v>
       </c>
       <c r="M43" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N43" s="2" t="s">
         <v>27</v>
@@ -3767,16 +3752,16 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>202</v>
@@ -3788,39 +3773,39 @@
         <v>20</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M44" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N44" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>203</v>
@@ -3832,25 +3817,25 @@
         <v>20</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
@@ -3885,13 +3870,13 @@
         <v>201</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>27</v>
@@ -3926,7 +3911,7 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K47" s="2" t="s">
         <v>24</v>
@@ -3935,7 +3920,7 @@
         <v>25</v>
       </c>
       <c r="M47" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N47" s="2" t="s">
         <v>27</v>
@@ -3973,13 +3958,13 @@
         <v>192</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M48" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N48" s="2" t="s">
         <v>27</v>
@@ -4023,7 +4008,7 @@
         <v>25</v>
       </c>
       <c r="M49" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N49" s="2" t="s">
         <v>27</v>
@@ -4049,7 +4034,7 @@
         <v>223</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H50" s="2" t="s">
         <v>224</v>
@@ -4058,7 +4043,7 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="K50" s="2" t="s">
         <v>24</v>
@@ -4067,10 +4052,10 @@
         <v>25</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
@@ -4081,7 +4066,7 @@
         <v>15</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>17</v>
@@ -4105,16 +4090,16 @@
         <v>229</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M51" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
@@ -4155,7 +4140,7 @@
         <v>25</v>
       </c>
       <c r="M52" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N52" s="2" t="s">
         <v>27</v>
@@ -4184,13 +4169,13 @@
         <v>20</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J53" s="2" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="K53" s="2" t="s">
         <v>24</v>
@@ -4199,7 +4184,7 @@
         <v>25</v>
       </c>
       <c r="M53" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N53" s="2" t="s">
         <v>27</v>
@@ -4216,7 +4201,7 @@
         <v>16</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>239</v>
@@ -4228,25 +4213,25 @@
         <v>20</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L54" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
@@ -4260,7 +4245,7 @@
         <v>16</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>241</v>
@@ -4269,28 +4254,28 @@
         <v>241</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J55" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N55" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
@@ -4331,7 +4316,7 @@
         <v>25</v>
       </c>
       <c r="M56" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N56" s="2" t="s">
         <v>27</v>
@@ -4348,7 +4333,7 @@
         <v>248</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>249</v>
@@ -4357,28 +4342,28 @@
         <v>249</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M57" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
@@ -4404,7 +4389,7 @@
         <v>20</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>22</v>
@@ -4419,10 +4404,10 @@
         <v>25</v>
       </c>
       <c r="M58" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
@@ -4457,16 +4442,16 @@
         <v>258</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L59" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M59" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
@@ -4489,7 +4474,7 @@
         <v>261</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H60" s="2" t="s">
         <v>262</v>
@@ -4507,10 +4492,10 @@
         <v>25</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
@@ -4542,16 +4527,16 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>111</v>
+        <v>116</v>
       </c>
       <c r="K61" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L61" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M61" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N61" s="2" t="s">
         <v>27</v>
@@ -4577,7 +4562,7 @@
         <v>270</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H62" s="2" t="s">
         <v>271</v>
@@ -4592,13 +4577,13 @@
         <v>24</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
@@ -4630,7 +4615,7 @@
         <v>22</v>
       </c>
       <c r="J63" s="2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="K63" s="2" t="s">
         <v>277</v>
@@ -4639,7 +4624,7 @@
         <v>25</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>27</v>
@@ -4677,57 +4662,57 @@
         <v>282</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>283</v>
+        <v>146</v>
       </c>
       <c r="L64" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M64" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N64" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B65" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D65" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E65" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="B65" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C65" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="F65" s="2" t="s">
+      <c r="G65" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H65" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="I65" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J65" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="G65" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H65" s="2" t="s">
-        <v>177</v>
-      </c>
-      <c r="I65" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J65" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="K65" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L65" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M65" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N65" s="2" t="s">
         <v>27</v>
@@ -4735,28 +4720,28 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B66" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C66" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D66" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E66" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="B66" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C66" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E66" s="2" t="s">
+      <c r="F66" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="G66" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H66" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="G66" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H66" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="I66" s="2" t="s">
         <v>22</v>
@@ -4765,42 +4750,42 @@
         <v>253</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M66" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N66" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B67" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C67" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D67" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E67" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="B67" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C67" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E67" s="2" t="s">
+      <c r="F67" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="F67" s="2" t="s">
+      <c r="G67" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H67" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="G67" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H67" s="2" t="s">
-        <v>139</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>22</v>
@@ -4809,21 +4794,21 @@
         <v>295</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>296</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4835,22 +4820,22 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K68" s="2" t="s">
         <v>277</v>
@@ -4862,12 +4847,12 @@
         <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4879,39 +4864,39 @@
         <v>17</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L69" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M69" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4923,83 +4908,83 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F70" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="G70" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H70" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I70" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J70" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="F70" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="G70" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H70" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="I70" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J70" s="2" t="s">
-        <v>303</v>
-      </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N70" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I71" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="J71" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L71" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M71" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N71" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -5011,16 +4996,16 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>22</v>
@@ -5035,7 +5020,7 @@
         <v>25</v>
       </c>
       <c r="M72" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N72" s="2" t="s">
         <v>27</v>
@@ -5043,7 +5028,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -5055,39 +5040,39 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="G73" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H73" s="2" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="I73" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M73" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -5099,31 +5084,31 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L74" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M74" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N74" s="2" t="s">
         <v>27</v>
@@ -5131,7 +5116,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -5143,22 +5128,22 @@
         <v>17</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="K75" s="2" t="s">
         <v>24</v>
@@ -5170,12 +5155,12 @@
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -5187,16 +5172,16 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>22</v>
@@ -5211,15 +5196,15 @@
         <v>25</v>
       </c>
       <c r="M76" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -5231,10 +5216,10 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>20</v>
@@ -5252,7 +5237,7 @@
         <v>24</v>
       </c>
       <c r="L77" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M77" s="2" t="s">
         <v>26</v>
@@ -5263,7 +5248,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -5275,39 +5260,39 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L78" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M78" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N78" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -5316,10 +5301,10 @@
         <v>16</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F79" s="2" t="s">
         <v>330</v>
@@ -5328,89 +5313,89 @@
         <v>20</v>
       </c>
       <c r="H79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="I79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="J79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="K79" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="L79" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="I79" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J79" s="2" t="s">
-        <v>282</v>
-      </c>
-      <c r="K79" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L79" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="M79" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N79" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B80" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D80" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E80" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B80" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E80" s="2" t="s">
+      <c r="F80" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="F80" s="2" t="s">
+      <c r="G80" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H80" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="G80" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H80" s="2" t="s">
+      <c r="I80" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J80" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="I80" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J80" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="K80" s="2" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N80" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B81" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D81" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E81" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B81" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C81" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E81" s="2" t="s">
+      <c r="F81" s="2" t="s">
         <v>339</v>
-      </c>
-      <c r="F81" s="2" t="s">
-        <v>340</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
@@ -5428,10 +5413,10 @@
         <v>24</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N81" s="2" t="s">
         <v>27</v>
@@ -5439,28 +5424,28 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B82" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D82" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E82" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B82" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C82" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E82" s="2" t="s">
+      <c r="F82" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="F82" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>22</v>
@@ -5475,7 +5460,7 @@
         <v>25</v>
       </c>
       <c r="M82" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N82" s="2" t="s">
         <v>27</v>
@@ -5483,34 +5468,34 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B83" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D83" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E83" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B83" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C83" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E83" s="2" t="s">
+      <c r="F83" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="F83" s="2" t="s">
+      <c r="G83" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H83" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="G83" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H83" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="I83" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="K83" s="2" t="s">
         <v>24</v>
@@ -5519,7 +5504,7 @@
         <v>25</v>
       </c>
       <c r="M83" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N83" s="2" t="s">
         <v>27</v>
@@ -5527,34 +5512,34 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B84" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D84" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E84" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B84" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C84" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E84" s="2" t="s">
+      <c r="F84" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="F84" s="2" t="s">
+      <c r="G84" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H84" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I84" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J84" s="2" t="s">
         <v>350</v>
-      </c>
-      <c r="G84" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H84" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I84" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J84" s="2" t="s">
-        <v>351</v>
       </c>
       <c r="K84" s="2" t="s">
         <v>24</v>
@@ -5563,30 +5548,30 @@
         <v>25</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N84" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B85" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D85" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E85" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B85" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C85" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E85" s="2" t="s">
+      <c r="F85" s="2" t="s">
         <v>353</v>
-      </c>
-      <c r="F85" s="2" t="s">
-        <v>354</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5598,16 +5583,16 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
+        <v>354</v>
+      </c>
+      <c r="K85" s="2" t="s">
         <v>355</v>
-      </c>
-      <c r="K85" s="2" t="s">
-        <v>356</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>27</v>
@@ -5615,69 +5600,69 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B86" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D86" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E86" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B86" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C86" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E86" s="2" t="s">
+      <c r="F86" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="F86" s="2" t="s">
+      <c r="G86" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H86" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I86" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J86" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G86" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H86" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I86" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J86" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N86" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
+        <v>360</v>
+      </c>
+      <c r="B87" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D87" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E87" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="B87" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C87" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E87" s="2" t="s">
+      <c r="F87" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="F87" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="G87" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H87" s="2" t="s">
         <v>219</v>
@@ -5686,7 +5671,7 @@
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="K87" s="2" t="s">
         <v>24</v>
@@ -5698,12 +5683,12 @@
         <v>26</v>
       </c>
       <c r="N87" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5715,39 +5700,39 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F88" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G88" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H88" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I88" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J88" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G88" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H88" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I88" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J88" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N88" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5759,60 +5744,60 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F89" s="2" t="s">
+        <v>358</v>
+      </c>
+      <c r="G89" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H89" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="I89" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J89" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="G89" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H89" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I89" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J89" s="2" t="s">
-        <v>360</v>
-      </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N89" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
+        <v>366</v>
+      </c>
+      <c r="B90" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D90" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E90" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="B90" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C90" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E90" s="2" t="s">
+      <c r="F90" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="F90" s="2" t="s">
+      <c r="G90" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H90" s="2" t="s">
         <v>369</v>
-      </c>
-      <c r="G90" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H90" s="2" t="s">
-        <v>370</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>22</v>
@@ -5827,7 +5812,7 @@
         <v>25</v>
       </c>
       <c r="M90" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N90" s="2" t="s">
         <v>27</v>
@@ -5835,51 +5820,51 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
+        <v>370</v>
+      </c>
+      <c r="B91" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C91" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D91" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E91" s="2" t="s">
         <v>371</v>
       </c>
-      <c r="B91" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C91" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E91" s="2" t="s">
+      <c r="F91" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="F91" s="2" t="s">
+      <c r="G91" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H91" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="I91" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J91" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="G91" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H91" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="I91" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J91" s="2" t="s">
-        <v>374</v>
-      </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L91" s="2" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="M91" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5891,31 +5876,31 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M92" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N92" s="2" t="s">
         <v>27</v>
@@ -5923,34 +5908,34 @@
     </row>
     <row r="93" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B93" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C93" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D93" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E93" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B93" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C93" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E93" s="2" t="s">
+      <c r="F93" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="F93" s="2" t="s">
+      <c r="G93" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H93" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="G93" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H93" s="2" t="s">
-        <v>379</v>
-      </c>
       <c r="I93" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>24</v>
@@ -5959,7 +5944,7 @@
         <v>25</v>
       </c>
       <c r="M93" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N93" s="2" t="s">
         <v>27</v>
@@ -5967,72 +5952,72 @@
     </row>
     <row r="94" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B94" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D94" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="E94" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B94" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C94" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E94" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="F94" s="2" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J94" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K94" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L94" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M94" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N94" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="95" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B95" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D95" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E95" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B95" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C95" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E95" s="2" t="s">
+      <c r="F95" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="F95" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="G95" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>22</v>
@@ -6041,13 +6026,13 @@
         <v>201</v>
       </c>
       <c r="K95" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L95" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>27</v>
@@ -6055,22 +6040,22 @@
     </row>
     <row r="96" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B96" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D96" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E96" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B96" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C96" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E96" s="2" t="s">
+      <c r="F96" s="2" t="s">
         <v>386</v>
-      </c>
-      <c r="F96" s="2" t="s">
-        <v>387</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>20</v>
@@ -6082,60 +6067,60 @@
         <v>22</v>
       </c>
       <c r="J96" s="2" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="K96" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L96" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M96" s="2" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N96" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="97" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B97" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D97" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E97" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B97" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C97" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E97" s="2" t="s">
+      <c r="F97" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="F97" s="2" t="s">
+      <c r="G97" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H97" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="I97" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J97" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="G97" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H97" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="I97" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J97" s="2" t="s">
-        <v>392</v>
-      </c>
       <c r="K97" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L97" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M97" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N97" s="2" t="s">
         <v>27</v>
@@ -6143,34 +6128,34 @@
     </row>
     <row r="98" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B98" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C98" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D98" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B98" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C98" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E98" s="2" t="s">
+      <c r="F98" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="F98" s="2" t="s">
+      <c r="G98" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H98" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="I98" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="J98" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="G98" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H98" s="2" t="s">
-        <v>347</v>
-      </c>
-      <c r="I98" s="2" t="s">
-        <v>308</v>
-      </c>
-      <c r="J98" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="K98" s="2" t="s">
         <v>24</v>
@@ -6182,39 +6167,39 @@
         <v>26</v>
       </c>
       <c r="N98" s="2" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
     </row>
     <row r="99" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B99" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D99" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E99" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B99" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C99" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E99" s="2" t="s">
+      <c r="F99" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="F99" s="2" t="s">
+      <c r="G99" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H99" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="G99" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H99" s="2" t="s">
-        <v>400</v>
-      </c>
       <c r="I99" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J99" s="2" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="K99" s="2" t="s">
         <v>24</v>
@@ -6226,39 +6211,39 @@
         <v>26</v>
       </c>
       <c r="N99" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="100" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
+        <v>400</v>
+      </c>
+      <c r="B100" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C100" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D100" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E100" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="B100" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C100" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E100" s="2" t="s">
+      <c r="F100" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="F100" s="2" t="s">
+      <c r="G100" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H100" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="G100" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H100" s="2" t="s">
+      <c r="I100" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J100" s="2" t="s">
         <v>404</v>
-      </c>
-      <c r="I100" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J100" s="2" t="s">
-        <v>405</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>24</v>
@@ -6267,86 +6252,86 @@
         <v>25</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
     </row>
     <row r="101" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
+        <v>405</v>
+      </c>
+      <c r="B101" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C101" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D101" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E101" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B101" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C101" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E101" s="2" t="s">
+      <c r="F101" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="F101" s="2" t="s">
+      <c r="G101" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H101" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="G101" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H101" s="2" t="s">
+      <c r="I101" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J101" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="I101" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J101" s="2" t="s">
-        <v>410</v>
-      </c>
       <c r="K101" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>25</v>
       </c>
       <c r="M101" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="102" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B102" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C102" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D102" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B102" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C102" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D102" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E102" s="2" t="s">
+      <c r="F102" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="F102" s="2" t="s">
+      <c r="G102" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H102" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="I102" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J102" s="2" t="s">
         <v>413</v>
-      </c>
-      <c r="G102" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H102" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="I102" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J102" s="2" t="s">
-        <v>414</v>
       </c>
       <c r="K102" s="2" t="s">
         <v>24</v>
@@ -6358,39 +6343,39 @@
         <v>26</v>
       </c>
       <c r="N102" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="103" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B103" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C103" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D103" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E103" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B103" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C103" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D103" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E103" s="2" t="s">
+      <c r="F103" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="F103" s="2" t="s">
+      <c r="G103" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="H103" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="G103" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="H103" s="2" t="s">
+      <c r="I103" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J103" s="2" t="s">
         <v>418</v>
-      </c>
-      <c r="I103" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J103" s="2" t="s">
-        <v>145</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>24</v>
@@ -6399,7 +6384,7 @@
         <v>25</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N103" s="2" t="s">
         <v>419</v>
@@ -6419,7 +6404,7 @@
         <v>17</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>30</v>
@@ -6437,16 +6422,16 @@
         <v>32</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L104" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M104" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N104" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="105" spans="1:14" x14ac:dyDescent="0.25">
@@ -6457,7 +6442,7 @@
         <v>15</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D105" s="2" t="s">
         <v>17</v>
@@ -6469,10 +6454,10 @@
         <v>422</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I105" s="2" t="s">
         <v>22</v>
@@ -6481,16 +6466,16 @@
         <v>423</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L105" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M105" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N105" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
     <row r="106" spans="1:14" x14ac:dyDescent="0.25">
@@ -6501,10 +6486,10 @@
         <v>15</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E106" s="2" t="s">
         <v>425</v>
@@ -6516,25 +6501,25 @@
         <v>20</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L106" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="107" spans="1:14" x14ac:dyDescent="0.25">
@@ -6548,57 +6533,57 @@
         <v>16</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E107" s="2" t="s">
         <v>427</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>91</v>
+        <v>33</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J107" s="2" t="s">
-        <v>429</v>
+        <v>33</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L107" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M107" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N107" s="2" t="s">
-        <v>50</v>
+        <v>33</v>
       </c>
     </row>
     <row r="108" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B108" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D108" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E108" s="2" t="s">
+        <v>429</v>
+      </c>
+      <c r="F108" s="2" t="s">
         <v>430</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C108" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D108" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E108" s="2" t="s">
-        <v>431</v>
-      </c>
-      <c r="F108" s="2" t="s">
-        <v>432</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>20</v>
@@ -6610,24 +6595,24 @@
         <v>22</v>
       </c>
       <c r="J108" s="2" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L108" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M108" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N108" s="2" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="109" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>434</v>
+        <v>432</v>
       </c>
       <c r="B109" s="2" t="s">
         <v>15</v>
@@ -6636,42 +6621,42 @@
         <v>16</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>17</v>
+        <v>33</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>436</v>
+        <v>433</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>437</v>
+        <v>33</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>22</v>
+        <v>33</v>
       </c>
       <c r="J109" s="2" t="s">
-        <v>438</v>
+        <v>33</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L109" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M109" s="2" t="s">
-        <v>61</v>
+        <v>70</v>
       </c>
       <c r="N109" s="2" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
     </row>
     <row r="110" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B110" s="2" t="s">
         <v>15</v>
@@ -6683,39 +6668,39 @@
         <v>17</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J110" s="2" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="K110" s="2" t="s">
         <v>24</v>
       </c>
       <c r="L110" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M110" s="2" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N110" s="2" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="111" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
       <c r="B111" s="2" t="s">
         <v>15</v>
@@ -6724,81 +6709,81 @@
         <v>16</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="J111" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L111" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M111" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N111" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
     </row>
     <row r="112" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
       <c r="B112" s="2" t="s">
         <v>15</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="D112" s="2" t="s">
         <v>17</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
       <c r="I112" s="2" t="s">
         <v>22</v>
       </c>
       <c r="J112" s="2" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L112" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M112" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N112" s="2" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="113" spans="1:14" x14ac:dyDescent="0.25">
@@ -6815,16 +6800,16 @@
         <v>17</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>422</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="I113" s="2" t="s">
         <v>22</v>
@@ -6833,16 +6818,16 @@
         <v>423</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>24</v>
+        <v>33</v>
       </c>
       <c r="L113" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="M113" s="2" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N113" s="2" t="s">
-        <v>106</v>
+        <v>111</v>
       </c>
     </row>
   </sheetData>
@@ -6858,23 +6843,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
       <c r="B2" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
       <c r="D2" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
       <c r="E2" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -6882,16 +6867,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>455</v>
+        <v>450</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>456</v>
+        <v>451</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>457</v>
+        <v>452</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -6899,7 +6884,7 @@
         <v>112</v>
       </c>
       <c r="D5" s="5">
-        <v>0.017857142857142856</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="G5" s="4">
         <v>12.25</v>
@@ -6910,7 +6895,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>458</v>
+        <v>453</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -6923,7 +6908,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K23">
         <v>9</v>
@@ -6931,7 +6916,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>459</v>
+        <v>454</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -6962,12 +6947,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>460</v>
+        <v>455</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>454</v>
+        <v>449</v>
       </c>
       <c r="B2">
         <v>112</v>
@@ -6975,7 +6960,7 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.017857142857142856</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="B5" s="7"/>
     </row>
@@ -6991,25 +6976,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>461</v>
+        <v>456</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>462</v>
+        <v>457</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>463</v>
+        <v>458</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>464</v>
+        <v>459</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>465</v>
+        <v>460</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>466</v>
+        <v>461</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -7026,16 +7011,16 @@
         <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>467</v>
+        <v>462</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>468</v>
+        <v>463</v>
       </c>
       <c r="K10">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M10" t="s">
         <v>25</v>
@@ -7044,47 +7029,47 @@
         <v>67</v>
       </c>
       <c r="P10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="Q10">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="E11">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="H11">
         <v>29</v>
       </c>
       <c r="J11" t="s">
-        <v>469</v>
+        <v>464</v>
       </c>
       <c r="K11">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="M11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="N11">
         <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="Q11">
-        <v>18</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
       <c r="D12" t="s">
-        <v>102</v>
+        <v>107</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -7096,7 +7081,7 @@
         <v>83</v>
       </c>
       <c r="M12" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -7105,7 +7090,7 @@
         <v>26</v>
       </c>
       <c r="Q12">
-        <v>16</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -7116,22 +7101,22 @@
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>470</v>
+        <v>465</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
       <c r="P13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="Q13">
-        <v>19</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="4:17" x14ac:dyDescent="0.25">
@@ -7142,27 +7127,27 @@
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>471</v>
+        <v>466</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="N14">
         <v>9</v>
       </c>
       <c r="P14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="Q14">
-        <v>8</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -7170,7 +7155,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -7178,7 +7163,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>473</v>
+        <v>468</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -7186,7 +7171,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>474</v>
+        <v>469</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -7197,7 +7182,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>475</v>
+        <v>470</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -7205,128 +7190,128 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>333</v>
+        <v>100</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>452</v>
+        <v>574</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>334</v>
+        <v>101</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>57</v>
+        <v>434</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>127</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>439</v>
+        <v>131</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>318</v>
+        <v>332</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>409</v>
+        <v>446</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>319</v>
+        <v>333</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>296</v>
+        <v>319</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>402</v>
+        <v>410</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>297</v>
+        <v>320</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>284</v>
+        <v>297</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>385</v>
+        <v>397</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>285</v>
+        <v>298</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>242</v>
+        <v>283</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>243</v>
+        <v>284</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>420</v>
+        <v>242</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F29" s="2">
-        <v>334</v>
+        <v>375</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>421</v>
+        <v>243</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -7337,10 +7322,10 @@
         <v>15</v>
       </c>
       <c r="F30" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>448</v>
+        <v>421</v>
       </c>
     </row>
   </sheetData>

--- a/utils/monday_sprint_sprint_2026-13.xlsx
+++ b/utils/monday_sprint_sprint_2026-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1791" uniqueCount="443">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1795" uniqueCount="458">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -108,1219 +108,1264 @@
     <t>37473</t>
   </si>
   <si>
+    <t>Fundição</t>
+  </si>
+  <si>
+    <t>Bloqueio de apontamento eletrônico - Painel de consulta</t>
+  </si>
+  <si>
+    <t>Boa tarde senhores. Conforme discutido em reunião, abro este chamado para duas situações; 1. Setores a serem liberados a abrir apontamento eletrônico produtivo de sequencias que não tiveram a movimentação da fusão ou setores anteriores a fusão realizada. Corte: 1408/1411/1412/1413/1414/1415/1416/141</t>
+  </si>
+  <si>
+    <t>Bruno da Silva</t>
+  </si>
+  <si>
+    <t>05/05/2026</t>
+  </si>
+  <si>
+    <t>04/05/2026</t>
+  </si>
+  <si>
+    <t>A fazer</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>36893</t>
+  </si>
+  <si>
+    <t>UPR</t>
+  </si>
+  <si>
+    <t>Redução tamanho de lotes de moldagem</t>
+  </si>
+  <si>
+    <t>Bom dia! Favor reduzir os lotes de moldagem, no APS, conforme tabela abaixo: MODELO QTD ORIGINAL QTD AJUSTADA 000120002 50 10 000220002 50 10 000220002 28 10 000410001 50 10 000910002 50 10 002110001 50 10 008320002 50 10 042200861 160 40 042200874 80 20 042202092 60 20 301849699 26 10 84D721189P2 6</t>
+  </si>
+  <si>
+    <t>Cristiano Nazário</t>
+  </si>
+  <si>
+    <t>20/03/2026</t>
+  </si>
+  <si>
+    <t>Semana 3</t>
+  </si>
+  <si>
+    <t>Março</t>
+  </si>
+  <si>
+    <t>36335</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I - Alteração Dashboard</t>
+  </si>
+  <si>
+    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Matheus Rodrigues de Almeida</t>
+  </si>
+  <si>
+    <t>14/05/2026</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>38018</t>
+  </si>
+  <si>
+    <t>Envio de avaliação - Reunião</t>
+  </si>
+  <si>
+    <t>Boa tarde, No sistema de avaliação de serviço/ Material Precisamos de uma integração entre o relatório de avaliação de desempenho e o geral para enviar as avaliações de modo automático para os fornecedores selecionados. @Sandro para duvidas podemos marcar uma reunião via Teams, item pontuado em audi</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>12/06/2026</t>
+  </si>
+  <si>
+    <t>30012</t>
+  </si>
+  <si>
+    <t>PCP</t>
+  </si>
+  <si>
+    <t>Projeto</t>
+  </si>
+  <si>
+    <t>Obter dados itens comerciais, macharia, embalagem</t>
+  </si>
+  <si>
+    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
+  </si>
+  <si>
+    <t>João Pedro Beccon</t>
+  </si>
+  <si>
+    <t>37774</t>
+  </si>
+  <si>
+    <t>TI</t>
+  </si>
+  <si>
+    <t>Oferta/oportunidade - identificação analista de vendas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prezado, bom dia. O processo que migra as ofertas/oportunidades para o CRM está definindo o ADMINISTRADOR como responsável por todas elas. Isso gera um problema quando o usuário tenta localizar suas próprias ofertas/oportunidades no CRM. A Senior analisou a situação e sugeriu uma forma de contornar </t>
+  </si>
+  <si>
+    <t>Alexandre Longo</t>
+  </si>
+  <si>
+    <t>11925887059</t>
+  </si>
+  <si>
     <t>Setor não informado</t>
   </si>
   <si>
-    <t>Bloqueio de apontamento eletrônico - Painel de consulta</t>
-  </si>
-  <si>
-    <t>Boa tarde senhores. Conforme discutido em reunião, abro este chamado para duas situações; 1. Setores a serem liberados a abrir apontamento eletrônico produtivo de sequencias que não tiveram a movimentação da fusão ou setores anteriores a fusão realizada. Corte: 1408/1411/1412/1413/1414/1415/1416/141</t>
-  </si>
-  <si>
-    <t>Bruno da Silva</t>
-  </si>
-  <si>
-    <t>05/05/2026</t>
+    <t>Categoria não informada</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Frontend</t>
+  </si>
+  <si>
+    <t>Solicitante não informado</t>
+  </si>
+  <si>
+    <t>Equipe não informada</t>
+  </si>
+  <si>
+    <t>10/05/2026</t>
+  </si>
+  <si>
+    <t>37826</t>
+  </si>
+  <si>
+    <t>IROG Corte pó de ferro no BI</t>
+  </si>
+  <si>
+    <t>Boa tarde, Esteva verificando que alguns modelos não puxaram o tempo padrão de corte para o BI. Esse e apenas alguns desse modelo. Acho que o motivo de não estar buscando e que o setor de corte dessa peça não e o 1415 "Corte pó de ferro" e sim o 1414 "Corte de Canal com Maçarico" se realmente esse f</t>
+  </si>
+  <si>
+    <t>Eduardo Basso Pinto</t>
+  </si>
+  <si>
+    <t>37361</t>
+  </si>
+  <si>
+    <t>Logística</t>
+  </si>
+  <si>
+    <t>Base Histórica da Data de Reconhecimento  de Receita (copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>06/05/2026</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>Bloqueio de apontamento eletrônico</t>
+  </si>
+  <si>
+    <t>17/04/2026</t>
+  </si>
+  <si>
+    <t>11/05/2026</t>
+  </si>
+  <si>
+    <t>33130</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Consulta Cadastro de LEADs</t>
   </si>
   <si>
     <t>N/A</t>
   </si>
   <si>
-    <t>A fazer</t>
-  </si>
-  <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>36893</t>
-  </si>
-  <si>
-    <t>Redução tamanho de lotes de moldagem</t>
-  </si>
-  <si>
-    <t>Bom dia! Favor reduzir os lotes de moldagem, no APS, conforme tabela abaixo: MODELO QTD ORIGINAL QTD AJUSTADA 000120002 50 10 000220002 50 10 000220002 28 10 000410001 50 10 000910002 50 10 002110001 50 10 008320002 50 10 042200861 160 40 042200874 80 20 042202092 60 20 301849699 26 10 84D721189P2 6</t>
-  </si>
-  <si>
-    <t>Cristiano Nazário</t>
-  </si>
-  <si>
-    <t>20/03/2026</t>
-  </si>
-  <si>
-    <t>Semana 3</t>
-  </si>
-  <si>
-    <t>Março</t>
-  </si>
-  <si>
-    <t>36335</t>
-  </si>
-  <si>
-    <t>Fundição</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I - Alteração Dashboard</t>
-  </si>
-  <si>
-    <t>Boa tarde, Preciso de uns ajustes no Qlik Sense, existe um gráfico que fala sobre a movimentação da moldagem USE (Segue imagem do local): Essa é Tela inicial: 1 - Olhando para a questão dos filtros, preciso de uma filtro para semana, exemplo semana 2 (04/01 até 10/01), assim consigo visualizar melho</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>38018</t>
-  </si>
-  <si>
-    <t>Envio de avaliação - Reunião</t>
-  </si>
-  <si>
-    <t>Boa tarde, No sistema de avaliação de serviço/ Material Precisamos de uma integração entre o relatório de avaliação de desempenho e o geral para enviar as avaliações de modo automático para os fornecedores selecionados. @Sandro para duvidas podemos marcar uma reunião via Teams, item pontuado em audi</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>30012</t>
-  </si>
-  <si>
-    <t>Projeto</t>
-  </si>
-  <si>
-    <t>Obter dados itens comerciais, macharia, embalagem</t>
-  </si>
-  <si>
-    <t>Objetivo: alimentar dados mestres nas tabelas do APS 8-9. Levantamento de informações para a especificação funcional do projeto. ( TI especificação de interface inicial) REALIZADO @Edson João Hammermeister por favor indicar tempo para essa atividade. Atenciosamente, De: João Pedro Beccon Enviada em:</t>
-  </si>
-  <si>
-    <t>João Pedro Beccon</t>
+    <t>Laura Herrmann Schmickler</t>
+  </si>
+  <si>
+    <t>Bloqueio de apontamento eletrônico - Envio de e-mail</t>
+  </si>
+  <si>
+    <t>36741</t>
+  </si>
+  <si>
+    <t>Engenharia</t>
+  </si>
+  <si>
+    <t>ACERTO DE NÚMERO DE LINHAS EM MOVIMENTAÇÃO SETORIAL</t>
+  </si>
+  <si>
+    <t>Boa tarde, Permitir que o sistema de movimentação setorial [WCPP22AI] faça acerto do número de linhas nas sequências selecionadas conforme permitido na sistemática da tela WCPP2202. At.te</t>
+  </si>
+  <si>
+    <t>Willian Gabriel Paixão dos Santos</t>
+  </si>
+  <si>
+    <t>20/02/2026</t>
+  </si>
+  <si>
+    <t>Fevereiro</t>
+  </si>
+  <si>
+    <t>35453</t>
+  </si>
+  <si>
+    <t>Qualidade</t>
+  </si>
+  <si>
+    <t>Inclusão de informação CPP</t>
+  </si>
+  <si>
+    <t>Boa tarde, Conforme conversa, por gentileza incluir campo para preencher o "Tempo de Enchimento Projetado" no Formulário de Projeto no CPP: E, além disso, esse novo dado deve aparecer no sistema de corridas, na tela abaixo (ao lado dessa informação deve aparecer a tolerância de +-15%): At.te,</t>
+  </si>
+  <si>
+    <t>Helena Mariana Segalla</t>
+  </si>
+  <si>
+    <t>27/04/2026</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
+  </si>
+  <si>
+    <t>28277</t>
+  </si>
+  <si>
+    <t>Incluir OTF Romaneio</t>
+  </si>
+  <si>
+    <t>Boa tarde Gentileza incluir OTF no romaneio. Dúvidas, estou a disposição.</t>
+  </si>
+  <si>
+    <t>Rafael De Souza</t>
+  </si>
+  <si>
+    <t>32141</t>
+  </si>
+  <si>
+    <t>Correção</t>
+  </si>
+  <si>
+    <t>Cadastro de Embalagem no CPP (APS)</t>
+  </si>
+  <si>
+    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
+  </si>
+  <si>
+    <t>02/06/2026</t>
+  </si>
+  <si>
+    <t>37677</t>
+  </si>
+  <si>
+    <t>melhoria no cadastro e relatório do MRP - Reunião</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Criar relatório para gerar o mrp por itens lançados, estes itens o usuário vai alimentar em um campo, exemplo: tenho a programação da moldagem da semana 15 onde serão feitos um total 20 modelos aleatórios , vou alimentar o sistema como os 20 modelos e quantidades de peças a serem produzidas de cada </t>
+  </si>
+  <si>
+    <t>Fernando Beltrame</t>
+  </si>
+  <si>
+    <t>11/06/2026</t>
+  </si>
+  <si>
+    <t>37367</t>
+  </si>
+  <si>
+    <t>Download automático de arquivos excel.</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos que seja feita uma atualização no sistema Gestão de Ações. Quando colocamos uma anexo do tipo excel nas evidências, o sistema fica fazendo um download do arquivo sempre que a página é atualizada. Precisamos corrigir para o download ser por um botão. "Fazer download do arquivo?"</t>
+  </si>
+  <si>
+    <t>Matheus Gonçalves</t>
+  </si>
+  <si>
+    <t>34919</t>
+  </si>
+  <si>
+    <t>Solicitação de BI QlikSense – Indicadores de Ofertas</t>
+  </si>
+  <si>
+    <t>Bom dia, Gostaria de desenvolver um BI que apresente dois indicadores relacionados ao envio de ofertas: 1. % de ofertas enviadas dentro do prazo definido no momento da abertura do PO. Este será o indicador principal. 1. Prazo médio de envio das ofertas (em dias) Apenas para acompanhamento; não haver</t>
+  </si>
+  <si>
+    <t>10/02/2026</t>
+  </si>
+  <si>
+    <t>Semana 2</t>
+  </si>
+  <si>
+    <t>33549</t>
+  </si>
+  <si>
+    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
+  </si>
+  <si>
+    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
+  </si>
+  <si>
+    <t>Rosivaldo Silva</t>
+  </si>
+  <si>
+    <t>20/04/2026</t>
+  </si>
+  <si>
+    <t>Parte visual e filtros</t>
+  </si>
+  <si>
+    <t>11925887640</t>
+  </si>
+  <si>
+    <t>ALTC  - Acompanhamento</t>
+  </si>
+  <si>
+    <t>12/05/2026</t>
+  </si>
+  <si>
+    <t>Fazendo</t>
+  </si>
+  <si>
+    <t>37949</t>
+  </si>
+  <si>
+    <t>Almoxarifado</t>
+  </si>
+  <si>
+    <t>Trava na requisição em caso de inventário em aberto</t>
+  </si>
+  <si>
+    <t>Boa tarde! Estamos enfrentando uma situação que tem gerado saldo negativo no sistema quando há um inventário em andamento e, simultaneamente, ocorre a requisição de materiais. Para evitar esse problema, solicitamos a implementação de uma trava no sistema de requisição, de modo que, enquanto o invent</t>
+  </si>
+  <si>
+    <t>Alex Julio Estacio</t>
+  </si>
+  <si>
+    <t>11925827134</t>
+  </si>
+  <si>
+    <t>Alteração de registro de pintura</t>
+  </si>
+  <si>
+    <t>38154</t>
+  </si>
+  <si>
+    <t>Contabilidade</t>
+  </si>
+  <si>
+    <t>Altona | CC 40104 Bloqueado</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Sandro Favor criar uma regra na pré-lista ou requisição para que ao digitar o CC 40104 - 1.5.02.002 - Depósito e Despacho (Embalagem) O SNB veja se a conta contábil utilizada é 26851 - 5.1.2.01.120 - EMBALAGEM. Se a conta contábil for 26851, o SNB deve manter o CC 40104. Se não for a conta </t>
+  </si>
+  <si>
+    <t>Edson Vitor Scharf Filho</t>
+  </si>
+  <si>
+    <t>07/05/2026</t>
+  </si>
+  <si>
+    <t>37659</t>
+  </si>
+  <si>
+    <t>Altona || Estoque de Consignados - Contabilização da Devolução</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Preciso alterar a contabilização de requisição de devolução do consignado: Atualmente está assim: D - 32187 C - Estoque Consignado -------------------------------- Mas o correto é: D - Resultado Custo Se for inserto, por exemplo, a conta será 5.1.2.01.115 Centro de Custo - 60600 - 1</t>
+  </si>
+  <si>
+    <t>34223</t>
+  </si>
+  <si>
+    <t>Usinagem</t>
+  </si>
+  <si>
+    <t>Alterar gráfico IROG - Usinagem</t>
+  </si>
+  <si>
+    <t>Boa tarde Favor realizar alteração no gráfico de cluster, podendo ser utilizado um gráfico de barras na horizontal. Segue abaixo um exemplo de como pode ser o gráfico (no eixo onde está as operações, mostrar os modelos) Att,</t>
+  </si>
+  <si>
+    <t>Caio Henrique Vicente Bento</t>
+  </si>
+  <si>
+    <t>38108</t>
+  </si>
+  <si>
+    <t>Lentidão no apontamento eletrônico – Mesa Redonda -  Analise</t>
+  </si>
+  <si>
+    <t>Boa tarde, O operador que está em fase de testes com o apontamento eletrônico na mesa redonda relatou que o sistema está apresentando lentidão excessiva, com travamentos frequentes. Solicitamos, por gentileza, a reavaliação do assunto já tratado no chamado nº 36298. Temos um vídeo demonstrativo no q</t>
+  </si>
+  <si>
+    <t>Douglas Garcia</t>
+  </si>
+  <si>
+    <t>Envio de ofertar trocar o usuário responsável</t>
+  </si>
+  <si>
+    <t>37929</t>
+  </si>
+  <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
+    <t>Indicador de ACR</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos agora iniciar a implementação dos indicadores para as ACRs e temos alguns pontos a ajustar. 1. Precisamos ter a informação de que tipo de gatilho foi nessa coluna 1. Precisamos ter uma coluna que identifique se já temos anexo (1 - sim / 0 - não) 1. A ideia é termos um um resumo q</t>
+  </si>
+  <si>
+    <t>Enzo Luiz Okabe Auad</t>
+  </si>
+  <si>
+    <t>Atualizar campos: data, hora e prazo da proposta</t>
+  </si>
+  <si>
+    <t>37857</t>
+  </si>
+  <si>
+    <t>INLCUIR ALTERAÇÃO ( ESTAGIO DE FRABRICAÇÃO ) AONDE ALTERA DADOS E APONTAMENTOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Necessitamos da opção para alterar o estado de fabricação da peça ( bruto ) ou ( usinado, Colaboradores que apontam incorretamente esse estágio prejudica diretamente o Irog, conseguimos incluir esta opção? At.te.,</t>
+  </si>
+  <si>
+    <t>Otavio Zimmermann Neto</t>
+  </si>
+  <si>
+    <t>36722</t>
+  </si>
+  <si>
+    <t>Bloco K - Integração dados Altona / Benner.</t>
+  </si>
+  <si>
+    <t>Prezado, bom dia. Situação: Atualmente a integração dos dados Altona / Benner, para integrar o bloco K, precisa da intervenção de uma pessoa para disparar a rotina. Necessidade: Automatizar este processo. Ação: 1. Implementar status indicando que o dado está pronto para ser enviado para Benner. 2. A</t>
+  </si>
+  <si>
+    <t>38159</t>
+  </si>
+  <si>
+    <t>Cadastrar Rota Cinza</t>
+  </si>
+  <si>
+    <t>Bom dia O cadastro da rota Cinza não esta entrando para os operadores.</t>
+  </si>
+  <si>
+    <t>37963</t>
+  </si>
+  <si>
+    <t>Chamado Caminhão Munck - WMS</t>
+  </si>
+  <si>
+    <t>Bom dia Segue chamado para implementar o sistema do WMS no caminhão Munck.</t>
+  </si>
+  <si>
+    <t>37974</t>
+  </si>
+  <si>
+    <t>Problemas na baixa de ordens que estão sendo programadas</t>
+  </si>
+  <si>
+    <t>Boa tarde, Estou abrindo esse chamado referente a uns problemas que estamos tendo quanto as ordens que estamos cadastrando com método e base tempo que agora estão passando pela programação com a caixa "Gerar SS Planejamento" selecionada Ex: OS 327892 é uma preventiva mensal para a ponte rolante 14 c</t>
+  </si>
+  <si>
+    <t>37947</t>
+  </si>
+  <si>
+    <t>Sistema de apontamento - Tablets pó de ferro</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia é necessário a melhoria de algumas funções no sistema de apontamento pó de ferro. 1. As sequencias de peças cortadas no dia estão aparecendo para todos os cortadores, precisamos que apenas apareça a sequência cortada para edição e verificação do cortador que cortou a peça. 2. As observações </t>
+  </si>
+  <si>
+    <t>Amanda Vitoria Aroeira Marinho</t>
+  </si>
+  <si>
+    <t>37714</t>
+  </si>
+  <si>
+    <t>Solicitação de inclusão de tela no WMS – Inclusão de saldo no endereço de recebimento</t>
+  </si>
+  <si>
+    <t>Boa tarde! Solicitamos a inclusão de uma tela no WMS do Almoxarifado para inclusão de saldo virtual no endereço de recebimento. Essa funcionalidade se faz necessária pelas seguintes situações operacionais: Quando um material é movimentado para estoque de terceiros, o saldo virtual no WMS acaba sendo</t>
+  </si>
+  <si>
+    <t>38203</t>
+  </si>
+  <si>
+    <t>Melhorias no apontamento eletrônico – Corte Escarfa</t>
+  </si>
+  <si>
+    <t>Boa tarde, Retorno sobre o desenvolvimento do sistema de apontamento eletrônico – corte escarfa: * É necessário que, assim como nos demais sistemas, sejam exibidos modelo e croqui. * Para melhorar a confiabilidade do apontamento, devemos incluir perguntas de confirmação, por exemplo: “Deseja finaliz</t>
+  </si>
+  <si>
+    <t>38053</t>
+  </si>
+  <si>
+    <t>Orçamento</t>
+  </si>
+  <si>
+    <t>FW: Alteração Liga Stara- EA4257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia, Solicito uma solução para um problema rotineiro que o setor de orçamento vem enfrentando, caso exista a necessidade de gerar uma simulação, de uma liga nova para itens que já fornecemos. O sistema foi bloqueado no ano passado para alteração de itens que já fornecemos, o que não é errado no </t>
+  </si>
+  <si>
+    <t>Pierro Conrrad da Silva</t>
+  </si>
+  <si>
+    <t>11925903796</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Preparar Ambiente</t>
+  </si>
+  <si>
+    <t>11925903757</t>
+  </si>
+  <si>
+    <t>Aprimoramento Ailton - Backend</t>
+  </si>
+  <si>
+    <t>38052</t>
+  </si>
+  <si>
+    <t>pdi eletronico</t>
+  </si>
+  <si>
+    <t>Preciso que seja ajustado o campo de observação do PDI para o inspetor, pois hoje com o limite de caracteres que tem o inspetor não consegue passar a informação completa para o Analista. att</t>
+  </si>
+  <si>
+    <t>Gerson Mendonça</t>
+  </si>
+  <si>
+    <t>38166</t>
+  </si>
+  <si>
+    <t>ENC: Condição de pagamento  para Consórcio.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Richard/Sandro, Por solicitação do financeiro precisamos cadastrar uma nova condição de pagamento: Consorcio que no momento quando criamos aparece como antecipado. Aproveito a oportunidade para gerar um prazo de 15/30/45. @Larissa Gabriely Gaia Alves assim que for gerado os prazos por favor </t>
+  </si>
+  <si>
+    <t>Luciana Bello</t>
+  </si>
+  <si>
+    <t>37692</t>
+  </si>
+  <si>
+    <t>[COMPRAS] Cancelamento de saldo por item</t>
+  </si>
+  <si>
+    <t>Bom dia, Na tela de pedidos temos a opção de cancelar saldo do pedido. Gostaríamos que fosse criada a opção de cancelar o saldo em aberto somente de um material dentro do pedido. Como mostra a imagem, somente um dos itens teve entrada, mas ainda consta como aberto. Gostaríamos de cancelar esse saldo</t>
+  </si>
+  <si>
+    <t>Larissa Gabriely Gaia Alves</t>
+  </si>
+  <si>
+    <t>37690</t>
+  </si>
+  <si>
+    <t>Mecânica</t>
+  </si>
+  <si>
+    <t>Melhoria chamado 36233 incluir horário ponto como referência</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito uma melhoria no chamado 36233 (automatizar apontamento) para que ele tenha como base o horário ponto, ou seja, puxe desde que ele chegue na empresa até sua saída.</t>
+  </si>
+  <si>
+    <t>Glória Danielly Lima Rodrigues</t>
+  </si>
+  <si>
+    <t>32133</t>
+  </si>
+  <si>
+    <t>Novo Recurso</t>
+  </si>
+  <si>
+    <t>Automatização planilha comercial - PARTE 2/2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
+  </si>
+  <si>
+    <t>Jacson Schneider Movidesk</t>
+  </si>
+  <si>
+    <t>36206</t>
+  </si>
+  <si>
+    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
+  </si>
+  <si>
+    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
+  </si>
+  <si>
+    <t>Adnan Pires</t>
+  </si>
+  <si>
+    <t>37783</t>
+  </si>
+  <si>
+    <t>Inclusão coluna no Planilhão</t>
+  </si>
+  <si>
+    <t>Bom dia Flávio, Favor incluir no Planilhão da Carteira UPR uma coluna com a informação se o modelo (ferramental) está bloqueado para produção. Essa informação geramos relatório em: Modelos &gt; Consulta &gt; Cadastrado de Modelos &gt; Por modelo &gt; Conserto de Modelos &gt; Imprimir &gt; Somente em aberto Data inici</t>
+  </si>
+  <si>
+    <t>Caroline Schmitt</t>
+  </si>
+  <si>
+    <t>38156</t>
+  </si>
+  <si>
+    <t>Cadastro de Linhas no Apontamento Eletrônico</t>
+  </si>
+  <si>
+    <t>Bom dia, Solicito, por gentileza, o cadastro das linhas Volvo e Alstom no sistema de apontamento eletrônico, conforme abaixo: * Alstom: utilizar o mesmo modelo aplicado à mesa redonda; * Volvo: utilizar o mesmo modelo da fase 4. Fico à disposição para quaisquer dúvidas. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>11925903298</t>
+  </si>
+  <si>
+    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
+  </si>
+  <si>
+    <t>11925904760</t>
+  </si>
+  <si>
+    <t>Criar API para receber informações do MES para a abertura da SS</t>
+  </si>
+  <si>
+    <t>31319</t>
+  </si>
+  <si>
+    <t>Ajuste na inclusão de sequência manual no coletor do WMS</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de solicitar um ajuste no sistema do coletor WMS para que, ao incluir uma sequência manual, o sistema aceite a entrada independentemente da utilização de letras maiúsculas ou minúsculas. Essa melhoria contribuirá para a padronização do processo e reduzirá possíveis erros operacio</t>
+  </si>
+  <si>
+    <t>Johnny José Rocha</t>
+  </si>
+  <si>
+    <t>11925904921</t>
+  </si>
+  <si>
+    <t>Novo Sistema</t>
+  </si>
+  <si>
+    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
+  </si>
+  <si>
+    <t>36809</t>
+  </si>
+  <si>
+    <t>FINALIZAR 501</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor finalizar todos os formulários do setor 501 que estão em aberto antes da conclusão do ticket 28147. At.te</t>
+  </si>
+  <si>
+    <t>06/03/2026</t>
+  </si>
+  <si>
+    <t>37190</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
+  </si>
+  <si>
+    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
+  </si>
+  <si>
+    <t>Guilherme Ferreira</t>
+  </si>
+  <si>
+    <t>37095</t>
+  </si>
+  <si>
+    <t>Logistica</t>
+  </si>
+  <si>
+    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
+  </si>
+  <si>
+    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
+  </si>
+  <si>
+    <t>Rodrigo Santos Rocha</t>
+  </si>
+  <si>
+    <t>37672</t>
+  </si>
+  <si>
+    <t>RES: Certificados de Qualidade</t>
+  </si>
+  <si>
+    <t>Bom dia Senhores, Temos algum retorno sobre a demanda abaixo? Atenciosamente, De: Andre Traleski Enviada em: terça-feira, 28 de outubro de 2025 10:26 Para: sistemas@ti-altona.movidesk.com Cc: Maciel Nolli Assunto: ENC: Certificados de Qualidade Bom dia, Favor abrir chamado para verificação das diver</t>
+  </si>
+  <si>
+    <t>Andre Traleski</t>
+  </si>
+  <si>
+    <t>36972</t>
+  </si>
+  <si>
+    <t>Inserir CPC e Ordem de compra automaticamente no GED</t>
+  </si>
+  <si>
+    <t>Boa tarde, Precisamos implementar uma melhoria no sistema de emissão de CPC para que, no momento da criação, a CPC seja automaticamente integrada ao GED. Além disso, é necessário avaliar a possibilidade de incluir a opção de anexar a Ordem de Compra à CPC, garantindo que esse documento também seja e</t>
+  </si>
+  <si>
+    <t>Jaqueline Cogorni Mendes</t>
+  </si>
+  <si>
+    <t>23/03/2026</t>
+  </si>
+  <si>
+    <t>38021</t>
+  </si>
+  <si>
+    <t>RES: Sucata Retorno Mar2026</t>
+  </si>
+  <si>
+    <t>Boa tarde Sandro, Favor incluir o Saldos abaixo em 31/03/2026 no sistemas de requisição, mantendo o mesmo custo médio (Isto é referente aquele problema de não contabilização do refugo nas entradas de sucata retorno em março). Conta Descrição da Conta Código Descrição do Material UN Incluir ou Retira</t>
+  </si>
+  <si>
+    <t>Rafael Pereira</t>
+  </si>
+  <si>
+    <t>36544</t>
+  </si>
+  <si>
+    <t>Excelência Operacional</t>
+  </si>
+  <si>
+    <t>Sistema de Metas</t>
+  </si>
+  <si>
+    <t>Bom dia Srs., O sistema de cadastro de Metas n?o est? funcionando, visto que fiz o cadastro para os setores de Inspe??o conforme abaixo: O B.I. est? trazendo a informa??o, conforme abaixo: Solicitei ao Felipe que desse uma carga de dados para avaliar, o mesmo fez e o B.I. n?o trouxe as informa??es c</t>
+  </si>
+  <si>
+    <t>Gabriel Lucas Kertichka</t>
+  </si>
+  <si>
+    <t>29/04/2026</t>
+  </si>
+  <si>
+    <t>31158</t>
+  </si>
+  <si>
+    <t>Status movimentação OM -WMS</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme verificado em Consulta O.M., se eu coloco o status de "AGUARDANDO" ele está puxando as OM entregue, ou seja, não está puxando corretamente.</t>
+  </si>
+  <si>
+    <t>11925856386</t>
+  </si>
+  <si>
+    <t>Gráfico de barras empilhadas “Retrabalhos para aprovação”</t>
+  </si>
+  <si>
+    <t>37412</t>
+  </si>
+  <si>
+    <t>Registro de Preset - Reunião</t>
+  </si>
+  <si>
+    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
+  </si>
+  <si>
+    <t>Lucas Sebold Movidesk</t>
+  </si>
+  <si>
+    <t>18/05/2026</t>
+  </si>
+  <si>
+    <t>30722</t>
+  </si>
+  <si>
+    <t>NOVO ESTADO DE FORNECIMENTO</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar um novo estado de fornecimento no CPP tela WWCPP221 chamado "I.C sem fundido": Esta opção com liga 0 deve permitir a montagem de conjuntos para serem faturados no depósito sem a necessidade de um item fundido no conjunto. At.te</t>
+  </si>
+  <si>
+    <t>35503</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Usinagem - subáreas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Na reunião realizada em 02/10/2025, foi discutido o tema apropriação do custeio. Estiveram presentes: Rafael Pereira, Paulo Cruz e Alexandre Longo. Como já existiam dois chamados1 abertos, as tarefas foram inicialmente vinculadas a eles. Porém, com a evolução das demandas, ficou acordada a abertura </t>
+  </si>
+  <si>
+    <t>06/10/2025</t>
+  </si>
+  <si>
+    <t>Outubro</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Inspeção - subáreas</t>
+  </si>
+  <si>
+    <t>34336</t>
+  </si>
+  <si>
+    <t>DIÁRIO DE BORDO - Acompanhamento</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
+  </si>
+  <si>
+    <t>38074</t>
+  </si>
+  <si>
+    <t>ALTERAÇÃO DE NOMENCLATURA DESENHOS CPP</t>
+  </si>
+  <si>
+    <t>Boa tarde, Favor renomear os termos abaixo das telas WWCPP221 e TTCPP conforme: "Desenho Fornec." para "Desenho Ref. Cliente". "DESENHOS" para "DESENHOS PARA PRODUÇÃO". At.te</t>
+  </si>
+  <si>
+    <t>Ajuste em gráficos no B.I -Mapear dados</t>
+  </si>
+  <si>
+    <t>13/05/2026</t>
+  </si>
+  <si>
+    <t>37781</t>
+  </si>
+  <si>
+    <t>Controle de sequência por nota fiscal -Trava no ROMANEIO</t>
+  </si>
+  <si>
+    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
+  </si>
+  <si>
+    <t>Edson João Hammermeister</t>
+  </si>
+  <si>
+    <t>17/05/2026</t>
+  </si>
+  <si>
+    <t>30712</t>
+  </si>
+  <si>
+    <t>Altona || Sistema ERP || Data Inclusão Material</t>
+  </si>
+  <si>
+    <t>Bom dia, Sandro! Eu fiz umas alterações em alguns itens no módulo de materiais e reparei que o sistema está mudando a data de inclusão junto com a alteração do cadastro. Esse problema não impacta em nada meu serviço, no entanto, achei importante avisar. Atenciosamente,</t>
+  </si>
+  <si>
+    <t>36201</t>
+  </si>
+  <si>
+    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
+  </si>
+  <si>
+    <t>37889</t>
+  </si>
+  <si>
+    <t>Solicitação de Transferência</t>
+  </si>
+  <si>
+    <t>Boa tarde, Por gentileza, poderia realizar a transferência dos itens destacados em verde, conforme ilustrado na imagem abaixo? Essa ação visa melhorar a experiência dos usuários no sistema. At.te</t>
+  </si>
+  <si>
+    <t>Calculo do custo - Apoio - subáreas</t>
+  </si>
+  <si>
+    <t>36541</t>
+  </si>
+  <si>
+    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
+  </si>
+  <si>
+    <t>Bom dia Prezados Espero que estejam bem. Precisamos da implementação de uma funcionalidade no que diz respeito a NF de devolução e baixa de estoque: CENÁRIO ATUAL A NF de devolução é emitida e saldo do item continua no sistema, requerendo que a baixa seja efetuada manualmente. O que, por vezes, ocas</t>
+  </si>
+  <si>
+    <t>Alini Ferreira Ganda</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>29847</t>
+  </si>
+  <si>
+    <t>Valor do ICMS Desonerado - XML</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde Sandro, O Estado de SC instituiu a obrigação do preenchimento do campo do valor do ICMS desonerado das notas, desde 01/01/2025. Campos a serem preenchidos: vICMSDeson e motDesICMS Dentro do XML da nota nós temos que informar o ICMS que foi desonerado na operação. Como nosso valor de saída </t>
+  </si>
+  <si>
+    <t>Jessica Priscila Gonçalves</t>
+  </si>
+  <si>
+    <t>38057</t>
+  </si>
+  <si>
+    <t>Apontamento tablets - pó de ferro</t>
+  </si>
+  <si>
+    <t>Bom dia, as observações das paradas não estão sendo transferidas para o excel, teria como fazer esse ajuste ? Atenciosamente,</t>
+  </si>
+  <si>
+    <t>37792</t>
+  </si>
+  <si>
+    <t>VISUALIZAÇÃO DO PROCEDIMENTO DE DESMOLDAGEM NO AP119</t>
+  </si>
+  <si>
+    <t>Bom dia! No AP119, no formulário de DESMOLDAGEM não aparece nenhum procedimento anexo: Mesmo que ele tenha sido anexado no formulário, durante o preenchimento do AP119: A sugestão é que ele apareça da mesma maneira que os procedimentos aparecem quando anexados em perguntas: Precisamos que o código e</t>
+  </si>
+  <si>
+    <t>Andre Gustavo Scharf</t>
+  </si>
+  <si>
+    <t>38117</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - vaso</t>
+  </si>
+  <si>
+    <t>Solicito melhorias</t>
+  </si>
+  <si>
+    <t>Marcelo Americo</t>
+  </si>
+  <si>
+    <t>37230</t>
+  </si>
+  <si>
+    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
+  </si>
+  <si>
+    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
+  </si>
+  <si>
+    <t>38043</t>
+  </si>
+  <si>
+    <t>Proporção de tempo de processo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reavaliar cálculo de rateio para intervalos iguais: - peças identificadas com divergência, (considerar o peso bruto da peça (OTF)) - EJ4293 1650kg, sequência 018MS; &gt;&gt;00:24:06 minutos - 5230585 506,25kg, sequência 022MP; &gt;&gt;00:22:11 minutos Conforme apontamento, essas duas peças iniciaram o processo </t>
+  </si>
+  <si>
+    <t>08/05/2026</t>
+  </si>
+  <si>
+    <t>37591</t>
+  </si>
+  <si>
+    <t>Passar sistema de Ordens na TV e Gatilhos ACR para WEB</t>
+  </si>
+  <si>
+    <t>Boa tarde, Chamado combinado com o Tiago para fazermos a transição do sistema de TV e ACR da manutenção para a WEB. A ideia é termos mais flexibilidade para trabalhar com o sistema para deixar ele mais moderno e funcional. Muito obrigado. Att,</t>
+  </si>
+  <si>
+    <t>35367</t>
+  </si>
+  <si>
+    <t>Indicadores MTTR e MDT</t>
+  </si>
+  <si>
+    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
+  </si>
+  <si>
+    <t>Criar CARDs Ordens na TV e Gatilhos ACR para WEB (copy)</t>
+  </si>
+  <si>
+    <t>16/05/2026</t>
+  </si>
+  <si>
+    <t>Criar Controlar paginação TV e Gatilhos ACR para WEB</t>
+  </si>
+  <si>
+    <t>38054</t>
+  </si>
+  <si>
+    <t>Criação de Sistema de Gestão de Treinamentos Usinagem</t>
+  </si>
+  <si>
+    <t>Bom dia, O objetivo desse ticket é para discutirmos o desenvolvimento de um Sistema Web de Gestão de Treinamentos para o setor de Usinagem. Na prática o que ele precisa fazer: * Cadastro de operadores, máquinas, instrutores e ementa de treinamentos; * Registro de treinamentos com presença digital, n</t>
+  </si>
+  <si>
+    <t>Pedro Henrique Poburko</t>
+  </si>
+  <si>
+    <t>37298</t>
+  </si>
+  <si>
+    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
+  </si>
+  <si>
+    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
+  </si>
+  <si>
+    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
+  </si>
+  <si>
+    <t>37855</t>
+  </si>
+  <si>
+    <t>Estratificação dos dados na tela Anexos do CPP</t>
+  </si>
+  <si>
+    <t>Bom dia, Sres., @Sandro, conforme conversado, precisamos de um botão "excel" para estratificar os dados na tela Anexos do CPP. Segue a tela em questão: Obrigado, Atenciosamente,</t>
+  </si>
+  <si>
+    <t>Gabriel Zancanella</t>
+  </si>
+  <si>
+    <t>11925936501</t>
+  </si>
+  <si>
+    <t>Layout ofertas exportação</t>
+  </si>
+  <si>
+    <t>38071</t>
+  </si>
+  <si>
+    <t>Avaliação de Ferramenta - LogX Narwall</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, Estou abrindo o chamado para avaliação da integração com API aberta da Ferramental LogX da Narwal com o sistema de Invoice. Abaixo o link da documentação enviada pela empresa. Desconheço procedimentos, gentileza informar o que há necessidade do nosso lado para avaliação. Acredito que uma </t>
+  </si>
+  <si>
+    <t>37552</t>
+  </si>
+  <si>
+    <t>Requisições BINAAR - Reunião</t>
+  </si>
+  <si>
+    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
+  </si>
+  <si>
+    <t>37746</t>
+  </si>
+  <si>
+    <t>Altona || Consignados - Diferença nos saldos</t>
+  </si>
+  <si>
+    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
+  </si>
+  <si>
+    <t>33631</t>
+  </si>
+  <si>
+    <t>Sistema de corridas - Custos - Reunião</t>
+  </si>
+  <si>
+    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
+  </si>
+  <si>
+    <t>37301</t>
+  </si>
+  <si>
+    <t>Registro de solda Digital</t>
+  </si>
+  <si>
+    <t>Boa tarde Maciel, Tudo bem? Maciel, seria possível para o Registro de solda Digital assim que o soldador preencher a sequência o campo de IS já vir automático com as duas IS que estão cadastradas no roteiro? O soldador só iria selecionar a qual ele iria usar dependendo o estágio da peça conforme rot</t>
+  </si>
+  <si>
+    <t>Danilo da Silva Pereira</t>
+  </si>
+  <si>
+    <t>33956</t>
+  </si>
+  <si>
+    <t>Definição de metas de custos de manutenção (META GERAL) (copy)</t>
+  </si>
+  <si>
+    <t>Edson, Por gentileza criar campo para definição de metas para os custos de manutenção.</t>
+  </si>
+  <si>
+    <t>Robmar Xavier</t>
+  </si>
+  <si>
+    <t>36842</t>
+  </si>
+  <si>
+    <t>Ajuste de Layout das ofertas</t>
+  </si>
+  <si>
+    <t>Boa Tarde Maciel, tudo bem? Favor padronizar a fonte das letras em nossas ofertas, após atualização as fontes estão aparecendo desconfiguradas e as ofertas estão saindo com "Feias". Segue exemplo a baixo: Note que os valores, e as informações da peça estão completamente fora do padrão. Aguardo corre</t>
+  </si>
+  <si>
+    <t>Alexandre Girardi</t>
+  </si>
+  <si>
+    <t>37323</t>
+  </si>
+  <si>
+    <t>BOTÃO DE EXCEL NA TELA WCPP22CP1</t>
+  </si>
+  <si>
+    <t>Bom dia, Favor criar um novo botão de exportar informações para o Excel na tela WCPP22CP1. At.te</t>
+  </si>
+  <si>
+    <t>38435</t>
+  </si>
+  <si>
+    <t>Controladoria</t>
+  </si>
+  <si>
+    <t>Divergência Integração Requisições FEADLER | BINAAR | KITO</t>
+  </si>
+  <si>
+    <t>Boa tarde a todos! Ações para correção dos registros do processo de requisições e compra de materiais de peças de reposição dos fornecedores FEADLER e BINAAR. 1. @Sandro Schram: orientação do Alexandro é desenvolvimento de melhoria Sistema para lançamento item a item (não item genérico). Como na tel</t>
+  </si>
+  <si>
+    <t>Paulo Giovani da Cruz</t>
+  </si>
+  <si>
+    <t>11925831287</t>
+  </si>
+  <si>
+    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES (copy)</t>
+  </si>
+  <si>
+    <t>11340954478</t>
+  </si>
+  <si>
+    <t>Levantamento de dados para Residencia de IA</t>
+  </si>
+  <si>
+    <t>23/02/2026</t>
+  </si>
+  <si>
+    <t>11925846238</t>
+  </si>
+  <si>
+    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER (copy)</t>
+  </si>
+  <si>
+    <t>37169</t>
+  </si>
+  <si>
+    <t>Alteração em relatorio dentro do sistema "Apontamento de produção" (copy)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
+  </si>
+  <si>
+    <t>11925846251</t>
+  </si>
+  <si>
+    <t>Sequencial number Clientes (copy)</t>
+  </si>
+  <si>
+    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy) (copy) (copy)</t>
+  </si>
+  <si>
+    <t>11925846920</t>
+  </si>
+  <si>
+    <t>Liberação Ensaio Mecanico Automatico (copy)</t>
+  </si>
+  <si>
+    <t>11925846254</t>
+  </si>
+  <si>
+    <t>Erro Planilhão - Itens conjuntos (copy)</t>
+  </si>
+  <si>
+    <t>11925846848</t>
+  </si>
+  <si>
+    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada (copy)</t>
+  </si>
+  <si>
+    <t>Dashboard de Change Log - Governança de TI</t>
+  </si>
+  <si>
+    <t>Período</t>
+  </si>
+  <si>
+    <t>Out/2025</t>
+  </si>
+  <si>
+    <t>Base</t>
+  </si>
+  <si>
+    <t>Tickets corporativos para intranet / Power BI / Excel</t>
+  </si>
+  <si>
+    <t>Total de tickets</t>
+  </si>
+  <si>
+    <t>% dentro do SLA</t>
+  </si>
+  <si>
+    <t>Tempo médio (dias)</t>
+  </si>
+  <si>
+    <t>Áreas atendidas</t>
+  </si>
+  <si>
+    <t>Status final</t>
+  </si>
+  <si>
+    <t>Encerrado</t>
+  </si>
+  <si>
+    <t>Resumo Executivo</t>
+  </si>
+  <si>
+    <t>Tickets por Área</t>
+  </si>
+  <si>
+    <t>Distribuição por Tipo</t>
+  </si>
+  <si>
+    <t>Cumprimento SLA (15 dias)</t>
+  </si>
+  <si>
+    <t>Status Final</t>
+  </si>
+  <si>
+    <t>Tickets por Semana</t>
+  </si>
+  <si>
+    <t>Volume</t>
+  </si>
+  <si>
+    <t>Muito Alta</t>
   </si>
   <si>
     <t>Sim</t>
-  </si>
-  <si>
-    <t>37774</t>
-  </si>
-  <si>
-    <t>Oferta/oportunidade - identificação analista de vendas.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prezado, bom dia. O processo que migra as ofertas/oportunidades para o CRM está definindo o ADMINISTRADOR como responsável por todas elas. Isso gera um problema quando o usuário tenta localizar suas próprias ofertas/oportunidades no CRM. A Senior analisou a situação e sugeriu uma forma de contornar </t>
-  </si>
-  <si>
-    <t>Alexandre Longo</t>
-  </si>
-  <si>
-    <t>36046</t>
-  </si>
-  <si>
-    <t>Categoria não informada</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Frontend</t>
-  </si>
-  <si>
-    <t>Solicitante não informado</t>
-  </si>
-  <si>
-    <t>Equipe não informada</t>
-  </si>
-  <si>
-    <t>37826</t>
-  </si>
-  <si>
-    <t>IROG Corte pó de ferro no BI</t>
-  </si>
-  <si>
-    <t>Boa tarde, Esteva verificando que alguns modelos não puxaram o tempo padrão de corte para o BI. Esse e apenas alguns desse modelo. Acho que o motivo de não estar buscando e que o setor de corte dessa peça não e o 1415 "Corte pó de ferro" e sim o 1414 "Corte de Canal com Maçarico" se realmente esse f</t>
-  </si>
-  <si>
-    <t>Eduardo Basso Pinto</t>
-  </si>
-  <si>
-    <t>37361</t>
-  </si>
-  <si>
-    <t>Base Histórica da Data de Reconhecimento  de Receita (copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Conforme conversamos, segue solicitado para criar base histórica do reconhecimento de receita. Necessário gerar congelamento no último dia do mês e todo domingo (semanal). Segundo Alexandro, a necessidade é de 1 mês e meio de histórico. Regras na Tabela * Coluna - reconhecimento de receita </t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>Bloqueio de apontamento eletrônico</t>
-  </si>
-  <si>
-    <t>17/04/2026</t>
-  </si>
-  <si>
-    <t>33130</t>
-  </si>
-  <si>
-    <t>Comercial</t>
-  </si>
-  <si>
-    <t>Consulta Cadastro de LEADs</t>
-  </si>
-  <si>
-    <t>Laura Herrmann Schmickler</t>
-  </si>
-  <si>
-    <t>Bloqueio de apontamento eletrônico - Envio de e-mail</t>
-  </si>
-  <si>
-    <t>36741</t>
-  </si>
-  <si>
-    <t>Engenharia</t>
-  </si>
-  <si>
-    <t>ACERTO DE NÚMERO DE LINHAS EM MOVIMENTAÇÃO SETORIAL</t>
-  </si>
-  <si>
-    <t>Boa tarde, Permitir que o sistema de movimentação setorial [WCPP22AI] faça acerto do número de linhas nas sequências selecionadas conforme permitido na sistemática da tela WCPP2202. At.te</t>
-  </si>
-  <si>
-    <t>Willian Gabriel Paixão dos Santos</t>
-  </si>
-  <si>
-    <t>20/02/2026</t>
-  </si>
-  <si>
-    <t>Fevereiro</t>
-  </si>
-  <si>
-    <t>35453</t>
-  </si>
-  <si>
-    <t>Qualidade</t>
-  </si>
-  <si>
-    <t>Inclusão de informação CPP</t>
-  </si>
-  <si>
-    <t>Boa tarde, Conforme conversa, por gentileza incluir campo para preencher o "Tempo de Enchimento Projetado" no Formulário de Projeto no CPP: E, além disso, esse novo dado deve aparecer no sistema de corridas, na tela abaixo (ao lado dessa informação deve aparecer a tolerância de +-15%): At.te,</t>
-  </si>
-  <si>
-    <t>Helena Mariana Segalla</t>
-  </si>
-  <si>
-    <t>27/04/2026</t>
-  </si>
-  <si>
-    <t>Semana 4</t>
-  </si>
-  <si>
-    <t>28277</t>
-  </si>
-  <si>
-    <t>Logística</t>
-  </si>
-  <si>
-    <t>Incluir OTF Romaneio</t>
-  </si>
-  <si>
-    <t>Boa tarde Gentileza incluir OTF no romaneio. Dúvidas, estou a disposição.</t>
-  </si>
-  <si>
-    <t>Rafael De Souza</t>
-  </si>
-  <si>
-    <t>32141</t>
-  </si>
-  <si>
-    <t>Correção</t>
-  </si>
-  <si>
-    <t>Cadastro de Embalagem no CPP (APS)</t>
-  </si>
-  <si>
-    <t>Bom dia, Flavio, Gentileza criar na tela do CPP 03 campos. * Código da Embalagem: * Dimensão: * Peso Embalagem: O preenchimento será feito de duas formas: * O histórico vamos enviar uma lista com o modelo e as informações para a atualização de todos os vigentes. * Os novos modelos o Diego irá preenc</t>
-  </si>
-  <si>
-    <t>02/06/2026</t>
-  </si>
-  <si>
-    <t>37677</t>
-  </si>
-  <si>
-    <t>melhoria no cadastro e relatório do MRP - Reunião</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Criar relatório para gerar o mrp por itens lançados, estes itens o usuário vai alimentar em um campo, exemplo: tenho a programação da moldagem da semana 15 onde serão feitos um total 20 modelos aleatórios , vou alimentar o sistema como os 20 modelos e quantidades de peças a serem produzidas de cada </t>
-  </si>
-  <si>
-    <t>Fernando Beltrame</t>
-  </si>
-  <si>
-    <t>37367</t>
-  </si>
-  <si>
-    <t>Download automático de arquivos excel.</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos que seja feita uma atualização no sistema Gestão de Ações. Quando colocamos uma anexo do tipo excel nas evidências, o sistema fica fazendo um download do arquivo sempre que a página é atualizada. Precisamos corrigir para o download ser por um botão. "Fazer download do arquivo?"</t>
-  </si>
-  <si>
-    <t>Matheus Gonçalves</t>
-  </si>
-  <si>
-    <t>34919</t>
-  </si>
-  <si>
-    <t>Solicitação de BI QlikSense – Indicadores de Ofertas</t>
-  </si>
-  <si>
-    <t>Bom dia, Gostaria de desenvolver um BI que apresente dois indicadores relacionados ao envio de ofertas: 1. % de ofertas enviadas dentro do prazo definido no momento da abertura do PO. Este será o indicador principal. 1. Prazo médio de envio das ofertas (em dias) Apenas para acompanhamento; não haver</t>
-  </si>
-  <si>
-    <t>10/02/2026</t>
-  </si>
-  <si>
-    <t>Semana 2</t>
-  </si>
-  <si>
-    <t>33549</t>
-  </si>
-  <si>
-    <t>Integração de sistema Logística x data book - Relatório x Registro End's</t>
-  </si>
-  <si>
-    <t>bom dia, Com a alta demanda de peças entrando no depósito, precisamos fazer um sistema que integre Logística x data book, ou seja, peças que (entram no depósito/embarcam e necessitam que seja enviada documentação ao cliente). Com esta integração acreditamos que conseguiremos acelerar a montagem de d</t>
-  </si>
-  <si>
-    <t>Rosivaldo Silva</t>
-  </si>
-  <si>
-    <t>20/04/2026</t>
-  </si>
-  <si>
-    <t>Parte visual e filtros</t>
-  </si>
-  <si>
-    <t>34073</t>
-  </si>
-  <si>
-    <t>ALTC  - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Fazendo</t>
-  </si>
-  <si>
-    <t>37949</t>
-  </si>
-  <si>
-    <t>Almoxarifado</t>
-  </si>
-  <si>
-    <t>Trava na requisição em caso de inventário em aberto</t>
-  </si>
-  <si>
-    <t>Boa tarde! Estamos enfrentando uma situação que tem gerado saldo negativo no sistema quando há um inventário em andamento e, simultaneamente, ocorre a requisição de materiais. Para evitar esse problema, solicitamos a implementação de uma trava no sistema de requisição, de modo que, enquanto o invent</t>
-  </si>
-  <si>
-    <t>Alex Julio Estacio</t>
-  </si>
-  <si>
-    <t>36724</t>
-  </si>
-  <si>
-    <t>Alteração de registro de pintura</t>
-  </si>
-  <si>
-    <t>38154</t>
-  </si>
-  <si>
-    <t>Altona | CC 40104 Bloqueado</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Sandro Favor criar uma regra na pré-lista ou requisição para que ao digitar o CC 40104 - 1.5.02.002 - Depósito e Despacho (Embalagem) O SNB veja se a conta contábil utilizada é 26851 - 5.1.2.01.120 - EMBALAGEM. Se a conta contábil for 26851, o SNB deve manter o CC 40104. Se não for a conta </t>
-  </si>
-  <si>
-    <t>Edson Vitor Scharf Filho</t>
-  </si>
-  <si>
-    <t>07/05/2026</t>
-  </si>
-  <si>
-    <t>37659</t>
-  </si>
-  <si>
-    <t>Altona || Estoque de Consignados - Contabilização da Devolução</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Preciso alterar a contabilização de requisição de devolução do consignado: Atualmente está assim: D - 32187 C - Estoque Consignado -------------------------------- Mas o correto é: D - Resultado Custo Se for inserto, por exemplo, a conta será 5.1.2.01.115 Centro de Custo - 60600 - 1</t>
-  </si>
-  <si>
-    <t>34223</t>
-  </si>
-  <si>
-    <t>Usinagem</t>
-  </si>
-  <si>
-    <t>Alterar gráfico IROG - Usinagem</t>
-  </si>
-  <si>
-    <t>Boa tarde Favor realizar alteração no gráfico de cluster, podendo ser utilizado um gráfico de barras na horizontal. Segue abaixo um exemplo de como pode ser o gráfico (no eixo onde está as operações, mostrar os modelos) Att,</t>
-  </si>
-  <si>
-    <t>Caio Henrique Vicente Bento</t>
-  </si>
-  <si>
-    <t>38108</t>
-  </si>
-  <si>
-    <t>Lentidão no apontamento eletrônico – Mesa Redonda -  Analise</t>
-  </si>
-  <si>
-    <t>Boa tarde, O operador que está em fase de testes com o apontamento eletrônico na mesa redonda relatou que o sistema está apresentando lentidão excessiva, com travamentos frequentes. Solicitamos, por gentileza, a reavaliação do assunto já tratado no chamado nº 36298. Temos um vídeo demonstrativo no q</t>
-  </si>
-  <si>
-    <t>Douglas Garcia</t>
-  </si>
-  <si>
-    <t>Envio de ofertar trocar o usuário responsável</t>
-  </si>
-  <si>
-    <t>37929</t>
-  </si>
-  <si>
-    <t>Indicador de ACR</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos agora iniciar a implementação dos indicadores para as ACRs e temos alguns pontos a ajustar. 1. Precisamos ter a informação de que tipo de gatilho foi nessa coluna 1. Precisamos ter uma coluna que identifique se já temos anexo (1 - sim / 0 - não) 1. A ideia é termos um um resumo q</t>
-  </si>
-  <si>
-    <t>Enzo Luiz Okabe Auad</t>
-  </si>
-  <si>
-    <t>Atualizar campos: data, hora e prazo da proposta</t>
-  </si>
-  <si>
-    <t>37857</t>
-  </si>
-  <si>
-    <t>INLCUIR ALTERAÇÃO ( ESTAGIO DE FRABRICAÇÃO ) AONDE ALTERA DADOS E APONTAMENTOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Necessitamos da opção para alterar o estado de fabricação da peça ( bruto ) ou ( usinado, Colaboradores que apontam incorretamente esse estágio prejudica diretamente o Irog, conseguimos incluir esta opção? At.te.,</t>
-  </si>
-  <si>
-    <t>Otavio Zimmermann Neto</t>
-  </si>
-  <si>
-    <t>36722</t>
-  </si>
-  <si>
-    <t>Bloco K - Integração dados Altona / Benner.</t>
-  </si>
-  <si>
-    <t>38159</t>
-  </si>
-  <si>
-    <t>Cadastrar Rota Cinza</t>
-  </si>
-  <si>
-    <t>Bom dia O cadastro da rota Cinza não esta entrando para os operadores.</t>
-  </si>
-  <si>
-    <t>37963</t>
-  </si>
-  <si>
-    <t>Chamado Caminhão Munck - WMS</t>
-  </si>
-  <si>
-    <t>Bom dia Segue chamado para implementar o sistema do WMS no caminhão Munck.</t>
-  </si>
-  <si>
-    <t>37974</t>
-  </si>
-  <si>
-    <t>Problemas na baixa de ordens que estão sendo programadas</t>
-  </si>
-  <si>
-    <t>Boa tarde, Estou abrindo esse chamado referente a uns problemas que estamos tendo quanto as ordens que estamos cadastrando com método e base tempo que agora estão passando pela programação com a caixa "Gerar SS Planejamento" selecionada Ex: OS 327892 é uma preventiva mensal para a ponte rolante 14 c</t>
-  </si>
-  <si>
-    <t>37947</t>
-  </si>
-  <si>
-    <t>Sistema de apontamento - Tablets pó de ferro</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia é necessário a melhoria de algumas funções no sistema de apontamento pó de ferro. 1. As sequencias de peças cortadas no dia estão aparecendo para todos os cortadores, precisamos que apenas apareça a sequência cortada para edição e verificação do cortador que cortou a peça. 2. As observações </t>
-  </si>
-  <si>
-    <t>Amanda Vitoria Aroeira Marinho</t>
-  </si>
-  <si>
-    <t>37714</t>
-  </si>
-  <si>
-    <t>Solicitação de inclusão de tela no WMS – Inclusão de saldo no endereço de recebimento</t>
-  </si>
-  <si>
-    <t>Boa tarde! Solicitamos a inclusão de uma tela no WMS do Almoxarifado para inclusão de saldo virtual no endereço de recebimento. Essa funcionalidade se faz necessária pelas seguintes situações operacionais: Quando um material é movimentado para estoque de terceiros, o saldo virtual no WMS acaba sendo</t>
-  </si>
-  <si>
-    <t>38203</t>
-  </si>
-  <si>
-    <t>Melhorias no apontamento eletrônico – Corte Escarfa</t>
-  </si>
-  <si>
-    <t>Boa tarde, Retorno sobre o desenvolvimento do sistema de apontamento eletrônico – corte escarfa: * É necessário que, assim como nos demais sistemas, sejam exibidos modelo e croqui. * Para melhorar a confiabilidade do apontamento, devemos incluir perguntas de confirmação, por exemplo: “Deseja finaliz</t>
-  </si>
-  <si>
-    <t>38053</t>
-  </si>
-  <si>
-    <t>FW: Alteração Liga Stara- EA4257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia, Solicito uma solução para um problema rotineiro que o setor de orçamento vem enfrentando, caso exista a necessidade de gerar uma simulação, de uma liga nova para itens que já fornecemos. O sistema foi bloqueado no ano passado para alteração de itens que já fornecemos, o que não é errado no </t>
-  </si>
-  <si>
-    <t>Pierro Conrrad da Silva</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Preparar Ambiente</t>
-  </si>
-  <si>
-    <t>Aprimoramento Ailton - Backend</t>
-  </si>
-  <si>
-    <t>38052</t>
-  </si>
-  <si>
-    <t>pdi eletronico</t>
-  </si>
-  <si>
-    <t>Preciso que seja ajustado o campo de observação do PDI para o inspetor, pois hoje com o limite de caracteres que tem o inspetor não consegue passar a informação completa para o Analista. att</t>
-  </si>
-  <si>
-    <t>Gerson Mendonça</t>
-  </si>
-  <si>
-    <t>38166</t>
-  </si>
-  <si>
-    <t>ENC: Condição de pagamento  para Consórcio.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Richard/Sandro, Por solicitação do financeiro precisamos cadastrar uma nova condição de pagamento: Consorcio que no momento quando criamos aparece como antecipado. Aproveito a oportunidade para gerar um prazo de 15/30/45. @Larissa Gabriely Gaia Alves assim que for gerado os prazos por favor </t>
-  </si>
-  <si>
-    <t>Luciana Bello</t>
-  </si>
-  <si>
-    <t>37692</t>
-  </si>
-  <si>
-    <t>[COMPRAS] Cancelamento de saldo por item</t>
-  </si>
-  <si>
-    <t>Bom dia, Na tela de pedidos temos a opção de cancelar saldo do pedido. Gostaríamos que fosse criada a opção de cancelar o saldo em aberto somente de um material dentro do pedido. Como mostra a imagem, somente um dos itens teve entrada, mas ainda consta como aberto. Gostaríamos de cancelar esse saldo</t>
-  </si>
-  <si>
-    <t>Larissa Gabriely Gaia Alves</t>
-  </si>
-  <si>
-    <t>37690</t>
-  </si>
-  <si>
-    <t>Melhoria chamado 36233 incluir horário ponto como referência</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito uma melhoria no chamado 36233 (automatizar apontamento) para que ele tenha como base o horário ponto, ou seja, puxe desde que ele chegue na empresa até sua saída.</t>
-  </si>
-  <si>
-    <t>Glória Danielly Lima Rodrigues</t>
-  </si>
-  <si>
-    <t>32133</t>
-  </si>
-  <si>
-    <t>Novo Recurso</t>
-  </si>
-  <si>
-    <t>Automatização planilha comercial - PARTE 2/2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
-  </si>
-  <si>
-    <t>Jacson Schneider Movidesk</t>
-  </si>
-  <si>
-    <t>36206</t>
-  </si>
-  <si>
-    <t>Cadastro de LEADs para Desenvolvimento de Negócios - Tela web</t>
-  </si>
-  <si>
-    <t>Criar uma aba no ERP Altona de cadastro de Leads do Desenvolvimento de Negócios para utilização no CRM. No documento possui, o formato da tela, fluxograma, observações quanto a uso. Em caso de reunião para alinharmos a ferramenta, por favor, adicionar as seguintes pessoas: Adnan, Alexandre Girardi e</t>
-  </si>
-  <si>
-    <t>Adnan Pires</t>
-  </si>
-  <si>
-    <t>37783</t>
-  </si>
-  <si>
-    <t>PCP</t>
-  </si>
-  <si>
-    <t>Inclusão coluna no Planilhão</t>
-  </si>
-  <si>
-    <t>Bom dia Flávio, Favor incluir no Planilhão da Carteira UPR uma coluna com a informação se o modelo (ferramental) está bloqueado para produção. Essa informação geramos relatório em: Modelos &gt; Consulta &gt; Cadastrado de Modelos &gt; Por modelo &gt; Conserto de Modelos &gt; Imprimir &gt; Somente em aberto Data inici</t>
-  </si>
-  <si>
-    <t>Caroline Schmitt</t>
-  </si>
-  <si>
-    <t>38156</t>
-  </si>
-  <si>
-    <t>Cadastro de Linhas no Apontamento Eletrônico</t>
-  </si>
-  <si>
-    <t>Bom dia, Solicito, por gentileza, o cadastro das linhas Volvo e Alstom no sistema de apontamento eletrônico, conforme abaixo: * Alstom: utilizar o mesmo modelo aplicado à mesa redonda; * Volvo: utilizar o mesmo modelo da fase 4. Fico à disposição para quaisquer dúvidas. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>35602</t>
-  </si>
-  <si>
-    <t>Coleta e identificação de sequencia - Analise de multiplas Fotos</t>
-  </si>
-  <si>
-    <t>35890</t>
-  </si>
-  <si>
-    <t>Criar API para receber informações do MES para a abertura da SS</t>
-  </si>
-  <si>
-    <t>31319</t>
-  </si>
-  <si>
-    <t>Ajuste na inclusão de sequência manual no coletor do WMS</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de solicitar um ajuste no sistema do coletor WMS para que, ao incluir uma sequência manual, o sistema aceite a entrada independentemente da utilização de letras maiúsculas ou minúsculas. Essa melhoria contribuirá para a padronização do processo e reduzirá possíveis erros operacio</t>
-  </si>
-  <si>
-    <t>Johnny José Rocha</t>
-  </si>
-  <si>
-    <t>23838</t>
-  </si>
-  <si>
-    <t>Novo Sistema</t>
-  </si>
-  <si>
-    <t>Verificar se foi vinculada a entrada e saida com o outro módulo do sistema</t>
-  </si>
-  <si>
-    <t>36809</t>
-  </si>
-  <si>
-    <t>FINALIZAR 501</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor finalizar todos os formulários do setor 501 que estão em aberto antes da conclusão do ticket 28147. At.te</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
-  </si>
-  <si>
-    <t>37190</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO NO SISTEMA DE ORDENS.</t>
-  </si>
-  <si>
-    <t>Boa tarde, Gostaria de solicitar uma pequena alteração no sistema de Listas de ordens, onde para nós MANUTENÇÃO USINAGEM. Hoje aparece ordens de equipamentos pneumáticos, manutenção CIVIL, ENCANADOR, dentre outras que não fazem parte da nossa M.O, isso seria possível direcionar aos setores responsáv</t>
-  </si>
-  <si>
-    <t>Guilherme Ferreira</t>
-  </si>
-  <si>
-    <t>37095</t>
-  </si>
-  <si>
-    <t>INCLUSAO E EXCLUSAO DE NF/ROMANEIOS</t>
-  </si>
-  <si>
-    <t>Bom dia, Maciel/Sandro Segue em anexo, apresentação das telas de inclusão e exclusão de NFS/ROMANEIOS, conforme conversado via teems.</t>
-  </si>
-  <si>
-    <t>Rodrigo Santos Rocha</t>
-  </si>
-  <si>
-    <t>37672</t>
-  </si>
-  <si>
-    <t>RES: Certificados de Qualidade</t>
-  </si>
-  <si>
-    <t>Bom dia Senhores, Temos algum retorno sobre a demanda abaixo? Atenciosamente, De: Andre Traleski Enviada em: terça-feira, 28 de outubro de 2025 10:26 Para: sistemas@ti-altona.movidesk.com Cc: Maciel Nolli Assunto: ENC: Certificados de Qualidade Bom dia, Favor abrir chamado para verificação das diver</t>
-  </si>
-  <si>
-    <t>Andre Traleski</t>
-  </si>
-  <si>
-    <t>36972</t>
-  </si>
-  <si>
-    <t>Inserir CPC e Ordem de compra automaticamente no GED</t>
-  </si>
-  <si>
-    <t>Boa tarde, Precisamos implementar uma melhoria no sistema de emissão de CPC para que, no momento da criação, a CPC seja automaticamente integrada ao GED. Além disso, é necessário avaliar a possibilidade de incluir a opção de anexar a Ordem de Compra à CPC, garantindo que esse documento também seja e</t>
-  </si>
-  <si>
-    <t>Jaqueline Cogorni Mendes</t>
-  </si>
-  <si>
-    <t>23/03/2026</t>
-  </si>
-  <si>
-    <t>38021</t>
-  </si>
-  <si>
-    <t>Contabilidade</t>
-  </si>
-  <si>
-    <t>RES: Sucata Retorno Mar2026</t>
-  </si>
-  <si>
-    <t>Boa tarde Sandro, Favor incluir o Saldos abaixo em 31/03/2026 no sistemas de requisição, mantendo o mesmo custo médio (Isto é referente aquele problema de não contabilização do refugo nas entradas de sucata retorno em março). Conta Descrição da Conta Código Descrição do Material UN Incluir ou Retira</t>
-  </si>
-  <si>
-    <t>Rafael Pereira</t>
-  </si>
-  <si>
-    <t>06/05/2026</t>
-  </si>
-  <si>
-    <t>36544</t>
-  </si>
-  <si>
-    <t>Excelência Operacional</t>
-  </si>
-  <si>
-    <t>Sistema de Metas</t>
-  </si>
-  <si>
-    <t>Bom dia Srs., O sistema de cadastro de Metas n?o est? funcionando, visto que fiz o cadastro para os setores de Inspe??o conforme abaixo: O B.I. est? trazendo a informa??o, conforme abaixo: Solicitei ao Felipe que desse uma carga de dados para avaliar, o mesmo fez e o B.I. n?o trouxe as informa??es c</t>
-  </si>
-  <si>
-    <t>Gabriel Lucas Kertichka</t>
-  </si>
-  <si>
-    <t>29/04/2026</t>
-  </si>
-  <si>
-    <t>31158</t>
-  </si>
-  <si>
-    <t>Status movimentação OM -WMS</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme verificado em Consulta O.M., se eu coloco o status de "AGUARDANDO" ele está puxando as OM entregue, ou seja, não está puxando corretamente.</t>
-  </si>
-  <si>
-    <t>36816</t>
-  </si>
-  <si>
-    <t>Gráfico de barras empilhadas “Retrabalhos para aprovação”</t>
-  </si>
-  <si>
-    <t>37412</t>
-  </si>
-  <si>
-    <t>Registro de Preset - Reunião</t>
-  </si>
-  <si>
-    <t>Se faz necessário desenvolver um registro de requisição para uso da usinagem/Preset.</t>
-  </si>
-  <si>
-    <t>Lucas Sebold Movidesk</t>
-  </si>
-  <si>
-    <t>18/05/2026</t>
-  </si>
-  <si>
-    <t>30722</t>
-  </si>
-  <si>
-    <t>NOVO ESTADO DE FORNECIMENTO</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar um novo estado de fornecimento no CPP tela WWCPP221 chamado "I.C sem fundido": Esta opção com liga 0 deve permitir a montagem de conjuntos para serem faturados no depósito sem a necessidade de um item fundido no conjunto. At.te</t>
-  </si>
-  <si>
-    <t>35503</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Usinagem - subáreas</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Na reunião realizada em 02/10/2025, foi discutido o tema apropriação do custeio. Estiveram presentes: Rafael Pereira, Paulo Cruz e Alexandre Longo. Como já existiam dois chamados1 abertos, as tarefas foram inicialmente vinculadas a eles. Porém, com a evolução das demandas, ficou acordada a abertura </t>
-  </si>
-  <si>
-    <t>06/10/2025</t>
-  </si>
-  <si>
-    <t>Outubro</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Inspeção - subáreas</t>
-  </si>
-  <si>
-    <t>34336</t>
-  </si>
-  <si>
-    <t>DIÁRIO DE BORDO - Acompanhamento</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor atualizar o sistema de Diário de Bordo [UCPP221Y] no CPP para que permita mais opções de cadastros e consultas conforme campos existentes da tela WCPP22K, exceto os riscados na imagem abaixo, e com duas opções a mais sendo "Peso Unitário" e "Tipo de Produção": At.te</t>
-  </si>
-  <si>
-    <t>38074</t>
-  </si>
-  <si>
-    <t>ALTERAÇÃO DE NOMENCLATURA DESENHOS CPP</t>
-  </si>
-  <si>
-    <t>Boa tarde, Favor renomear os termos abaixo das telas WWCPP221 e TTCPP conforme: "Desenho Fornec." para "Desenho Ref. Cliente". "DESENHOS" para "DESENHOS PARA PRODUÇÃO". At.te</t>
-  </si>
-  <si>
-    <t>Ajuste em gráficos no B.I -Mapear dados</t>
-  </si>
-  <si>
-    <t>37781</t>
-  </si>
-  <si>
-    <t>TI</t>
-  </si>
-  <si>
-    <t>Controle de sequência por nota fiscal -Trava no ROMANEIO</t>
-  </si>
-  <si>
-    <t>Prezados, Em reunião realizada nesta data, foram identificadas as demandas necessárias para a estruturação da DRE gerencial, com base nas notas fiscais emitidas no mês e no respectivo custo de cada sequência faturada, contemplando os grupos de receitas e despesas: - a linha de ROL, referente ao fatu</t>
-  </si>
-  <si>
-    <t>Edson João Hammermeister</t>
-  </si>
-  <si>
-    <t>30712</t>
-  </si>
-  <si>
-    <t>Altona || Sistema ERP || Data Inclusão Material</t>
-  </si>
-  <si>
-    <t>Bom dia, Sandro! Eu fiz umas alterações em alguns itens no módulo de materiais e reparei que o sistema está mudando a data de inclusão junto com a alteração do cadastro. Esse problema não impacta em nada meu serviço, no entanto, achei importante avisar. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>36201</t>
-  </si>
-  <si>
-    <t>ATUALIZAÇÃO DE FLUXOS E SISTEMAS PARA INCLUSÃO DE P&amp;D</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor proceder com as seguintes solicitações: 1. Revisar fluxos 100, 101, 102, 103, 104, 105, 108, 112, 113, 114, 115 e 116, conforme imagens e planilha de dependências anexas. 2. Criar pergunta na movimentação dos setores 509, 516 e 527, somente nos fluxos citados acima, perguntando "O ite</t>
-  </si>
-  <si>
-    <t>37889</t>
-  </si>
-  <si>
-    <t>Solicitação de Transferência</t>
-  </si>
-  <si>
-    <t>Boa tarde, Por gentileza, poderia realizar a transferência dos itens destacados em verde, conforme ilustrado na imagem abaixo? Essa ação visa melhorar a experiência dos usuários no sistema. At.te</t>
-  </si>
-  <si>
-    <t>Calculo do custo - Apoio - subáreas</t>
-  </si>
-  <si>
-    <t>36541</t>
-  </si>
-  <si>
-    <t>[COMPRAS] MELHORIA NF de devolução e baixa de estoque</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>29847</t>
-  </si>
-  <si>
-    <t>Valor do ICMS Desonerado - XML</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde Sandro, O Estado de SC instituiu a obrigação do preenchimento do campo do valor do ICMS desonerado das notas, desde 01/01/2025. Campos a serem preenchidos: vICMSDeson e motDesICMS Dentro do XML da nota nós temos que informar o ICMS que foi desonerado na operação. Como nosso valor de saída </t>
-  </si>
-  <si>
-    <t>Jessica Priscila Gonçalves</t>
-  </si>
-  <si>
-    <t>38057</t>
-  </si>
-  <si>
-    <t>Apontamento tablets - pó de ferro</t>
-  </si>
-  <si>
-    <t>Bom dia, as observações das paradas não estão sendo transferidas para o excel, teria como fazer esse ajuste ? Atenciosamente,</t>
-  </si>
-  <si>
-    <t>37792</t>
-  </si>
-  <si>
-    <t>VISUALIZAÇÃO DO PROCEDIMENTO DE DESMOLDAGEM NO AP119</t>
-  </si>
-  <si>
-    <t>Bom dia! No AP119, no formulário de DESMOLDAGEM não aparece nenhum procedimento anexo: Mesmo que ele tenha sido anexado no formulário, durante o preenchimento do AP119: A sugestão é que ele apareça da mesma maneira que os procedimentos aparecem quando anexados em perguntas: Precisamos que o código e</t>
-  </si>
-  <si>
-    <t>Andre Gustavo Scharf</t>
-  </si>
-  <si>
-    <t>38117</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - vaso</t>
-  </si>
-  <si>
-    <t>Solicito melhorias</t>
-  </si>
-  <si>
-    <t>Marcelo Americo</t>
-  </si>
-  <si>
-    <t>37230</t>
-  </si>
-  <si>
-    <t>Melhoria SMI - Solicitação da supervisão - Homologação</t>
-  </si>
-  <si>
-    <t>Bom dia, Precisamos implementar um módulo de Monitoramento de Preventiva de Máquinas (Criticidade de programação). A ideia é fazermos algo similar o Módulo de Máquinas monitoradas ACR. O objetivo é criarmos um modulo para cadastrar máquinas críticas que precisam ser monitoradas pelo programador e ao</t>
-  </si>
-  <si>
-    <t>38043</t>
-  </si>
-  <si>
-    <t>Proporção de tempo de processo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reavaliar cálculo de rateio para intervalos iguais: - peças identificadas com divergência, (considerar o peso bruto da peça (OTF)) - EJ4293 1650kg, sequência 018MS; &gt;&gt;00:24:06 minutos - 5230585 506,25kg, sequência 022MP; &gt;&gt;00:22:11 minutos Conforme apontamento, essas duas peças iniciaram o processo </t>
-  </si>
-  <si>
-    <t>08/05/2026</t>
-  </si>
-  <si>
-    <t>37591</t>
-  </si>
-  <si>
-    <t>Passar sistema de Ordens na TV e Gatilhos ACR para WEB</t>
-  </si>
-  <si>
-    <t>Boa tarde, Chamado combinado com o Tiago para fazermos a transição do sistema de TV e ACR da manutenção para a WEB. A ideia é termos mais flexibilidade para trabalhar com o sistema para deixar ele mais moderno e funcional. Muito obrigado. Att,</t>
-  </si>
-  <si>
-    <t>35367</t>
-  </si>
-  <si>
-    <t>Indicadores MTTR e MDT</t>
-  </si>
-  <si>
-    <t>Bom dia, Quero solicitar, se possível, fazer uma alteração no sistema de manutenção para que ele possa calcular o MTTR e o MDT separados. Todavia, sabendo que ambos se complementam porque o MDT calcula o tempo total da máquina parada que seria quando o operador abre a O.S e coloca a máquina em manut</t>
-  </si>
-  <si>
-    <t>Criar CARDs Ordens na TV e Gatilhos ACR para WEB (copy)</t>
-  </si>
-  <si>
-    <t>17/05/2026</t>
-  </si>
-  <si>
-    <t>Criar Controlar paginação TV e Gatilhos ACR para WEB</t>
-  </si>
-  <si>
-    <t>38054</t>
-  </si>
-  <si>
-    <t>Criação de Sistema de Gestão de Treinamentos Usinagem</t>
-  </si>
-  <si>
-    <t>Bom dia, O objetivo desse ticket é para discutirmos o desenvolvimento de um Sistema Web de Gestão de Treinamentos para o setor de Usinagem. Na prática o que ele precisa fazer: * Cadastro de operadores, máquinas, instrutores e ementa de treinamentos; * Registro de treinamentos com presença digital, n</t>
-  </si>
-  <si>
-    <t>Pedro Henrique Poburko</t>
-  </si>
-  <si>
-    <t>37298</t>
-  </si>
-  <si>
-    <t>Melhoria | Custo de venda Orçamento Nacional (REUNIÃO)</t>
-  </si>
-  <si>
-    <t>Bom dia, Gentileza criar a melhoria na CPC impressa conforme abaixo: * Quando gerar uma CPC para cliente do mercado Nacional, apresentar os novos campos abaixo, abaixo do campo de frete: * % de despesa de frete, verificar com o comercial onde é preenchido (Aline) * %valor de despesa de frete orçado:</t>
-  </si>
-  <si>
-    <t>Controle de sequência por nota fiscal - Alerta notas fiscais sem sequencia informada</t>
-  </si>
-  <si>
-    <t>37855</t>
-  </si>
-  <si>
-    <t>Estratificação dos dados na tela Anexos do CPP</t>
-  </si>
-  <si>
-    <t>Bom dia, Sres., @Sandro, conforme conversado, precisamos de um botão "excel" para estratificar os dados na tela Anexos do CPP. Segue a tela em questão: Obrigado, Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Gabriel Zancanella</t>
-  </si>
-  <si>
-    <t>37530</t>
-  </si>
-  <si>
-    <t>Layout ofertas exportação</t>
-  </si>
-  <si>
-    <t>38071</t>
-  </si>
-  <si>
-    <t>Avaliação de Ferramenta - LogX Narwall</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, Estou abrindo o chamado para avaliação da integração com API aberta da Ferramental LogX da Narwal com o sistema de Invoice. Abaixo o link da documentação enviada pela empresa. Desconheço procedimentos, gentileza informar o que há necessidade do nosso lado para avaliação. Acredito que uma </t>
-  </si>
-  <si>
-    <t>37552</t>
-  </si>
-  <si>
-    <t>Requisições BINAAR - Reunião</t>
-  </si>
-  <si>
-    <t>Bom dia. Solicitação de implementação de sistema WMS para requisição de itens na manutenção de equipamentos pneumáticos. Utilização de coletor para leitura dos itens utilizados em cada equipamentos consertado. Importante ressaltar que existem itens utilizados que não são fornecidos pela BINAAR, como</t>
-  </si>
-  <si>
-    <t>37746</t>
-  </si>
-  <si>
-    <t>Altona || Consignados - Diferença nos saldos</t>
-  </si>
-  <si>
-    <t>Sandro! O estoque de consignados ainda não fecha, perceba na comparação que eu fiz. Nela eu conferi entradas e consumo no Benner e no SNB, mas os saldos finais são diferentes. De onde eu tirei o saldo de R$ 521.678,11. Usando teu relatório e excluindo alguns grupos que não devem estar ali: Podes ver</t>
-  </si>
-  <si>
-    <t>33631</t>
-  </si>
-  <si>
-    <t>Sistema de corridas - Custos - Reunião</t>
-  </si>
-  <si>
-    <t>Solicito revisão nas informações de custos no sistema de corridas Incluir novas informações de custos</t>
-  </si>
-  <si>
-    <t>37301</t>
-  </si>
-  <si>
-    <t>Registro de solda Digital</t>
-  </si>
-  <si>
-    <t>Boa tarde Maciel, Tudo bem? Maciel, seria possível para o Registro de solda Digital assim que o soldador preencher a sequência o campo de IS já vir automático com as duas IS que estão cadastradas no roteiro? O soldador só iria selecionar a qual ele iria usar dependendo o estágio da peça conforme rot</t>
-  </si>
-  <si>
-    <t>Danilo da Silva Pereira</t>
-  </si>
-  <si>
-    <t>33956</t>
-  </si>
-  <si>
-    <t>Definição de metas de custos de manutenção (META GERAL) (copy)</t>
-  </si>
-  <si>
-    <t>Edson, Por gentileza criar campo para definição de metas para os custos de manutenção.</t>
-  </si>
-  <si>
-    <t>Robmar Xavier</t>
-  </si>
-  <si>
-    <t>12/05/2026</t>
-  </si>
-  <si>
-    <t>36842</t>
-  </si>
-  <si>
-    <t>Ajuste de Layout das ofertas</t>
-  </si>
-  <si>
-    <t>Boa Tarde Maciel, tudo bem? Favor padronizar a fonte das letras em nossas ofertas, após atualização as fontes estão aparecendo desconfiguradas e as ofertas estão saindo com "Feias". Segue exemplo a baixo: Note que os valores, e as informações da peça estão completamente fora do padrão. Aguardo corre</t>
-  </si>
-  <si>
-    <t>Alexandre Girardi</t>
-  </si>
-  <si>
-    <t>37323</t>
-  </si>
-  <si>
-    <t>BOTÃO DE EXCEL NA TELA WCPP22CP1</t>
-  </si>
-  <si>
-    <t>Bom dia, Favor criar um novo botão de exportar informações para o Excel na tela WCPP22CP1. At.te</t>
-  </si>
-  <si>
-    <t>38435</t>
-  </si>
-  <si>
-    <t>Divergência Integração Requisições FEADLER | BINAAR | KITO</t>
-  </si>
-  <si>
-    <t>Boa tarde a todos! Ações para correção dos registros do processo de requisições e compra de materiais de peças de reposição dos fornecedores FEADLER e BINAAR. 1. @Sandro Schram: orientação do Alexandro é desenvolvimento de melhoria Sistema para lançamento item a item (não item genérico). Como na tel</t>
-  </si>
-  <si>
-    <t>Paulo Giovani da Cruz</t>
-  </si>
-  <si>
-    <t>13/05/2026</t>
-  </si>
-  <si>
-    <t>32079</t>
-  </si>
-  <si>
-    <t>Homologação IMPORTA_OS e EXPORTA_OS para a virada do MES (copy)</t>
-  </si>
-  <si>
-    <t>Prezados, Precisamos validar a documentação enviada pela Directa, conforme reunião da ultima semana. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>31701</t>
-  </si>
-  <si>
-    <t>Levantamento de dados para Residencia de IA</t>
-  </si>
-  <si>
-    <t>23/02/2026</t>
-  </si>
-  <si>
-    <t>36055</t>
-  </si>
-  <si>
-    <t>IDENTIFICADOR ESPECIAL - LOT NUMBER (copy)</t>
-  </si>
-  <si>
-    <t>37169</t>
-  </si>
-  <si>
-    <t>Alteração em relatorio dentro do sistema "Apontamento de produção" (copy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Boa tarde, solicito a alteração no relatório de apontamento por funcionário quando "gerar o Excel". Preciso que no relatório saia o turno e o setor que cada funcionário faz parte ( inspeção END ou DIM). Motivo: Facilitar e otimizar o tempo de elaboração do relatório disponibilizado para liderança e </t>
-  </si>
-  <si>
-    <t>36641</t>
-  </si>
-  <si>
-    <t>Sequencial number Clientes (copy)</t>
-  </si>
-  <si>
-    <t>Ter uma tela para poder priorizar máquinas por sku, informando prioridade, máquina e tempo. (copy) (copy) (copy) (copy)</t>
-  </si>
-  <si>
-    <t>36063</t>
-  </si>
-  <si>
-    <t>Liberação Ensaio Mecanico Automatico (copy)</t>
-  </si>
-  <si>
-    <t>35727</t>
-  </si>
-  <si>
-    <t>Erro Planilhão - Itens conjuntos (copy)</t>
-  </si>
-  <si>
-    <t>Boa tarde Pela primeira vez na UPR, teremos um item de fundido que atenderá a dois conjuntos diferentes. Atualmente, temos 13 peças do fundido em processo e 4 peças dos conjuntos em depósito. No entanto, o Planilhão está considerando apenas 1 peça em estoque, não reconhecendo as outras 3. É importan</t>
-  </si>
-  <si>
-    <t>Taynara Frare</t>
-  </si>
-  <si>
-    <t>Fazer uma tela para informar a OP e a quantidade refugada, alimentado o campo APS_PlanoOPRot_17. Com isso para considerar se a op está atendida teria que considerar qtd apontada + qtd refugada (copy)</t>
-  </si>
-  <si>
-    <t>Dashboard de Change Log - Governança de TI</t>
-  </si>
-  <si>
-    <t>Período</t>
-  </si>
-  <si>
-    <t>SPRINT 2026-13</t>
-  </si>
-  <si>
-    <t>Base</t>
-  </si>
-  <si>
-    <t>Tickets corporativos para intranet / Power BI / Excel</t>
-  </si>
-  <si>
-    <t>Total de tickets</t>
-  </si>
-  <si>
-    <t>% dentro do SLA</t>
-  </si>
-  <si>
-    <t>Tempo médio (dias)</t>
-  </si>
-  <si>
-    <t>Áreas atendidas</t>
-  </si>
-  <si>
-    <t>Status final</t>
-  </si>
-  <si>
-    <t>Encerrado</t>
-  </si>
-  <si>
-    <t>Resumo Executivo</t>
-  </si>
-  <si>
-    <t>Tickets por Área</t>
-  </si>
-  <si>
-    <t>Distribuição por Tipo</t>
-  </si>
-  <si>
-    <t>Cumprimento SLA (15 dias)</t>
-  </si>
-  <si>
-    <t>Status Final</t>
-  </si>
-  <si>
-    <t>Tickets por Semana</t>
-  </si>
-  <si>
-    <t>Volume</t>
-  </si>
-  <si>
-    <t>Muito Alta</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1908,21 +1953,21 @@
         <v>37</v>
       </c>
       <c r="M3" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N3" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="B4" s="2" t="s">
-        <v>31</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>17</v>
@@ -1969,25 +2014,25 @@
         <v>48</v>
       </c>
       <c r="B5" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C5" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="2" t="s">
+      <c r="F5" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="F5" s="2" t="s">
+      <c r="G5" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G5" s="2" t="s">
+      <c r="H5" s="2" t="s">
         <v>52</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>53</v>
       </c>
       <c r="I5" s="2" t="s">
         <v>23</v>
@@ -1996,7 +2041,7 @@
         <v>35</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>54</v>
@@ -2005,10 +2050,10 @@
         <v>27</v>
       </c>
       <c r="N5" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O5" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -2043,7 +2088,7 @@
         <v>24</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L6" s="2" t="s">
         <v>26</v>
@@ -2060,28 +2105,28 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I7" s="2" t="s">
         <v>23</v>
@@ -2096,21 +2141,21 @@
         <v>26</v>
       </c>
       <c r="M7" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N7" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O7" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O7" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C8" s="2" t="s">
         <v>17</v>
@@ -2119,16 +2164,16 @@
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I8" s="2" t="s">
         <v>23</v>
@@ -2154,37 +2199,37 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I9" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J9" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K9" s="2" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="L9" s="2" t="s">
         <v>26</v>
@@ -2193,15 +2238,15 @@
         <v>27</v>
       </c>
       <c r="N9" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O9" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O9" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>31</v>
@@ -2213,16 +2258,16 @@
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="I10" s="2" t="s">
         <v>23</v>
@@ -2240,18 +2285,18 @@
         <v>27</v>
       </c>
       <c r="N10" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O10" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O10" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>78</v>
+        <v>82</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C11" s="2" t="s">
         <v>17</v>
@@ -2260,16 +2305,16 @@
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>79</v>
+        <v>84</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I11" s="2" t="s">
         <v>23</v>
@@ -2278,19 +2323,19 @@
         <v>35</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="L11" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M11" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="O11" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O11" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -2307,7 +2352,7 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>33</v>
@@ -2322,10 +2367,10 @@
         <v>23</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K12" s="2" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="L12" s="2" t="s">
         <v>54</v>
@@ -2342,28 +2387,28 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I13" s="2" t="s">
         <v>23</v>
@@ -2378,13 +2423,13 @@
         <v>37</v>
       </c>
       <c r="M13" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N13" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="O13" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O13" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -2401,7 +2446,7 @@
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>89</v>
+        <v>97</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>33</v>
@@ -2425,21 +2470,21 @@
         <v>37</v>
       </c>
       <c r="M14" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N14" s="2" t="s">
+      <c r="O14" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O14" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>17</v>
@@ -2448,22 +2493,22 @@
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>92</v>
+        <v>100</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>93</v>
+        <v>101</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I15" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="K15" s="2" t="s">
         <v>25</v>
@@ -2478,15 +2523,15 @@
         <v>46</v>
       </c>
       <c r="O15" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>97</v>
+        <v>105</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>17</v>
@@ -2495,25 +2540,25 @@
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="I16" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J16" s="2" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>26</v>
@@ -2522,7 +2567,7 @@
         <v>27</v>
       </c>
       <c r="N16" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="O16" s="2" t="s">
         <v>29</v>
@@ -2530,10 +2575,10 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C17" s="2" t="s">
         <v>17</v>
@@ -2542,16 +2587,16 @@
         <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>107</v>
+        <v>114</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I17" s="2" t="s">
         <v>23</v>
@@ -2577,28 +2622,28 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>109</v>
+        <v>116</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>111</v>
+        <v>118</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>112</v>
+        <v>119</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I18" s="2" t="s">
         <v>58</v>
@@ -2607,7 +2652,7 @@
         <v>35</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="L18" s="2" t="s">
         <v>26</v>
@@ -2616,15 +2661,15 @@
         <v>27</v>
       </c>
       <c r="N18" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O18" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O18" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>114</v>
+        <v>121</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>31</v>
@@ -2636,16 +2681,16 @@
         <v>18</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>115</v>
+        <v>122</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>116</v>
+        <v>123</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>117</v>
+        <v>124</v>
       </c>
       <c r="I19" s="2" t="s">
         <v>23</v>
@@ -2654,7 +2699,7 @@
         <v>24</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>26</v>
@@ -2671,10 +2716,10 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>98</v>
+        <v>106</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>17</v>
@@ -2683,16 +2728,16 @@
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="I20" s="2" t="s">
         <v>23</v>
@@ -2718,10 +2763,10 @@
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>122</v>
+        <v>130</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>17</v>
@@ -2730,22 +2775,22 @@
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>124</v>
+        <v>132</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I21" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J21" s="2" t="s">
-        <v>125</v>
+        <v>133</v>
       </c>
       <c r="K21" s="2" t="s">
         <v>25</v>
@@ -2757,15 +2802,15 @@
         <v>27</v>
       </c>
       <c r="N21" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O21" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>127</v>
+        <v>135</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>31</v>
@@ -2777,31 +2822,31 @@
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>128</v>
+        <v>136</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>129</v>
+        <v>137</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>130</v>
+        <v>138</v>
       </c>
       <c r="I22" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="L22" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M22" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N22" s="2" t="s">
         <v>46</v>
@@ -2812,28 +2857,28 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>132</v>
+        <v>140</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I23" s="2" t="s">
         <v>23</v>
@@ -2848,68 +2893,68 @@
         <v>26</v>
       </c>
       <c r="M23" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N23" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O23" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O23" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>133</v>
+        <v>141</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>134</v>
+        <v>142</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I24" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J24" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M24" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N24" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N24" s="2" t="s">
+      <c r="O24" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>136</v>
+        <v>145</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C25" s="2" t="s">
         <v>17</v>
@@ -2918,16 +2963,16 @@
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>138</v>
+        <v>147</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>139</v>
+        <v>148</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I25" s="2" t="s">
         <v>23</v>
@@ -2965,7 +3010,7 @@
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>33</v>
@@ -2983,7 +3028,7 @@
         <v>35</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>54</v>
@@ -2992,39 +3037,39 @@
         <v>27</v>
       </c>
       <c r="N26" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O26" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O26" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>141</v>
+        <v>150</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>142</v>
+        <v>151</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J27" s="2" t="s">
         <v>35</v>
@@ -3036,21 +3081,21 @@
         <v>37</v>
       </c>
       <c r="M27" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N27" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N27" s="2" t="s">
+      <c r="O27" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O27" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>143</v>
+        <v>152</v>
       </c>
       <c r="B28" s="2" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C28" s="2" t="s">
         <v>17</v>
@@ -3059,16 +3104,16 @@
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>144</v>
+        <v>154</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="G28" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H28" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I28" s="2" t="s">
         <v>23</v>
@@ -3077,13 +3122,13 @@
         <v>24</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>28</v>
@@ -3094,10 +3139,10 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B29" s="2" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C29" s="2" t="s">
         <v>17</v>
@@ -3106,16 +3151,16 @@
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>149</v>
+        <v>159</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H29" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I29" s="2" t="s">
         <v>23</v>
@@ -3124,13 +3169,13 @@
         <v>24</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>36</v>
+        <v>143</v>
       </c>
       <c r="L29" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>28</v>
@@ -3141,10 +3186,10 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>151</v>
+        <v>161</v>
       </c>
       <c r="B30" s="2" t="s">
-        <v>152</v>
+        <v>162</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>17</v>
@@ -3153,16 +3198,16 @@
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>153</v>
+        <v>163</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>154</v>
+        <v>164</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H30" s="2" t="s">
-        <v>155</v>
+        <v>165</v>
       </c>
       <c r="I30" s="2" t="s">
         <v>23</v>
@@ -3188,10 +3233,10 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>156</v>
+        <v>166</v>
       </c>
       <c r="B31" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>17</v>
@@ -3200,16 +3245,16 @@
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>157</v>
+        <v>167</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>158</v>
+        <v>168</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H31" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I31" s="2" t="s">
         <v>23</v>
@@ -3235,28 +3280,28 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B32" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H32" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I32" s="2" t="s">
         <v>23</v>
@@ -3265,7 +3310,7 @@
         <v>35</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>26</v>
@@ -3274,18 +3319,18 @@
         <v>27</v>
       </c>
       <c r="N32" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O32" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O32" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="C33" s="2" t="s">
         <v>17</v>
@@ -3294,16 +3339,16 @@
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>162</v>
+        <v>173</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>163</v>
+        <v>174</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H33" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I33" s="2" t="s">
         <v>23</v>
@@ -3329,28 +3374,28 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>85</v>
+        <v>92</v>
       </c>
       <c r="B34" s="2" t="s">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>36</v>
+        <v>95</v>
       </c>
       <c r="G34" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H34" s="2" t="s">
-        <v>88</v>
+        <v>96</v>
       </c>
       <c r="I34" s="2" t="s">
         <v>23</v>
@@ -3359,24 +3404,24 @@
         <v>35</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L34" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N34" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N34" s="2" t="s">
+      <c r="O34" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O34" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>31</v>
@@ -3388,22 +3433,22 @@
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H35" s="2" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
       <c r="I35" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J35" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K35" s="2" t="s">
         <v>25</v>
@@ -3423,37 +3468,37 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
       <c r="B36" s="2" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C36" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D36" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E36" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F36" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G36" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="H36" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E36" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="G36" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="H36" s="2" t="s">
-        <v>72</v>
-      </c>
       <c r="I36" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="J36" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>26</v>
@@ -3462,18 +3507,18 @@
         <v>27</v>
       </c>
       <c r="N36" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O36" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O36" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>172</v>
+        <v>184</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C37" s="2" t="s">
         <v>17</v>
@@ -3482,16 +3527,16 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>173</v>
+        <v>185</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>174</v>
+        <v>186</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H37" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I37" s="2" t="s">
         <v>23</v>
@@ -3517,10 +3562,10 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>175</v>
+        <v>187</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C38" s="2" t="s">
         <v>17</v>
@@ -3529,16 +3574,16 @@
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>176</v>
+        <v>188</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>177</v>
+        <v>189</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H38" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I38" s="2" t="s">
         <v>23</v>
@@ -3547,13 +3592,13 @@
         <v>24</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="L38" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M38" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N38" s="2" t="s">
         <v>28</v>
@@ -3564,10 +3609,10 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>178</v>
+        <v>190</v>
       </c>
       <c r="B39" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="C39" s="2" t="s">
         <v>17</v>
@@ -3576,16 +3621,16 @@
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>180</v>
+        <v>192</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H39" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I39" s="2" t="s">
         <v>23</v>
@@ -3611,7 +3656,7 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>181</v>
+        <v>193</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>31</v>
@@ -3623,16 +3668,16 @@
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>182</v>
+        <v>194</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>183</v>
+        <v>195</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H40" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="I40" s="2" t="s">
         <v>23</v>
@@ -3658,10 +3703,10 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>185</v>
+        <v>197</v>
       </c>
       <c r="B41" s="2" t="s">
-        <v>137</v>
+        <v>146</v>
       </c>
       <c r="C41" s="2" t="s">
         <v>17</v>
@@ -3670,16 +3715,16 @@
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>186</v>
+        <v>198</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H41" s="2" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
       <c r="I41" s="2" t="s">
         <v>23</v>
@@ -3705,10 +3750,10 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>188</v>
+        <v>200</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C42" s="2" t="s">
         <v>17</v>
@@ -3717,16 +3762,16 @@
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>189</v>
+        <v>201</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>190</v>
+        <v>202</v>
       </c>
       <c r="G42" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H42" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I42" s="2" t="s">
         <v>23</v>
@@ -3752,10 +3797,10 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>191</v>
+        <v>203</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>31</v>
+        <v>204</v>
       </c>
       <c r="C43" s="2" t="s">
         <v>17</v>
@@ -3764,16 +3809,16 @@
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="G43" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H43" s="2" t="s">
-        <v>194</v>
+        <v>207</v>
       </c>
       <c r="I43" s="2" t="s">
         <v>23</v>
@@ -3799,37 +3844,37 @@
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>69</v>
+        <v>208</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H44" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I44" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J44" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>26</v>
@@ -3838,45 +3883,45 @@
         <v>27</v>
       </c>
       <c r="N44" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O44" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O44" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>69</v>
+        <v>210</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J45" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>36</v>
+        <v>77</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>26</v>
@@ -3885,15 +3930,15 @@
         <v>27</v>
       </c>
       <c r="N45" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O45" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O45" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>197</v>
+        <v>212</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>31</v>
@@ -3905,16 +3950,16 @@
         <v>18</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>198</v>
+        <v>213</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>199</v>
+        <v>214</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H46" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="I46" s="2" t="s">
         <v>23</v>
@@ -3923,13 +3968,13 @@
         <v>24</v>
       </c>
       <c r="K46" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L46" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M46" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N46" s="2" t="s">
         <v>28</v>
@@ -3940,7 +3985,7 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>201</v>
+        <v>216</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
@@ -3952,16 +3997,16 @@
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>202</v>
+        <v>217</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>203</v>
+        <v>218</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H47" s="2" t="s">
-        <v>204</v>
+        <v>219</v>
       </c>
       <c r="I47" s="2" t="s">
         <v>23</v>
@@ -3987,10 +4032,10 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>205</v>
+        <v>220</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
         <v>17</v>
@@ -3999,16 +4044,16 @@
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>206</v>
+        <v>221</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>207</v>
+        <v>222</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H48" s="2" t="s">
-        <v>208</v>
+        <v>223</v>
       </c>
       <c r="I48" s="2" t="s">
         <v>58</v>
@@ -4017,7 +4062,7 @@
         <v>24</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>36</v>
+        <v>59</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>26</v>
@@ -4034,10 +4079,10 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>209</v>
+        <v>224</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>17</v>
@@ -4046,16 +4091,16 @@
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>210</v>
+        <v>226</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H49" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="I49" s="2" t="s">
         <v>23</v>
@@ -4081,28 +4126,28 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>213</v>
+        <v>229</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>215</v>
+        <v>231</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>216</v>
+        <v>232</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H50" s="2" t="s">
-        <v>217</v>
+        <v>233</v>
       </c>
       <c r="I50" s="2" t="s">
         <v>23</v>
@@ -4117,39 +4162,39 @@
         <v>26</v>
       </c>
       <c r="M50" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N50" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O50" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O50" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>218</v>
+        <v>234</v>
       </c>
       <c r="B51" s="2" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>219</v>
+        <v>235</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>220</v>
+        <v>236</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H51" s="2" t="s">
-        <v>221</v>
+        <v>237</v>
       </c>
       <c r="I51" s="2" t="s">
         <v>23</v>
@@ -4167,18 +4212,18 @@
         <v>27</v>
       </c>
       <c r="N51" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O51" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O51" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>222</v>
+        <v>238</v>
       </c>
       <c r="B52" s="2" t="s">
-        <v>223</v>
+        <v>61</v>
       </c>
       <c r="C52" s="2" t="s">
         <v>17</v>
@@ -4187,22 +4232,22 @@
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>225</v>
+        <v>240</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H52" s="2" t="s">
-        <v>226</v>
+        <v>241</v>
       </c>
       <c r="I52" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K52" s="2" t="s">
         <v>25</v>
@@ -4222,10 +4267,10 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>227</v>
+        <v>242</v>
       </c>
       <c r="B53" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C53" s="2" t="s">
         <v>17</v>
@@ -4234,16 +4279,16 @@
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>229</v>
+        <v>244</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H53" s="2" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="I53" s="2" t="s">
         <v>23</v>
@@ -4269,31 +4314,31 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>230</v>
+        <v>245</v>
       </c>
       <c r="B54" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C54" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>231</v>
+        <v>246</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H54" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I54" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J54" s="2" t="s">
         <v>35</v>
@@ -4308,45 +4353,45 @@
         <v>27</v>
       </c>
       <c r="N54" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O54" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O54" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>232</v>
+        <v>247</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C55" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>233</v>
+        <v>248</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H55" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I55" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J55" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="L55" s="2" t="s">
         <v>26</v>
@@ -4355,18 +4400,18 @@
         <v>27</v>
       </c>
       <c r="N55" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O55" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O55" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>234</v>
+        <v>249</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C56" s="2" t="s">
         <v>17</v>
@@ -4375,16 +4420,16 @@
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>235</v>
+        <v>250</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>236</v>
+        <v>251</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H56" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="I56" s="2" t="s">
         <v>23</v>
@@ -4410,57 +4455,57 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>240</v>
+        <v>255</v>
       </c>
       <c r="G57" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H57" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I57" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J57" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L57" s="2" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="M57" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N57" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N57" s="2" t="s">
+      <c r="O57" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O57" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>241</v>
+        <v>256</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C58" s="2" t="s">
         <v>17</v>
@@ -4469,22 +4514,22 @@
         <v>18</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>242</v>
+        <v>257</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>243</v>
+        <v>258</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H58" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I58" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="K58" s="2" t="s">
         <v>25</v>
@@ -4496,7 +4541,7 @@
         <v>27</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>47</v>
@@ -4504,10 +4549,10 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>245</v>
+        <v>260</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="C59" s="2" t="s">
         <v>17</v>
@@ -4516,16 +4561,16 @@
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>246</v>
+        <v>261</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>247</v>
+        <v>262</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H59" s="2" t="s">
-        <v>248</v>
+        <v>263</v>
       </c>
       <c r="I59" s="2" t="s">
         <v>23</v>
@@ -4534,27 +4579,27 @@
         <v>35</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M59" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N59" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N59" s="2" t="s">
+      <c r="O59" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O59" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>249</v>
+        <v>264</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>31</v>
+        <v>265</v>
       </c>
       <c r="C60" s="2" t="s">
         <v>17</v>
@@ -4563,16 +4608,16 @@
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>251</v>
+        <v>267</v>
       </c>
       <c r="G60" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H60" s="2" t="s">
-        <v>252</v>
+        <v>268</v>
       </c>
       <c r="I60" s="2" t="s">
         <v>23</v>
@@ -4587,18 +4632,18 @@
         <v>26</v>
       </c>
       <c r="M60" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N60" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O60" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O60" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>253</v>
+        <v>269</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>31</v>
@@ -4610,16 +4655,16 @@
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>254</v>
+        <v>270</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>255</v>
+        <v>271</v>
       </c>
       <c r="G61" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H61" s="2" t="s">
-        <v>256</v>
+        <v>272</v>
       </c>
       <c r="I61" s="2" t="s">
         <v>23</v>
@@ -4645,10 +4690,10 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>257</v>
+        <v>273</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>17</v>
@@ -4657,22 +4702,22 @@
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>258</v>
+        <v>274</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>259</v>
+        <v>275</v>
       </c>
       <c r="G62" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H62" s="2" t="s">
-        <v>260</v>
+        <v>276</v>
       </c>
       <c r="I62" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>261</v>
+        <v>277</v>
       </c>
       <c r="K62" s="2" t="s">
         <v>25</v>
@@ -4684,7 +4729,7 @@
         <v>27</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>47</v>
@@ -4692,10 +4737,10 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>262</v>
+        <v>278</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>263</v>
+        <v>153</v>
       </c>
       <c r="C63" s="2" t="s">
         <v>17</v>
@@ -4704,16 +4749,16 @@
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>264</v>
+        <v>279</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>265</v>
+        <v>280</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H63" s="2" t="s">
-        <v>266</v>
+        <v>281</v>
       </c>
       <c r="I63" s="2" t="s">
         <v>23</v>
@@ -4722,13 +4767,13 @@
         <v>24</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>267</v>
+        <v>87</v>
       </c>
       <c r="L63" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>28</v>
@@ -4739,10 +4784,10 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>268</v>
+        <v>282</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>269</v>
+        <v>283</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>17</v>
@@ -4751,34 +4796,34 @@
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>270</v>
+        <v>284</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H64" s="2" t="s">
-        <v>272</v>
+        <v>286</v>
       </c>
       <c r="I64" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J64" s="2" t="s">
-        <v>244</v>
+        <v>259</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>273</v>
+        <v>287</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M64" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N64" s="2" t="s">
         <v>38</v>
-      </c>
-      <c r="N64" s="2" t="s">
-        <v>39</v>
       </c>
       <c r="O64" s="2" t="s">
         <v>47</v>
@@ -4786,10 +4831,10 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>274</v>
+        <v>288</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C65" s="2" t="s">
         <v>17</v>
@@ -4798,16 +4843,16 @@
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>276</v>
+        <v>290</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H65" s="2" t="s">
-        <v>108</v>
+        <v>115</v>
       </c>
       <c r="I65" s="2" t="s">
         <v>23</v>
@@ -4833,31 +4878,31 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>277</v>
+        <v>291</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>278</v>
+        <v>292</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H66" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I66" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J66" s="2" t="s">
         <v>35</v>
@@ -4869,21 +4914,21 @@
         <v>37</v>
       </c>
       <c r="M66" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N66" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N66" s="2" t="s">
+      <c r="O66" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O66" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>279</v>
+        <v>293</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="C67" s="2" t="s">
         <v>17</v>
@@ -4892,16 +4937,16 @@
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>280</v>
+        <v>294</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>281</v>
+        <v>295</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H67" s="2" t="s">
-        <v>282</v>
+        <v>296</v>
       </c>
       <c r="I67" s="2" t="s">
         <v>23</v>
@@ -4910,27 +4955,27 @@
         <v>35</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>283</v>
+        <v>297</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M67" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N67" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O67" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O67" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C68" s="2" t="s">
         <v>17</v>
@@ -4939,16 +4984,16 @@
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>285</v>
+        <v>299</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>286</v>
+        <v>300</v>
       </c>
       <c r="G68" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H68" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I68" s="2" t="s">
         <v>23</v>
@@ -4957,13 +5002,13 @@
         <v>24</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>267</v>
+        <v>87</v>
       </c>
       <c r="L68" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N68" s="2" t="s">
         <v>28</v>
@@ -4974,10 +5019,10 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C69" s="2" t="s">
         <v>17</v>
@@ -4986,22 +5031,22 @@
         <v>18</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>288</v>
+        <v>302</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="G69" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="K69" s="2" t="s">
         <v>36</v>
@@ -5010,21 +5055,21 @@
         <v>37</v>
       </c>
       <c r="M69" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N69" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N69" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="O69" s="2" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>17</v>
@@ -5033,22 +5078,22 @@
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>292</v>
+        <v>306</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H70" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I70" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J70" s="2" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="K70" s="2" t="s">
         <v>36</v>
@@ -5057,39 +5102,39 @@
         <v>37</v>
       </c>
       <c r="M70" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N70" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N70" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="O70" s="2" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>293</v>
+        <v>307</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>294</v>
+        <v>308</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>295</v>
+        <v>309</v>
       </c>
       <c r="G71" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H71" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I71" s="2" t="s">
         <v>58</v>
@@ -5104,21 +5149,21 @@
         <v>37</v>
       </c>
       <c r="M71" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N71" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N71" s="2" t="s">
+      <c r="O71" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O71" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>296</v>
+        <v>310</v>
       </c>
       <c r="B72" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C72" s="2" t="s">
         <v>17</v>
@@ -5127,16 +5172,16 @@
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>297</v>
+        <v>311</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>298</v>
+        <v>312</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H72" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I72" s="2" t="s">
         <v>23</v>
@@ -5165,7 +5210,7 @@
         <v>48</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>49</v>
+        <v>31</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>17</v>
@@ -5174,25 +5219,25 @@
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>299</v>
+        <v>313</v>
       </c>
       <c r="F73" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="G73" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="G73" s="2" t="s">
+      <c r="H73" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="H73" s="2" t="s">
-        <v>53</v>
-      </c>
       <c r="I73" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>36</v>
+        <v>314</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>26</v>
@@ -5209,10 +5254,10 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>301</v>
+        <v>67</v>
       </c>
       <c r="C74" s="2" t="s">
         <v>17</v>
@@ -5221,16 +5266,16 @@
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>302</v>
+        <v>316</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H74" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="I74" s="2" t="s">
         <v>23</v>
@@ -5239,27 +5284,27 @@
         <v>35</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M74" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N74" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N74" s="2" t="s">
+      <c r="O74" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O74" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C75" s="2" t="s">
         <v>17</v>
@@ -5268,16 +5313,16 @@
         <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>306</v>
+        <v>321</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>307</v>
+        <v>322</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>23</v>
@@ -5303,10 +5348,10 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>308</v>
+        <v>323</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>17</v>
@@ -5315,22 +5360,22 @@
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>309</v>
+        <v>324</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>310</v>
+        <v>325</v>
       </c>
       <c r="G76" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H76" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I76" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>131</v>
+        <v>139</v>
       </c>
       <c r="K76" s="2" t="s">
         <v>25</v>
@@ -5350,10 +5395,10 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>311</v>
+        <v>326</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>17</v>
@@ -5362,16 +5407,16 @@
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>312</v>
+        <v>327</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>313</v>
+        <v>328</v>
       </c>
       <c r="G77" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H77" s="2" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="I77" s="2" t="s">
         <v>23</v>
@@ -5397,10 +5442,10 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>287</v>
+        <v>301</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="C78" s="2" t="s">
         <v>17</v>
@@ -5409,22 +5454,22 @@
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>314</v>
+        <v>329</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>289</v>
+        <v>303</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H78" s="2" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I78" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J78" s="2" t="s">
-        <v>290</v>
+        <v>304</v>
       </c>
       <c r="K78" s="2" t="s">
         <v>36</v>
@@ -5433,42 +5478,42 @@
         <v>37</v>
       </c>
       <c r="M78" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N78" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N78" s="2" t="s">
-        <v>39</v>
-      </c>
       <c r="O78" s="2" t="s">
-        <v>291</v>
+        <v>305</v>
       </c>
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>315</v>
+        <v>330</v>
       </c>
       <c r="B79" s="2" t="s">
-        <v>31</v>
+        <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>70</v>
+        <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>316</v>
+        <v>331</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>316</v>
+        <v>332</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H79" s="2" t="s">
-        <v>72</v>
+        <v>333</v>
       </c>
       <c r="I79" s="2" t="s">
-        <v>73</v>
+        <v>23</v>
       </c>
       <c r="J79" s="2" t="s">
         <v>35</v>
@@ -5477,24 +5522,24 @@
         <v>36</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="M79" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N79" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N79" s="2" t="s">
+      <c r="O79" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O79" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>318</v>
+        <v>335</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C80" s="2" t="s">
         <v>17</v>
@@ -5503,16 +5548,16 @@
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>319</v>
+        <v>336</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>320</v>
+        <v>337</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H80" s="2" t="s">
-        <v>321</v>
+        <v>338</v>
       </c>
       <c r="I80" s="2" t="s">
         <v>23</v>
@@ -5521,13 +5566,13 @@
         <v>24</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="L80" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>28</v>
@@ -5538,7 +5583,7 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>322</v>
+        <v>339</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>31</v>
@@ -5550,16 +5595,16 @@
         <v>18</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>323</v>
+        <v>340</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>324</v>
+        <v>341</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>184</v>
+        <v>196</v>
       </c>
       <c r="I81" s="2" t="s">
         <v>23</v>
@@ -5585,10 +5630,10 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>325</v>
+        <v>342</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C82" s="2" t="s">
         <v>17</v>
@@ -5597,22 +5642,22 @@
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>326</v>
+        <v>343</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>327</v>
+        <v>344</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H82" s="2" t="s">
-        <v>328</v>
+        <v>345</v>
       </c>
       <c r="I82" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K82" s="2" t="s">
         <v>25</v>
@@ -5632,7 +5677,7 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>329</v>
+        <v>346</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>31</v>
@@ -5644,16 +5689,16 @@
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>330</v>
+        <v>347</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>331</v>
+        <v>348</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H83" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="I83" s="2" t="s">
         <v>23</v>
@@ -5679,10 +5724,10 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>333</v>
+        <v>350</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="C84" s="2" t="s">
         <v>17</v>
@@ -5691,16 +5736,16 @@
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>334</v>
+        <v>351</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>335</v>
+        <v>352</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H84" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I84" s="2" t="s">
         <v>23</v>
@@ -5715,18 +5760,18 @@
         <v>26</v>
       </c>
       <c r="M84" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N84" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O84" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O84" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>336</v>
+        <v>353</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>31</v>
@@ -5738,10 +5783,10 @@
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>337</v>
+        <v>354</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>338</v>
+        <v>355</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>21</v>
@@ -5756,13 +5801,13 @@
         <v>24</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>339</v>
+        <v>356</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>26</v>
       </c>
       <c r="M85" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N85" s="2" t="s">
         <v>28</v>
@@ -5773,10 +5818,10 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="C86" s="2" t="s">
         <v>17</v>
@@ -5785,16 +5830,16 @@
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>341</v>
+        <v>358</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H86" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I86" s="2" t="s">
         <v>23</v>
@@ -5803,13 +5848,13 @@
         <v>24</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>36</v>
+        <v>314</v>
       </c>
       <c r="L86" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M86" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N86" s="2" t="s">
         <v>28</v>
@@ -5820,10 +5865,10 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>343</v>
+        <v>360</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>31</v>
+        <v>225</v>
       </c>
       <c r="C87" s="2" t="s">
         <v>17</v>
@@ -5832,16 +5877,16 @@
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>344</v>
+        <v>361</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>345</v>
+        <v>362</v>
       </c>
       <c r="G87" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H87" s="2" t="s">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="I87" s="2" t="s">
         <v>23</v>
@@ -5867,10 +5912,10 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="C88" s="2" t="s">
         <v>17</v>
@@ -5879,45 +5924,45 @@
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>346</v>
+        <v>363</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H88" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I88" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>36</v>
+        <v>364</v>
       </c>
       <c r="L88" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M88" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N88" s="2" t="s">
         <v>46</v>
       </c>
       <c r="O88" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>340</v>
+        <v>357</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="C89" s="2" t="s">
         <v>17</v>
@@ -5926,45 +5971,45 @@
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>348</v>
+        <v>365</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>342</v>
+        <v>359</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H89" s="2" t="s">
-        <v>164</v>
+        <v>175</v>
       </c>
       <c r="I89" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>347</v>
+        <v>319</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>36</v>
+        <v>364</v>
       </c>
       <c r="L89" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="M89" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N89" s="2" t="s">
         <v>46</v>
       </c>
       <c r="O89" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>349</v>
+        <v>366</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>31</v>
+        <v>162</v>
       </c>
       <c r="C90" s="2" t="s">
         <v>17</v>
@@ -5973,16 +6018,16 @@
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>350</v>
+        <v>367</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>351</v>
+        <v>368</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H90" s="2" t="s">
-        <v>352</v>
+        <v>369</v>
       </c>
       <c r="I90" s="2" t="s">
         <v>23</v>
@@ -6008,10 +6053,10 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>353</v>
+        <v>370</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>17</v>
@@ -6020,16 +6065,16 @@
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>354</v>
+        <v>371</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>355</v>
+        <v>372</v>
       </c>
       <c r="G91" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H91" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I91" s="2" t="s">
         <v>23</v>
@@ -6038,7 +6083,7 @@
         <v>35</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>36</v>
+        <v>87</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>54</v>
@@ -6047,18 +6092,18 @@
         <v>27</v>
       </c>
       <c r="N91" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O91" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O91" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>301</v>
+        <v>67</v>
       </c>
       <c r="C92" s="2" t="s">
         <v>17</v>
@@ -6067,16 +6112,16 @@
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>356</v>
+        <v>373</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>303</v>
+        <v>317</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H92" s="2" t="s">
-        <v>304</v>
+        <v>318</v>
       </c>
       <c r="I92" s="2" t="s">
         <v>23</v>
@@ -6085,7 +6130,7 @@
         <v>35</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>36</v>
+        <v>53</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>26</v>
@@ -6094,15 +6139,15 @@
         <v>27</v>
       </c>
       <c r="N92" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O92" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O92" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="93" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>357</v>
+        <v>374</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>31</v>
@@ -6114,16 +6159,16 @@
         <v>18</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>358</v>
+        <v>375</v>
       </c>
       <c r="F93" s="2" t="s">
-        <v>359</v>
+        <v>376</v>
       </c>
       <c r="G93" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H93" s="2" t="s">
-        <v>360</v>
+        <v>377</v>
       </c>
       <c r="I93" s="2" t="s">
         <v>23</v>
@@ -6149,31 +6194,31 @@
     </row>
     <row r="94" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>361</v>
+        <v>378</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C94" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="F94" s="2" t="s">
-        <v>362</v>
+        <v>379</v>
       </c>
       <c r="G94" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H94" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I94" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J94" s="2" t="s">
         <v>35</v>
@@ -6185,21 +6230,21 @@
         <v>37</v>
       </c>
       <c r="M94" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N94" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N94" s="2" t="s">
+      <c r="O94" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O94" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="95" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>363</v>
+        <v>380</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="C95" s="2" t="s">
         <v>17</v>
@@ -6208,16 +6253,16 @@
         <v>18</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>364</v>
+        <v>381</v>
       </c>
       <c r="F95" s="2" t="s">
-        <v>365</v>
+        <v>382</v>
       </c>
       <c r="G95" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H95" s="2" t="s">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="I95" s="2" t="s">
         <v>23</v>
@@ -6232,7 +6277,7 @@
         <v>37</v>
       </c>
       <c r="M95" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N95" s="2" t="s">
         <v>28</v>
@@ -6243,7 +6288,7 @@
     </row>
     <row r="96" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>366</v>
+        <v>383</v>
       </c>
       <c r="B96" s="2" t="s">
         <v>31</v>
@@ -6255,10 +6300,10 @@
         <v>18</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>367</v>
+        <v>384</v>
       </c>
       <c r="F96" s="2" t="s">
-        <v>368</v>
+        <v>385</v>
       </c>
       <c r="G96" s="2" t="s">
         <v>21</v>
@@ -6282,18 +6327,18 @@
         <v>27</v>
       </c>
       <c r="N96" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O96" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O96" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="97" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>369</v>
+        <v>386</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="C97" s="2" t="s">
         <v>17</v>
@@ -6302,16 +6347,16 @@
         <v>18</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>370</v>
+        <v>387</v>
       </c>
       <c r="F97" s="2" t="s">
-        <v>371</v>
+        <v>388</v>
       </c>
       <c r="G97" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H97" s="2" t="s">
-        <v>146</v>
+        <v>156</v>
       </c>
       <c r="I97" s="2" t="s">
         <v>23</v>
@@ -6326,18 +6371,18 @@
         <v>37</v>
       </c>
       <c r="M97" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N97" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N97" s="2" t="s">
+      <c r="O97" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O97" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="98" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>372</v>
+        <v>389</v>
       </c>
       <c r="B98" s="2" t="s">
         <v>31</v>
@@ -6349,16 +6394,16 @@
         <v>18</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>373</v>
+        <v>390</v>
       </c>
       <c r="F98" s="2" t="s">
-        <v>374</v>
+        <v>391</v>
       </c>
       <c r="G98" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H98" s="2" t="s">
-        <v>332</v>
+        <v>349</v>
       </c>
       <c r="I98" s="2" t="s">
         <v>58</v>
@@ -6373,21 +6418,21 @@
         <v>26</v>
       </c>
       <c r="M98" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N98" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="O98" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O98" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="99" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>375</v>
+        <v>392</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C99" s="2" t="s">
         <v>17</v>
@@ -6396,16 +6441,16 @@
         <v>18</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>376</v>
+        <v>393</v>
       </c>
       <c r="F99" s="2" t="s">
-        <v>377</v>
+        <v>394</v>
       </c>
       <c r="G99" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H99" s="2" t="s">
-        <v>378</v>
+        <v>395</v>
       </c>
       <c r="I99" s="2" t="s">
         <v>23</v>
@@ -6431,10 +6476,10 @@
     </row>
     <row r="100" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>379</v>
+        <v>396</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>31</v>
+        <v>172</v>
       </c>
       <c r="C100" s="2" t="s">
         <v>17</v>
@@ -6443,22 +6488,22 @@
         <v>18</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>380</v>
+        <v>397</v>
       </c>
       <c r="F100" s="2" t="s">
-        <v>381</v>
+        <v>398</v>
       </c>
       <c r="G100" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H100" s="2" t="s">
-        <v>382</v>
+        <v>399</v>
       </c>
       <c r="I100" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J100" s="2" t="s">
-        <v>383</v>
+        <v>143</v>
       </c>
       <c r="K100" s="2" t="s">
         <v>25</v>
@@ -6467,21 +6512,21 @@
         <v>26</v>
       </c>
       <c r="M100" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N100" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O100" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="101" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>384</v>
+        <v>400</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>31</v>
+        <v>93</v>
       </c>
       <c r="C101" s="2" t="s">
         <v>17</v>
@@ -6490,25 +6535,25 @@
         <v>18</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>385</v>
+        <v>401</v>
       </c>
       <c r="F101" s="2" t="s">
-        <v>386</v>
+        <v>402</v>
       </c>
       <c r="G101" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H101" s="2" t="s">
-        <v>387</v>
+        <v>403</v>
       </c>
       <c r="I101" s="2" t="s">
         <v>58</v>
       </c>
       <c r="J101" s="2" t="s">
-        <v>383</v>
+        <v>143</v>
       </c>
       <c r="K101" s="2" t="s">
-        <v>36</v>
+        <v>91</v>
       </c>
       <c r="L101" s="2" t="s">
         <v>26</v>
@@ -6517,18 +6562,18 @@
         <v>27</v>
       </c>
       <c r="N101" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O101" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="102" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>388</v>
+        <v>404</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="C102" s="2" t="s">
         <v>17</v>
@@ -6537,16 +6582,16 @@
         <v>18</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>389</v>
+        <v>405</v>
       </c>
       <c r="F102" s="2" t="s">
-        <v>390</v>
+        <v>406</v>
       </c>
       <c r="G102" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H102" s="2" t="s">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="I102" s="2" t="s">
         <v>23</v>
@@ -6572,10 +6617,10 @@
     </row>
     <row r="103" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>391</v>
+        <v>407</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>31</v>
+        <v>408</v>
       </c>
       <c r="C103" s="2" t="s">
         <v>17</v>
@@ -6584,22 +6629,22 @@
         <v>18</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>392</v>
+        <v>409</v>
       </c>
       <c r="F103" s="2" t="s">
-        <v>393</v>
+        <v>410</v>
       </c>
       <c r="G103" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H103" s="2" t="s">
-        <v>394</v>
+        <v>411</v>
       </c>
       <c r="I103" s="2" t="s">
         <v>23</v>
       </c>
       <c r="J103" s="2" t="s">
-        <v>395</v>
+        <v>314</v>
       </c>
       <c r="K103" s="2" t="s">
         <v>25</v>
@@ -6608,13 +6653,13 @@
         <v>26</v>
       </c>
       <c r="M103" s="2" t="s">
-        <v>64</v>
+        <v>27</v>
       </c>
       <c r="N103" s="2" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="O103" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="104" spans="1:15" x14ac:dyDescent="0.25">
@@ -6631,7 +6676,7 @@
         <v>18</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F104" s="2" t="s">
         <v>33</v>
@@ -6649,165 +6694,165 @@
         <v>35</v>
       </c>
       <c r="K104" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L104" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M104" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N104" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N104" s="2" t="s">
+      <c r="O104" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O104" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="105" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>396</v>
+        <v>412</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>301</v>
+        <v>72</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D105" s="2" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>397</v>
+        <v>413</v>
       </c>
       <c r="F105" s="2" t="s">
-        <v>398</v>
+        <v>413</v>
       </c>
       <c r="G105" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H105" s="2" t="s">
-        <v>304</v>
+        <v>75</v>
       </c>
       <c r="I105" s="2" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="J105" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K105" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L105" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M105" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N105" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N105" s="2" t="s">
+      <c r="O105" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O105" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="106" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>399</v>
+        <v>414</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="D106" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="F106" s="2" t="s">
-        <v>400</v>
+        <v>415</v>
       </c>
       <c r="G106" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H106" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I106" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J106" s="2" t="s">
-        <v>401</v>
+        <v>416</v>
       </c>
       <c r="K106" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L106" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M106" s="2" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="N106" s="2" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
       <c r="O106" s="2" t="s">
-        <v>96</v>
+        <v>104</v>
       </c>
     </row>
     <row r="107" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>402</v>
+        <v>417</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D107" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="F107" s="2" t="s">
-        <v>403</v>
+        <v>418</v>
       </c>
       <c r="G107" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H107" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I107" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J107" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K107" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L107" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M107" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N107" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N107" s="2" t="s">
+      <c r="O107" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O107" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="108" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>404</v>
+        <v>419</v>
       </c>
       <c r="B108" s="2" t="s">
         <v>31</v>
@@ -6819,16 +6864,16 @@
         <v>18</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>405</v>
+        <v>420</v>
       </c>
       <c r="F108" s="2" t="s">
-        <v>406</v>
+        <v>421</v>
       </c>
       <c r="G108" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H108" s="2" t="s">
-        <v>200</v>
+        <v>215</v>
       </c>
       <c r="I108" s="2" t="s">
         <v>23</v>
@@ -6837,74 +6882,74 @@
         <v>35</v>
       </c>
       <c r="K108" s="2" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="L108" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M108" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N108" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N108" s="2" t="s">
+      <c r="O108" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O108" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="109" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>407</v>
+        <v>422</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D109" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="F109" s="2" t="s">
-        <v>408</v>
+        <v>423</v>
       </c>
       <c r="G109" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H109" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I109" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J109" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K109" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L109" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M109" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N109" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N109" s="2" t="s">
+      <c r="O109" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O109" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="110" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>31</v>
+        <v>61</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>17</v>
@@ -6913,16 +6958,16 @@
         <v>18</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>409</v>
+        <v>424</v>
       </c>
       <c r="F110" s="2" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="G110" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H110" s="2" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="I110" s="2" t="s">
         <v>23</v>
@@ -6937,154 +6982,154 @@
         <v>37</v>
       </c>
       <c r="M110" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N110" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N110" s="2" t="s">
+      <c r="O110" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O110" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="111" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>410</v>
+        <v>425</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D111" s="2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="F111" s="2" t="s">
-        <v>411</v>
+        <v>426</v>
       </c>
       <c r="G111" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H111" s="2" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I111" s="2" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="J111" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K111" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L111" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M111" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N111" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N111" s="2" t="s">
+      <c r="O111" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O111" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="112" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>412</v>
+        <v>427</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="D112" s="2" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>413</v>
+        <v>428</v>
       </c>
       <c r="F112" s="2" t="s">
-        <v>414</v>
+        <v>428</v>
       </c>
       <c r="G112" s="2" t="s">
         <v>21</v>
       </c>
       <c r="H112" s="2" t="s">
-        <v>415</v>
+        <v>75</v>
       </c>
       <c r="I112" s="2" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="J112" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K112" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L112" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M112" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N112" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N112" s="2" t="s">
+      <c r="O112" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O112" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="113" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>396</v>
+        <v>429</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>301</v>
+        <v>72</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>17</v>
       </c>
       <c r="D113" s="2" t="s">
-        <v>18</v>
+        <v>73</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>416</v>
+        <v>430</v>
       </c>
       <c r="F113" s="2" t="s">
-        <v>398</v>
+        <v>430</v>
       </c>
       <c r="G113" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H113" s="2" t="s">
-        <v>304</v>
+        <v>75</v>
       </c>
       <c r="I113" s="2" t="s">
-        <v>23</v>
+        <v>76</v>
       </c>
       <c r="J113" s="2" t="s">
         <v>35</v>
       </c>
       <c r="K113" s="2" t="s">
-        <v>36</v>
+        <v>319</v>
       </c>
       <c r="L113" s="2" t="s">
         <v>37</v>
       </c>
       <c r="M113" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="N113" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N113" s="2" t="s">
+      <c r="O113" s="2" t="s">
         <v>39</v>
-      </c>
-      <c r="O113" s="2" t="s">
-        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -7100,23 +7145,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>417</v>
+        <v>431</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>418</v>
+        <v>432</v>
       </c>
       <c r="B2" t="s">
-        <v>419</v>
+        <v>433</v>
       </c>
       <c r="D2" t="s">
-        <v>420</v>
+        <v>434</v>
       </c>
       <c r="E2" t="s">
-        <v>421</v>
+        <v>435</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -7124,16 +7169,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>423</v>
+        <v>437</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>424</v>
+        <v>438</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>425</v>
+        <v>439</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -7141,18 +7186,18 @@
         <v>112</v>
       </c>
       <c r="D5" s="5">
-        <v>0.19736842105263158</v>
+        <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>25.26</v>
+        <v>21.78</v>
       </c>
       <c r="J5" s="4">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>426</v>
+        <v>440</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -7173,7 +7218,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>427</v>
+        <v>441</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -7204,12 +7249,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>428</v>
+        <v>442</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>422</v>
+        <v>436</v>
       </c>
       <c r="B2">
         <v>112</v>
@@ -7217,41 +7262,41 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5">
-        <v>0.19736842105263158</v>
+        <v>0</v>
       </c>
       <c r="B5" s="7"/>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>25.26</v>
+        <v>21.78</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>13</v>
+        <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>429</v>
+        <v>443</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>430</v>
+        <v>444</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>431</v>
+        <v>445</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>432</v>
+        <v>446</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>433</v>
+        <v>447</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>434</v>
+        <v>448</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -7259,7 +7304,7 @@
         <v>31</v>
       </c>
       <c r="B10">
-        <v>75</v>
+        <v>24</v>
       </c>
       <c r="D10" t="s">
         <v>17</v>
@@ -7268,16 +7313,16 @@
         <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>435</v>
+        <v>449</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>64</v>
+        <v>450</v>
       </c>
       <c r="K10">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="M10" t="s">
         <v>26</v>
@@ -7286,27 +7331,27 @@
         <v>67</v>
       </c>
       <c r="P10" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="Q10">
-        <v>20</v>
+        <v>14</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="B11">
-        <v>7</v>
+        <v>19</v>
       </c>
       <c r="D11" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="E11">
         <v>12</v>
       </c>
       <c r="G11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="H11">
         <v>29</v>
@@ -7315,7 +7360,7 @@
         <v>27</v>
       </c>
       <c r="K11">
-        <v>61</v>
+        <v>112</v>
       </c>
       <c r="M11" t="s">
         <v>37</v>
@@ -7324,21 +7369,21 @@
         <v>26</v>
       </c>
       <c r="P11" t="s">
-        <v>126</v>
+        <v>134</v>
       </c>
       <c r="Q11">
-        <v>2</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>105</v>
+        <v>83</v>
       </c>
       <c r="B12">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="D12" t="s">
-        <v>110</v>
+        <v>117</v>
       </c>
       <c r="E12">
         <v>3</v>
@@ -7350,13 +7395,13 @@
         <v>83</v>
       </c>
       <c r="J12" t="s">
-        <v>436</v>
+        <v>451</v>
       </c>
       <c r="K12">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>317</v>
+        <v>334</v>
       </c>
       <c r="N12">
         <v>1</v>
@@ -7365,56 +7410,50 @@
         <v>46</v>
       </c>
       <c r="Q12">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>49</v>
+        <v>93</v>
       </c>
       <c r="B13">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="D13" t="s">
-        <v>214</v>
+        <v>230</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
       <c r="G13" t="s">
-        <v>437</v>
+        <v>452</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>135</v>
+        <v>144</v>
       </c>
       <c r="N13">
         <v>3</v>
       </c>
-      <c r="P13" t="s">
-        <v>103</v>
-      </c>
-      <c r="Q13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>86</v>
+        <v>67</v>
       </c>
       <c r="B14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D14" t="s">
-        <v>239</v>
+        <v>254</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
       <c r="G14" t="s">
-        <v>438</v>
+        <v>453</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -7425,22 +7464,16 @@
       <c r="N14">
         <v>9</v>
       </c>
-      <c r="P14" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q14">
-        <v>4</v>
-      </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>301</v>
+        <v>99</v>
       </c>
       <c r="B15">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="M15" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="N15">
         <v>6</v>
@@ -7448,13 +7481,13 @@
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>16</v>
+        <v>172</v>
       </c>
       <c r="B16">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="M16" t="s">
-        <v>439</v>
+        <v>454</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -7462,13 +7495,13 @@
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>98</v>
+        <v>153</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="M17" t="s">
-        <v>440</v>
+        <v>455</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -7476,29 +7509,29 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>137</v>
+        <v>16</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>152</v>
+        <v>61</v>
       </c>
       <c r="B19">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="1:7" x14ac:dyDescent="0.25">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>223</v>
+        <v>162</v>
       </c>
       <c r="B20">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>0</v>
@@ -7507,7 +7540,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>442</v>
+        <v>457</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -7515,154 +7548,190 @@
     </row>
     <row r="21" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>263</v>
+        <v>225</v>
       </c>
       <c r="B21" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>122</v>
+        <v>30</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>86</v>
+        <v>31</v>
       </c>
       <c r="F21" s="2">
-        <v>84</v>
+        <v>240</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>123</v>
+        <v>32</v>
       </c>
     </row>
     <row r="22" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>269</v>
+        <v>106</v>
       </c>
       <c r="B22" s="2">
+        <v>2</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="F22" s="2">
+        <v>240</v>
+      </c>
+      <c r="G22" s="2" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A23" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" s="2">
+        <v>2</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="F23" s="2">
+        <v>240</v>
+      </c>
+      <c r="G23" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A24" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="B24" s="2">
         <v>1</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>90</v>
-      </c>
-      <c r="E22" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F22" s="2">
-        <v>74</v>
-      </c>
-      <c r="G22" s="2" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="D23" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="E23" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="F23" s="2">
-        <v>60</v>
-      </c>
-      <c r="G23" s="2" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>31</v>
       </c>
       <c r="F24" s="2">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A25" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="B25" s="2">
+        <v>1</v>
+      </c>
       <c r="D25" s="2" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>98</v>
+        <v>31</v>
       </c>
       <c r="F25" s="2">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A26" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B26" s="2">
+        <v>1</v>
+      </c>
       <c r="D26" s="2" t="s">
-        <v>388</v>
+        <v>141</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>91</v>
+        <v>72</v>
       </c>
       <c r="F26" s="2">
-        <v>46</v>
+        <v>240</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>389</v>
-      </c>
-    </row>
-    <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A27" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B27" s="2">
+        <v>1</v>
+      </c>
       <c r="D27" s="2" t="s">
-        <v>257</v>
+        <v>150</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>31</v>
+        <v>72</v>
       </c>
       <c r="F27" s="2">
-        <v>43</v>
+        <v>240</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B28" s="2">
+        <v>1</v>
+      </c>
       <c r="D28" s="2" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>31</v>
+        <v>153</v>
       </c>
       <c r="F28" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>222</v>
+        <v>92</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>223</v>
+        <v>93</v>
       </c>
       <c r="F29" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>224</v>
+        <v>176</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>325</v>
+        <v>187</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>31</v>
+        <v>83</v>
       </c>
       <c r="F30" s="2">
-        <v>18</v>
+        <v>240</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>326</v>
+        <v>188</v>
       </c>
     </row>
   </sheetData>
